--- a/quan-ly-du-an/quan-ly-du-an.xlsx
+++ b/quan-ly-du-an/quan-ly-du-an.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Esclipe_Web\Quan ly du an HTTT\quan-ly-du-an\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8D70FAC-BDC1-4185-821A-3B8793BE59D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3655C91-85D1-47BB-B424-8247AAD608DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1848" yWindow="1848" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -627,7 +627,7 @@
     <t>Tối thiểu 20 trang ruột</t>
   </si>
   <si>
-    <t>Chưa kiểm tra</t>
+    <t>Đạt (ước tính 35–40 trang)</t>
   </si>
   <si>
     <t>Chữ trong bảng, hình là tiếng Việt</t>
@@ -675,7 +675,7 @@
     <t>Ghi chú đọc bài báo, thuật ngữ, điểm mâu thuẫn, tài liệu tham khảo</t>
   </si>
   <si>
-    <t>Nhập số liệu, script kiểm tra số liệu, khung LaTeX, Chương 1–2, sơ đồ</t>
+    <t>Số liệu, kiểm tra số liệu, mô phỏng, PLS-SEM, Monte Carlo, Excel/MS Project, Chương 1–4</t>
   </si>
   <si>
     <t>Tổng</t>
@@ -1652,7 +1652,7 @@
       <c r="H13" s="6"/>
       <c r="I13" s="9">
         <f>IFERROR(SUMPRODUCT(I14:I18,J14:J18)/SUM(J14:J18),0)</f>
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="J13" s="8">
         <f>SUM(J14:J18)</f>
@@ -1763,25 +1763,29 @@
       <c r="D16" s="12">
         <v>46322</v>
       </c>
-      <c r="E16" s="12"/>
-      <c r="F16" s="12"/>
+      <c r="E16" s="12">
+        <v>46321</v>
+      </c>
+      <c r="F16" s="12">
+        <v>46321</v>
+      </c>
       <c r="G16" s="13">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="H16" s="14" t="str">
+      <c r="H16" s="14">
         <f>IF(F16="","",F16-D16)</f>
-        <v/>
+        <v>-1</v>
       </c>
       <c r="I16" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" s="16">
         <v>4</v>
       </c>
       <c r="K16" s="10" t="str">
         <f>IF(I16&gt;=1,"Hoàn thành",IF(I16&gt;0,"Đang làm",IF(D16&lt;$B$2,"Trễ hạn","Chưa bắt đầu")))</f>
-        <v>Chưa bắt đầu</v>
+        <v>Hoàn thành</v>
       </c>
       <c r="L16" s="11" t="s">
         <v>49</v>
@@ -1803,25 +1807,29 @@
       <c r="D17" s="12">
         <v>46322</v>
       </c>
-      <c r="E17" s="12"/>
-      <c r="F17" s="12"/>
+      <c r="E17" s="12">
+        <v>46321</v>
+      </c>
+      <c r="F17" s="12">
+        <v>46321</v>
+      </c>
       <c r="G17" s="13">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="H17" s="14" t="str">
+      <c r="H17" s="14">
         <f>IF(F17="","",F17-D17)</f>
-        <v/>
+        <v>-1</v>
       </c>
       <c r="I17" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" s="16">
         <v>4</v>
       </c>
       <c r="K17" s="10" t="str">
         <f>IF(I17&gt;=1,"Hoàn thành",IF(I17&gt;0,"Đang làm",IF(D17&lt;$B$2,"Trễ hạn","Chưa bắt đầu")))</f>
-        <v>Chưa bắt đầu</v>
+        <v>Hoàn thành</v>
       </c>
       <c r="L17" s="11" t="s">
         <v>52</v>
@@ -1843,25 +1851,29 @@
       <c r="D18" s="12">
         <v>46323</v>
       </c>
-      <c r="E18" s="12"/>
-      <c r="F18" s="12"/>
+      <c r="E18" s="12">
+        <v>46321</v>
+      </c>
+      <c r="F18" s="12">
+        <v>46321</v>
+      </c>
       <c r="G18" s="13">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="H18" s="14" t="str">
+      <c r="H18" s="14">
         <f>IF(F18="","",F18-D18)</f>
-        <v/>
+        <v>-2</v>
       </c>
       <c r="I18" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18" s="16">
         <v>8</v>
       </c>
       <c r="K18" s="10" t="str">
         <f>IF(I18&gt;=1,"Hoàn thành",IF(I18&gt;0,"Đang làm",IF(D18&lt;$B$2,"Trễ hạn","Chưa bắt đầu")))</f>
-        <v>Chưa bắt đầu</v>
+        <v>Hoàn thành</v>
       </c>
       <c r="L18" s="11" t="s">
         <v>55</v>
@@ -1894,7 +1906,7 @@
       <c r="H19" s="6"/>
       <c r="I19" s="9">
         <f>IFERROR(SUMPRODUCT(I20:I28,J20:J28)/SUM(J20:J28),0)</f>
-        <v>0.34615384615384615</v>
+        <v>0.9538461538461539</v>
       </c>
       <c r="J19" s="8">
         <f>SUM(J20:J28)</f>
@@ -2093,25 +2105,29 @@
       <c r="D24" s="12">
         <v>46324</v>
       </c>
-      <c r="E24" s="12"/>
-      <c r="F24" s="12"/>
+      <c r="E24" s="12">
+        <v>46321</v>
+      </c>
+      <c r="F24" s="12">
+        <v>46321</v>
+      </c>
       <c r="G24" s="13">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="H24" s="14" t="str">
+      <c r="H24" s="14">
         <f t="shared" si="1"/>
-        <v/>
+        <v>-3</v>
       </c>
       <c r="I24" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24" s="16">
         <v>8</v>
       </c>
       <c r="K24" s="10" t="str">
         <f t="shared" si="2"/>
-        <v>Chưa bắt đầu</v>
+        <v>Hoàn thành</v>
       </c>
       <c r="L24" s="11" t="s">
         <v>73</v>
@@ -2133,25 +2149,29 @@
       <c r="D25" s="12">
         <v>46325</v>
       </c>
-      <c r="E25" s="12"/>
-      <c r="F25" s="12"/>
+      <c r="E25" s="12">
+        <v>46321</v>
+      </c>
+      <c r="F25" s="12">
+        <v>46321</v>
+      </c>
       <c r="G25" s="13">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="H25" s="14" t="str">
+      <c r="H25" s="14">
         <f t="shared" si="1"/>
-        <v/>
+        <v>-4</v>
       </c>
       <c r="I25" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J25" s="16">
         <v>6</v>
       </c>
       <c r="K25" s="10" t="str">
         <f t="shared" si="2"/>
-        <v>Chưa bắt đầu</v>
+        <v>Hoàn thành</v>
       </c>
       <c r="L25" s="11" t="s">
         <v>76</v>
@@ -2173,25 +2193,29 @@
       <c r="D26" s="12">
         <v>46326</v>
       </c>
-      <c r="E26" s="12"/>
-      <c r="F26" s="12"/>
+      <c r="E26" s="12">
+        <v>46321</v>
+      </c>
+      <c r="F26" s="12">
+        <v>46321</v>
+      </c>
       <c r="G26" s="13">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="H26" s="14" t="str">
+      <c r="H26" s="14">
         <f t="shared" si="1"/>
-        <v/>
+        <v>-5</v>
       </c>
       <c r="I26" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26" s="16">
         <v>8</v>
       </c>
       <c r="K26" s="10" t="str">
         <f t="shared" si="2"/>
-        <v>Chưa bắt đầu</v>
+        <v>Hoàn thành</v>
       </c>
       <c r="L26" s="11" t="s">
         <v>76</v>
@@ -2213,25 +2237,29 @@
       <c r="D27" s="12">
         <v>46327</v>
       </c>
-      <c r="E27" s="12"/>
-      <c r="F27" s="12"/>
+      <c r="E27" s="12">
+        <v>46321</v>
+      </c>
+      <c r="F27" s="12">
+        <v>46321</v>
+      </c>
       <c r="G27" s="13">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="H27" s="14" t="str">
+      <c r="H27" s="14">
         <f t="shared" si="1"/>
-        <v/>
+        <v>-6</v>
       </c>
       <c r="I27" s="15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27" s="16">
         <v>6</v>
       </c>
       <c r="K27" s="10" t="str">
         <f t="shared" si="2"/>
-        <v>Chưa bắt đầu</v>
+        <v>Hoàn thành</v>
       </c>
       <c r="L27" s="11" t="s">
         <v>76</v>
@@ -2253,7 +2281,9 @@
       <c r="D28" s="12">
         <v>46328</v>
       </c>
-      <c r="E28" s="12"/>
+      <c r="E28" s="12">
+        <v>46321</v>
+      </c>
       <c r="F28" s="12"/>
       <c r="G28" s="13">
         <f t="shared" si="0"/>
@@ -2264,14 +2294,14 @@
         <v/>
       </c>
       <c r="I28" s="15">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="J28" s="16">
         <v>6</v>
       </c>
       <c r="K28" s="10" t="str">
         <f t="shared" si="2"/>
-        <v>Chưa bắt đầu</v>
+        <v>Đang làm</v>
       </c>
       <c r="L28" s="11" t="s">
         <v>83</v>
@@ -2516,7 +2546,7 @@
       </c>
       <c r="I36" s="18">
         <f>(I6*J6+I9*J9+I13*J13+I19*J19+I29*J29+I33*J33)/(J6+J9+J13+J19+J29+J33)</f>
-        <v>0.42574257425742573</v>
+        <v>0.89702970297029694</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.3">
@@ -3515,7 +3545,7 @@
       </c>
       <c r="K15" s="22" t="str">
         <f>IF(WBS!$C16="","",IF(AND(WBS!$E16&lt;&gt;"",K$4&gt;=WBS!$E16,K$4&lt;=WBS!$F16),"■",IF(AND(K$4&gt;=WBS!$C16,K$4&lt;=WBS!$D16),"□","")))</f>
-        <v/>
+        <v>■</v>
       </c>
       <c r="L15" s="22" t="str">
         <f>IF(WBS!$C16="","",IF(AND(WBS!$E16&lt;&gt;"",L$4&gt;=WBS!$E16,L$4&lt;=WBS!$F16),"■",IF(AND(L$4&gt;=WBS!$C16,L$4&lt;=WBS!$D16),"□","")))</f>
@@ -3597,7 +3627,7 @@
       </c>
       <c r="K16" s="22" t="str">
         <f>IF(WBS!$C17="","",IF(AND(WBS!$E17&lt;&gt;"",K$4&gt;=WBS!$E17,K$4&lt;=WBS!$F17),"■",IF(AND(K$4&gt;=WBS!$C17,K$4&lt;=WBS!$D17),"□","")))</f>
-        <v/>
+        <v>■</v>
       </c>
       <c r="L16" s="22" t="str">
         <f>IF(WBS!$C17="","",IF(AND(WBS!$E17&lt;&gt;"",L$4&gt;=WBS!$E17,L$4&lt;=WBS!$F17),"■",IF(AND(L$4&gt;=WBS!$C17,L$4&lt;=WBS!$D17),"□","")))</f>
@@ -3679,7 +3709,7 @@
       </c>
       <c r="K17" s="22" t="str">
         <f>IF(WBS!$C18="","",IF(AND(WBS!$E18&lt;&gt;"",K$4&gt;=WBS!$E18,K$4&lt;=WBS!$F18),"■",IF(AND(K$4&gt;=WBS!$C18,K$4&lt;=WBS!$D18),"□","")))</f>
-        <v/>
+        <v>■</v>
       </c>
       <c r="L17" s="22" t="str">
         <f>IF(WBS!$C18="","",IF(AND(WBS!$E18&lt;&gt;"",L$4&gt;=WBS!$E18,L$4&lt;=WBS!$F18),"■",IF(AND(L$4&gt;=WBS!$C18,L$4&lt;=WBS!$D18),"□","")))</f>
@@ -4171,7 +4201,7 @@
       </c>
       <c r="K23" s="22" t="str">
         <f>IF(WBS!$C24="","",IF(AND(WBS!$E24&lt;&gt;"",K$4&gt;=WBS!$E24,K$4&lt;=WBS!$F24),"■",IF(AND(K$4&gt;=WBS!$C24,K$4&lt;=WBS!$D24),"□","")))</f>
-        <v/>
+        <v>■</v>
       </c>
       <c r="L23" s="22" t="str">
         <f>IF(WBS!$C24="","",IF(AND(WBS!$E24&lt;&gt;"",L$4&gt;=WBS!$E24,L$4&lt;=WBS!$F24),"■",IF(AND(L$4&gt;=WBS!$C24,L$4&lt;=WBS!$D24),"□","")))</f>
@@ -4253,7 +4283,7 @@
       </c>
       <c r="K24" s="22" t="str">
         <f>IF(WBS!$C25="","",IF(AND(WBS!$E25&lt;&gt;"",K$4&gt;=WBS!$E25,K$4&lt;=WBS!$F25),"■",IF(AND(K$4&gt;=WBS!$C25,K$4&lt;=WBS!$D25),"□","")))</f>
-        <v/>
+        <v>■</v>
       </c>
       <c r="L24" s="22" t="str">
         <f>IF(WBS!$C25="","",IF(AND(WBS!$E25&lt;&gt;"",L$4&gt;=WBS!$E25,L$4&lt;=WBS!$F25),"■",IF(AND(L$4&gt;=WBS!$C25,L$4&lt;=WBS!$D25),"□","")))</f>
@@ -4335,7 +4365,7 @@
       </c>
       <c r="K25" s="22" t="str">
         <f>IF(WBS!$C26="","",IF(AND(WBS!$E26&lt;&gt;"",K$4&gt;=WBS!$E26,K$4&lt;=WBS!$F26),"■",IF(AND(K$4&gt;=WBS!$C26,K$4&lt;=WBS!$D26),"□","")))</f>
-        <v/>
+        <v>■</v>
       </c>
       <c r="L25" s="22" t="str">
         <f>IF(WBS!$C26="","",IF(AND(WBS!$E26&lt;&gt;"",L$4&gt;=WBS!$E26,L$4&lt;=WBS!$F26),"■",IF(AND(L$4&gt;=WBS!$C26,L$4&lt;=WBS!$D26),"□","")))</f>
@@ -4417,7 +4447,7 @@
       </c>
       <c r="K26" s="22" t="str">
         <f>IF(WBS!$C27="","",IF(AND(WBS!$E27&lt;&gt;"",K$4&gt;=WBS!$E27,K$4&lt;=WBS!$F27),"■",IF(AND(K$4&gt;=WBS!$C27,K$4&lt;=WBS!$D27),"□","")))</f>
-        <v/>
+        <v>■</v>
       </c>
       <c r="L26" s="22" t="str">
         <f>IF(WBS!$C27="","",IF(AND(WBS!$E27&lt;&gt;"",L$4&gt;=WBS!$E27,L$4&lt;=WBS!$F27),"■",IF(AND(L$4&gt;=WBS!$C27,L$4&lt;=WBS!$D27),"□","")))</f>
@@ -5559,11 +5589,11 @@
         <v>2.5</v>
       </c>
       <c r="C5" s="15">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="D5" s="27">
         <f>B5*C5</f>
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="E5" s="11" t="s">
         <v>175</v>
@@ -5577,11 +5607,11 @@
         <v>2.5</v>
       </c>
       <c r="C6" s="15">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="D6" s="27">
         <f>B6*C6</f>
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="E6" s="11" t="s">
         <v>177</v>
@@ -5595,11 +5625,11 @@
         <v>2</v>
       </c>
       <c r="C7" s="15">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="D7" s="27">
         <f>B7*C7</f>
-        <v>0.4</v>
+        <v>2</v>
       </c>
       <c r="E7" s="11" t="s">
         <v>179</v>
@@ -5651,11 +5681,11 @@
       </c>
       <c r="C10" s="28">
         <f>D10/B10</f>
-        <v>0.36499999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="D10" s="29">
         <f>SUM(D5:D9)</f>
-        <v>3.65</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
@@ -5671,7 +5701,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
         <v>187</v>
       </c>
@@ -5803,19 +5833,19 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A6" s="30">
         <v>46321</v>
       </c>
       <c r="B6" s="23">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="C6" s="31" t="s">
         <v>204</v>
       </c>
       <c r="D6" s="10">
         <f>SUM($B$4:B6)</f>
-        <v>22</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -5824,7 +5854,7 @@
       </c>
       <c r="B7" s="24">
         <f>SUM(B4:B6)</f>
-        <v>22</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/quan-ly-du-an/quan-ly-du-an.xlsx
+++ b/quan-ly-du-an/quan-ly-du-an.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Esclipe_Web\Quan ly du an HTTT\quan-ly-du-an\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3655C91-85D1-47BB-B424-8247AAD608DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{579A1FAC-4FBD-4BA7-82D5-09F02EC42BFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1848" yWindow="1848" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="210">
   <si>
     <t>CẤU TRÚC PHÂN RÃ CÔNG VIỆC (WBS) – BÁO CÁO GIỮA KỲ</t>
   </si>
@@ -111,6 +111,9 @@
     <t>Mục barem</t>
   </si>
   <si>
+    <t>Nhóm công việc</t>
+  </si>
+  <si>
     <t>1</t>
   </si>
   <si>
@@ -180,6 +183,9 @@
     <t>docs/tai-lieu-tham-khao.md</t>
   </si>
   <si>
+    <t>Toàn dự án</t>
+  </si>
+  <si>
     <t>3</t>
   </si>
   <si>
@@ -585,6 +591,9 @@
     <t>Đáp ứng ở đâu</t>
   </si>
   <si>
+    <t>Mục</t>
+  </si>
+  <si>
     <t>Nội dung báo cáo: khái niệm, thành phần, mô hình, cách hoạt động, ứng dụng, ưu/nhược, xu hướng</t>
   </si>
   <si>
@@ -610,6 +619,9 @@
   </si>
   <si>
     <t>docs/phan-bien.md</t>
+  </si>
+  <si>
+    <t>Phản biện</t>
   </si>
   <si>
     <t>TỔNG</t>
@@ -788,7 +800,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -798,6 +810,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -812,10 +827,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -832,7 +850,7 @@
     <xf numFmtId="1" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="168" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -984,6 +1002,496 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="1"/>
+  <c:style val="2"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Mức độ hoàn thành theo nhóm công việc</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>WBS!$P$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>% hoàn thành</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="1"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>WBS!$O$6:$O$12</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>Khởi động dự án</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Đọc hiểu bài báo</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Tái hiện thực nghiệm</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Viết báo cáo</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Thuyết trình và nộp bài</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Quản lý dự án</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Toàn dự án</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>WBS!$P$6:$P$12</c:f>
+              <c:numCache>
+                <c:formatCode>0%</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.9538461538461539</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.89702970297029694</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-A976-4C94-B327-311B9C12BC84}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:axId val="10"/>
+        <c:axId val="100"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="10"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="100"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="1"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="100"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="1"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines/>
+        <c:numFmt formatCode="0%" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="10"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="1"/>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="1"/>
+  <c:style val="2"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Điểm tối đa và điểm dự kiến theo barem</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Barem!$B$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Điểm tối đa</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="1"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Barem!$G$5:$G$9</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Nội dung</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Tái hiện</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Mở rộng</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Thuyết trình</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Phản biện</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Barem!$B$5:$B$9</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-344E-4BF6-827F-64F7B1F3D506}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Barem!$D$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Điểm dự kiến</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </c:spPr>
+          <c:invertIfNegative val="1"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Barem!$G$5:$G$9</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Nội dung</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Tái hiện</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Mở rộng</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Thuyết trình</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Phản biện</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Barem!$D$5:$D$9</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-344E-4BF6-827F-64F7B1F3D506}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:axId val="10"/>
+        <c:axId val="100"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="10"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="100"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="1"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="100"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:numFmt formatCode="0.0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="10"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="1"/>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="5040000" cy="2880000"/>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="5760000" cy="2880000"/>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1271,7 +1779,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M38"/>
+  <dimension ref="A1:P38"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -1283,14 +1791,16 @@
     <col min="11" max="11" width="13" customWidth="1"/>
     <col min="12" max="12" width="30" customWidth="1"/>
     <col min="13" max="13" width="12" customWidth="1"/>
+    <col min="15" max="15" width="26" customWidth="1"/>
+    <col min="16" max="16" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -1298,12 +1808,12 @@
         <v>46321</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>3</v>
       </c>
@@ -1343,1226 +1853,1287 @@
       <c r="M5" s="5" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A6" s="6" t="s">
+      <c r="O5" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="P5" s="6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A6" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="7">
+      <c r="B6" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="8">
         <f>MIN(C7:C8)</f>
         <v>46313</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="8">
         <f>MAX(D7:D8)</f>
         <v>46313</v>
       </c>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="8">
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="9">
         <f t="shared" ref="G6:G34" si="0">D6-C6+1</f>
         <v>1</v>
       </c>
-      <c r="H6" s="6"/>
-      <c r="I6" s="9">
+      <c r="H6" s="7"/>
+      <c r="I6" s="10">
         <f>IFERROR(SUMPRODUCT(I7:I8,J7:J8)/SUM(J7:J8),0)</f>
         <v>0.75</v>
       </c>
-      <c r="J6" s="8">
+      <c r="J6" s="9">
         <f>SUM(J7:J8)</f>
         <v>4</v>
       </c>
-      <c r="K6" s="6"/>
-      <c r="L6" s="6"/>
-      <c r="M6" s="6"/>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A7" s="10" t="s">
-        <v>18</v>
+      <c r="K6" s="7"/>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7"/>
+      <c r="O6" s="11" t="str">
+        <f>WBS!B6</f>
+        <v>Khởi động dự án</v>
+      </c>
+      <c r="P6" s="12">
+        <f>I6</f>
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A7" s="13" t="s">
+        <v>19</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="12">
+        <v>20</v>
+      </c>
+      <c r="C7" s="14">
         <v>46313</v>
       </c>
-      <c r="D7" s="12">
+      <c r="D7" s="14">
         <v>46313</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="14">
         <v>46314</v>
       </c>
-      <c r="F7" s="12">
+      <c r="F7" s="14">
         <v>46314</v>
       </c>
-      <c r="G7" s="13">
+      <c r="G7" s="15">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="H7" s="14">
+      <c r="H7" s="16">
         <f>IF(F7="","",F7-D7)</f>
         <v>1</v>
       </c>
-      <c r="I7" s="15">
+      <c r="I7" s="17">
         <v>1</v>
       </c>
-      <c r="J7" s="16">
+      <c r="J7" s="18">
         <v>3</v>
       </c>
-      <c r="K7" s="10" t="str">
+      <c r="K7" s="13" t="str">
         <f>IF(I7&gt;=1,"Hoàn thành",IF(I7&gt;0,"Đang làm",IF(D7&lt;$B$2,"Trễ hạn","Chưa bắt đầu")))</f>
         <v>Hoàn thành</v>
       </c>
       <c r="L7" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="M7" s="10" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A8" s="10" t="s">
+      <c r="M7" s="13" t="s">
         <v>22</v>
       </c>
+      <c r="O7" s="11" t="str">
+        <f>WBS!B9</f>
+        <v>Đọc hiểu bài báo</v>
+      </c>
+      <c r="P7" s="12">
+        <f>I9</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A8" s="13" t="s">
+        <v>23</v>
+      </c>
       <c r="B8" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="12">
+        <v>24</v>
+      </c>
+      <c r="C8" s="14">
         <v>46313</v>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="14">
         <v>46313</v>
       </c>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="13">
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="15">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="H8" s="14" t="str">
+      <c r="H8" s="16" t="str">
         <f>IF(F8="","",F8-D8)</f>
         <v/>
       </c>
-      <c r="I8" s="15">
+      <c r="I8" s="17">
         <v>0</v>
       </c>
-      <c r="J8" s="16">
+      <c r="J8" s="18">
         <v>1</v>
       </c>
-      <c r="K8" s="10" t="str">
+      <c r="K8" s="13" t="str">
         <f>IF(I8&gt;=1,"Hoàn thành",IF(I8&gt;0,"Đang làm",IF(D8&lt;$B$2,"Trễ hạn","Chưa bắt đầu")))</f>
         <v>Trễ hạn</v>
       </c>
       <c r="L8" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="M8" s="10" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A9" s="6" t="s">
+      <c r="M8" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="O8" s="11" t="str">
+        <f>WBS!B13</f>
+        <v>Tái hiện thực nghiệm</v>
+      </c>
+      <c r="P8" s="12">
+        <f>I13</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A9" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="7">
+      <c r="B9" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="8">
         <f>MIN(C10:C12)</f>
         <v>46314</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D9" s="8">
         <f>MAX(D10:D12)</f>
         <v>46316</v>
       </c>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="8">
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="9">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="H9" s="6"/>
-      <c r="I9" s="9">
+      <c r="H9" s="7"/>
+      <c r="I9" s="10">
         <f>IFERROR(SUMPRODUCT(I10:I12,J10:J12)/SUM(J10:J12),0)</f>
         <v>1</v>
       </c>
-      <c r="J9" s="8">
+      <c r="J9" s="9">
         <f>SUM(J10:J12)</f>
         <v>12</v>
       </c>
-      <c r="K9" s="6"/>
-      <c r="L9" s="6"/>
-      <c r="M9" s="6"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A10" s="10" t="s">
-        <v>28</v>
+      <c r="K9" s="7"/>
+      <c r="L9" s="7"/>
+      <c r="M9" s="7"/>
+      <c r="O9" s="11" t="str">
+        <f>WBS!B19</f>
+        <v>Viết báo cáo</v>
+      </c>
+      <c r="P9" s="12">
+        <f>I19</f>
+        <v>0.9538461538461539</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A10" s="13" t="s">
+        <v>29</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10" s="12">
+        <v>30</v>
+      </c>
+      <c r="C10" s="14">
         <v>46314</v>
       </c>
-      <c r="D10" s="12">
+      <c r="D10" s="14">
         <v>46315</v>
       </c>
-      <c r="E10" s="12">
+      <c r="E10" s="14">
         <v>46315</v>
       </c>
-      <c r="F10" s="12">
+      <c r="F10" s="14">
         <v>46315</v>
       </c>
-      <c r="G10" s="13">
+      <c r="G10" s="15">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="H10" s="14">
+      <c r="H10" s="16">
         <f>IF(F10="","",F10-D10)</f>
         <v>0</v>
       </c>
-      <c r="I10" s="15">
+      <c r="I10" s="17">
         <v>1</v>
       </c>
-      <c r="J10" s="16">
+      <c r="J10" s="18">
         <v>6</v>
       </c>
-      <c r="K10" s="10" t="str">
+      <c r="K10" s="13" t="str">
         <f>IF(I10&gt;=1,"Hoàn thành",IF(I10&gt;0,"Đang làm",IF(D10&lt;$B$2,"Trễ hạn","Chưa bắt đầu")))</f>
         <v>Hoàn thành</v>
       </c>
       <c r="L10" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="M10" s="10" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A11" s="10" t="s">
+      <c r="M10" s="13" t="s">
         <v>32</v>
       </c>
+      <c r="O10" s="11" t="str">
+        <f>WBS!B29</f>
+        <v>Thuyết trình và nộp bài</v>
+      </c>
+      <c r="P10" s="12">
+        <f>I29</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A11" s="13" t="s">
+        <v>33</v>
+      </c>
       <c r="B11" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="C11" s="12">
+        <v>34</v>
+      </c>
+      <c r="C11" s="14">
         <v>46316</v>
       </c>
-      <c r="D11" s="12">
+      <c r="D11" s="14">
         <v>46316</v>
       </c>
-      <c r="E11" s="12">
+      <c r="E11" s="14">
         <v>46315</v>
       </c>
-      <c r="F11" s="12">
+      <c r="F11" s="14">
         <v>46315</v>
       </c>
-      <c r="G11" s="13">
+      <c r="G11" s="15">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="H11" s="14">
+      <c r="H11" s="16">
         <f>IF(F11="","",F11-D11)</f>
         <v>-1</v>
       </c>
-      <c r="I11" s="15">
+      <c r="I11" s="17">
         <v>1</v>
       </c>
-      <c r="J11" s="16">
+      <c r="J11" s="18">
         <v>4</v>
       </c>
-      <c r="K11" s="10" t="str">
+      <c r="K11" s="13" t="str">
         <f>IF(I11&gt;=1,"Hoàn thành",IF(I11&gt;0,"Đang làm",IF(D11&lt;$B$2,"Trễ hạn","Chưa bắt đầu")))</f>
         <v>Hoàn thành</v>
       </c>
       <c r="L11" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="M11" s="10" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A12" s="10" t="s">
+      <c r="M11" s="13" t="s">
         <v>36</v>
       </c>
+      <c r="O11" s="11" t="str">
+        <f>WBS!B33</f>
+        <v>Quản lý dự án</v>
+      </c>
+      <c r="P11" s="12">
+        <f>I33</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A12" s="13" t="s">
+        <v>37</v>
+      </c>
       <c r="B12" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="C12" s="12">
+        <v>38</v>
+      </c>
+      <c r="C12" s="14">
         <v>46316</v>
       </c>
-      <c r="D12" s="12">
+      <c r="D12" s="14">
         <v>46316</v>
       </c>
-      <c r="E12" s="12">
+      <c r="E12" s="14">
         <v>46315</v>
       </c>
-      <c r="F12" s="12">
+      <c r="F12" s="14">
         <v>46315</v>
       </c>
-      <c r="G12" s="13">
+      <c r="G12" s="15">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="H12" s="14">
+      <c r="H12" s="16">
         <f>IF(F12="","",F12-D12)</f>
         <v>-1</v>
       </c>
-      <c r="I12" s="15">
+      <c r="I12" s="17">
         <v>1</v>
       </c>
-      <c r="J12" s="16">
+      <c r="J12" s="18">
         <v>2</v>
       </c>
-      <c r="K12" s="10" t="str">
+      <c r="K12" s="13" t="str">
         <f>IF(I12&gt;=1,"Hoàn thành",IF(I12&gt;0,"Đang làm",IF(D12&lt;$B$2,"Trễ hạn","Chưa bắt đầu")))</f>
         <v>Hoàn thành</v>
       </c>
       <c r="L12" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="M12" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A13" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="M12" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="O12" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="C13" s="7">
+      <c r="P12" s="19">
+        <f>I36</f>
+        <v>0.89702970297029694</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A13" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" s="8">
         <f>MIN(C14:C18)</f>
         <v>46317</v>
       </c>
-      <c r="D13" s="7">
+      <c r="D13" s="8">
         <f>MAX(D14:D18)</f>
         <v>46323</v>
       </c>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
-      <c r="G13" s="8">
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="9">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="H13" s="6"/>
-      <c r="I13" s="9">
+      <c r="H13" s="7"/>
+      <c r="I13" s="10">
         <f>IFERROR(SUMPRODUCT(I14:I18,J14:J18)/SUM(J14:J18),0)</f>
         <v>1</v>
       </c>
-      <c r="J13" s="8">
+      <c r="J13" s="9">
         <f>SUM(J14:J18)</f>
         <v>24</v>
       </c>
-      <c r="K13" s="6"/>
-      <c r="L13" s="6"/>
-      <c r="M13" s="6"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A14" s="10" t="s">
-        <v>41</v>
+      <c r="K13" s="7"/>
+      <c r="L13" s="7"/>
+      <c r="M13" s="7"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A14" s="13" t="s">
+        <v>43</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="C14" s="12">
+        <v>44</v>
+      </c>
+      <c r="C14" s="14">
         <v>46317</v>
       </c>
-      <c r="D14" s="12">
+      <c r="D14" s="14">
         <v>46318</v>
       </c>
-      <c r="E14" s="12">
+      <c r="E14" s="14">
         <v>46321</v>
       </c>
-      <c r="F14" s="12">
+      <c r="F14" s="14">
         <v>46321</v>
       </c>
-      <c r="G14" s="13">
+      <c r="G14" s="15">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="H14" s="14">
+      <c r="H14" s="16">
         <f>IF(F14="","",F14-D14)</f>
         <v>3</v>
       </c>
-      <c r="I14" s="15">
+      <c r="I14" s="17">
         <v>1</v>
       </c>
-      <c r="J14" s="16">
+      <c r="J14" s="18">
         <v>3</v>
       </c>
-      <c r="K14" s="10" t="str">
+      <c r="K14" s="13" t="str">
         <f>IF(I14&gt;=1,"Hoàn thành",IF(I14&gt;0,"Đang làm",IF(D14&lt;$B$2,"Trễ hạn","Chưa bắt đầu")))</f>
         <v>Hoàn thành</v>
       </c>
       <c r="L14" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="M14" s="10" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A15" s="10" t="s">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="M14" s="13" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A15" s="13" t="s">
+        <v>46</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="C15" s="12">
+        <v>47</v>
+      </c>
+      <c r="C15" s="14">
         <v>46318</v>
       </c>
-      <c r="D15" s="12">
+      <c r="D15" s="14">
         <v>46318</v>
       </c>
-      <c r="E15" s="12">
+      <c r="E15" s="14">
         <v>46321</v>
       </c>
-      <c r="F15" s="12">
+      <c r="F15" s="14">
         <v>46321</v>
       </c>
-      <c r="G15" s="13">
+      <c r="G15" s="15">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="H15" s="14">
+      <c r="H15" s="16">
         <f>IF(F15="","",F15-D15)</f>
         <v>3</v>
       </c>
-      <c r="I15" s="15">
+      <c r="I15" s="17">
         <v>1</v>
       </c>
-      <c r="J15" s="16">
+      <c r="J15" s="18">
         <v>5</v>
       </c>
-      <c r="K15" s="10" t="str">
+      <c r="K15" s="13" t="str">
         <f>IF(I15&gt;=1,"Hoàn thành",IF(I15&gt;0,"Đang làm",IF(D15&lt;$B$2,"Trễ hạn","Chưa bắt đầu")))</f>
         <v>Hoàn thành</v>
       </c>
       <c r="L15" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="M15" s="10" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A16" s="10" t="s">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="M15" s="13" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A16" s="13" t="s">
+        <v>49</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="C16" s="12">
+        <v>50</v>
+      </c>
+      <c r="C16" s="14">
         <v>46322</v>
       </c>
-      <c r="D16" s="12">
+      <c r="D16" s="14">
         <v>46322</v>
       </c>
-      <c r="E16" s="12">
+      <c r="E16" s="14">
         <v>46321</v>
       </c>
-      <c r="F16" s="12">
+      <c r="F16" s="14">
         <v>46321</v>
       </c>
-      <c r="G16" s="13">
+      <c r="G16" s="15">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="H16" s="14">
+      <c r="H16" s="16">
         <f>IF(F16="","",F16-D16)</f>
         <v>-1</v>
       </c>
-      <c r="I16" s="15">
+      <c r="I16" s="17">
         <v>1</v>
       </c>
-      <c r="J16" s="16">
+      <c r="J16" s="18">
         <v>4</v>
       </c>
-      <c r="K16" s="10" t="str">
+      <c r="K16" s="13" t="str">
         <f>IF(I16&gt;=1,"Hoàn thành",IF(I16&gt;0,"Đang làm",IF(D16&lt;$B$2,"Trễ hạn","Chưa bắt đầu")))</f>
         <v>Hoàn thành</v>
       </c>
       <c r="L16" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="M16" s="10" t="s">
-        <v>25</v>
+        <v>51</v>
+      </c>
+      <c r="M16" s="13" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A17" s="10" t="s">
-        <v>50</v>
+      <c r="A17" s="13" t="s">
+        <v>52</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="C17" s="12">
+        <v>53</v>
+      </c>
+      <c r="C17" s="14">
         <v>46322</v>
       </c>
-      <c r="D17" s="12">
+      <c r="D17" s="14">
         <v>46322</v>
       </c>
-      <c r="E17" s="12">
+      <c r="E17" s="14">
         <v>46321</v>
       </c>
-      <c r="F17" s="12">
+      <c r="F17" s="14">
         <v>46321</v>
       </c>
-      <c r="G17" s="13">
+      <c r="G17" s="15">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="H17" s="14">
+      <c r="H17" s="16">
         <f>IF(F17="","",F17-D17)</f>
         <v>-1</v>
       </c>
-      <c r="I17" s="15">
+      <c r="I17" s="17">
         <v>1</v>
       </c>
-      <c r="J17" s="16">
+      <c r="J17" s="18">
         <v>4</v>
       </c>
-      <c r="K17" s="10" t="str">
+      <c r="K17" s="13" t="str">
         <f>IF(I17&gt;=1,"Hoàn thành",IF(I17&gt;0,"Đang làm",IF(D17&lt;$B$2,"Trễ hạn","Chưa bắt đầu")))</f>
         <v>Hoàn thành</v>
       </c>
       <c r="L17" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="M17" s="10" t="s">
-        <v>25</v>
+        <v>54</v>
+      </c>
+      <c r="M17" s="13" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A18" s="10" t="s">
-        <v>53</v>
+      <c r="A18" s="13" t="s">
+        <v>55</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="C18" s="12">
+        <v>56</v>
+      </c>
+      <c r="C18" s="14">
         <v>46323</v>
       </c>
-      <c r="D18" s="12">
+      <c r="D18" s="14">
         <v>46323</v>
       </c>
-      <c r="E18" s="12">
+      <c r="E18" s="14">
         <v>46321</v>
       </c>
-      <c r="F18" s="12">
+      <c r="F18" s="14">
         <v>46321</v>
       </c>
-      <c r="G18" s="13">
+      <c r="G18" s="15">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="H18" s="14">
+      <c r="H18" s="16">
         <f>IF(F18="","",F18-D18)</f>
         <v>-2</v>
       </c>
-      <c r="I18" s="15">
+      <c r="I18" s="17">
         <v>1</v>
       </c>
-      <c r="J18" s="16">
+      <c r="J18" s="18">
         <v>8</v>
       </c>
-      <c r="K18" s="10" t="str">
+      <c r="K18" s="13" t="str">
         <f>IF(I18&gt;=1,"Hoàn thành",IF(I18&gt;0,"Đang làm",IF(D18&lt;$B$2,"Trễ hạn","Chưa bắt đầu")))</f>
         <v>Hoàn thành</v>
       </c>
       <c r="L18" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="M18" s="10" t="s">
-        <v>25</v>
+        <v>57</v>
+      </c>
+      <c r="M18" s="13" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A19" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="C19" s="7">
+      <c r="A19" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C19" s="8">
         <f>MIN(C20:C28)</f>
         <v>46317</v>
       </c>
-      <c r="D19" s="7">
+      <c r="D19" s="8">
         <f>MAX(D20:D28)</f>
         <v>46328</v>
       </c>
-      <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
-      <c r="G19" s="8">
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="9">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="H19" s="6"/>
-      <c r="I19" s="9">
+      <c r="H19" s="7"/>
+      <c r="I19" s="10">
         <f>IFERROR(SUMPRODUCT(I20:I28,J20:J28)/SUM(J20:J28),0)</f>
         <v>0.9538461538461539</v>
       </c>
-      <c r="J19" s="8">
+      <c r="J19" s="9">
         <f>SUM(J20:J28)</f>
         <v>52</v>
       </c>
-      <c r="K19" s="6"/>
-      <c r="L19" s="6"/>
-      <c r="M19" s="6"/>
+      <c r="K19" s="7"/>
+      <c r="L19" s="7"/>
+      <c r="M19" s="7"/>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A20" s="10" t="s">
-        <v>58</v>
+      <c r="A20" s="13" t="s">
+        <v>60</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="C20" s="12">
+        <v>61</v>
+      </c>
+      <c r="C20" s="14">
         <v>46317</v>
       </c>
-      <c r="D20" s="12">
+      <c r="D20" s="14">
         <v>46317</v>
       </c>
-      <c r="E20" s="12">
+      <c r="E20" s="14">
         <v>46321</v>
       </c>
-      <c r="F20" s="12">
+      <c r="F20" s="14">
         <v>46321</v>
       </c>
-      <c r="G20" s="13">
+      <c r="G20" s="15">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="H20" s="14">
+      <c r="H20" s="16">
         <f t="shared" ref="H20:H28" si="1">IF(F20="","",F20-D20)</f>
         <v>4</v>
       </c>
-      <c r="I20" s="15">
+      <c r="I20" s="17">
         <v>1</v>
       </c>
-      <c r="J20" s="16">
+      <c r="J20" s="18">
         <v>2</v>
       </c>
-      <c r="K20" s="10" t="str">
+      <c r="K20" s="13" t="str">
         <f t="shared" ref="K20:K28" si="2">IF(I20&gt;=1,"Hoàn thành",IF(I20&gt;0,"Đang làm",IF(D20&lt;$B$2,"Trễ hạn","Chưa bắt đầu")))</f>
         <v>Hoàn thành</v>
       </c>
       <c r="L20" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="M20" s="10" t="s">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="M20" s="13" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A21" s="10" t="s">
-        <v>62</v>
+      <c r="A21" s="13" t="s">
+        <v>64</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="C21" s="12">
+        <v>65</v>
+      </c>
+      <c r="C21" s="14">
         <v>46319</v>
       </c>
-      <c r="D21" s="12">
+      <c r="D21" s="14">
         <v>46319</v>
       </c>
-      <c r="E21" s="12">
+      <c r="E21" s="14">
         <v>46321</v>
       </c>
-      <c r="F21" s="12">
+      <c r="F21" s="14">
         <v>46321</v>
       </c>
-      <c r="G21" s="13">
+      <c r="G21" s="15">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="H21" s="14">
+      <c r="H21" s="16">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="I21" s="15">
+      <c r="I21" s="17">
         <v>1</v>
       </c>
-      <c r="J21" s="16">
+      <c r="J21" s="18">
         <v>5</v>
       </c>
-      <c r="K21" s="10" t="str">
+      <c r="K21" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Hoàn thành</v>
       </c>
       <c r="L21" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="M21" s="10" t="s">
-        <v>31</v>
+        <v>66</v>
+      </c>
+      <c r="M21" s="13" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A22" s="10" t="s">
-        <v>65</v>
+      <c r="A22" s="13" t="s">
+        <v>67</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="C22" s="12">
+        <v>68</v>
+      </c>
+      <c r="C22" s="14">
         <v>46320</v>
       </c>
-      <c r="D22" s="12">
+      <c r="D22" s="14">
         <v>46320</v>
       </c>
-      <c r="E22" s="12">
+      <c r="E22" s="14">
         <v>46321</v>
       </c>
-      <c r="F22" s="12">
+      <c r="F22" s="14">
         <v>46321</v>
       </c>
-      <c r="G22" s="13">
+      <c r="G22" s="15">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="H22" s="14">
+      <c r="H22" s="16">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="I22" s="15">
+      <c r="I22" s="17">
         <v>1</v>
       </c>
-      <c r="J22" s="16">
+      <c r="J22" s="18">
         <v>3</v>
       </c>
-      <c r="K22" s="10" t="str">
+      <c r="K22" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Hoàn thành</v>
       </c>
       <c r="L22" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="M22" s="10" t="s">
-        <v>31</v>
+        <v>69</v>
+      </c>
+      <c r="M22" s="13" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A23" s="10" t="s">
-        <v>68</v>
+      <c r="A23" s="13" t="s">
+        <v>70</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="C23" s="12">
+        <v>71</v>
+      </c>
+      <c r="C23" s="14">
         <v>46320</v>
       </c>
-      <c r="D23" s="12">
+      <c r="D23" s="14">
         <v>46321</v>
       </c>
-      <c r="E23" s="12">
+      <c r="E23" s="14">
         <v>46321</v>
       </c>
-      <c r="F23" s="12">
+      <c r="F23" s="14">
         <v>46321</v>
       </c>
-      <c r="G23" s="13">
+      <c r="G23" s="15">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="H23" s="14">
+      <c r="H23" s="16">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="I23" s="15">
+      <c r="I23" s="17">
         <v>1</v>
       </c>
-      <c r="J23" s="16">
+      <c r="J23" s="18">
         <v>8</v>
       </c>
-      <c r="K23" s="10" t="str">
+      <c r="K23" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Hoàn thành</v>
       </c>
       <c r="L23" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="M23" s="10" t="s">
-        <v>31</v>
+        <v>72</v>
+      </c>
+      <c r="M23" s="13" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A24" s="10" t="s">
-        <v>71</v>
+      <c r="A24" s="13" t="s">
+        <v>73</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="C24" s="12">
+        <v>74</v>
+      </c>
+      <c r="C24" s="14">
         <v>46324</v>
       </c>
-      <c r="D24" s="12">
+      <c r="D24" s="14">
         <v>46324</v>
       </c>
-      <c r="E24" s="12">
+      <c r="E24" s="14">
         <v>46321</v>
       </c>
-      <c r="F24" s="12">
+      <c r="F24" s="14">
         <v>46321</v>
       </c>
-      <c r="G24" s="13">
+      <c r="G24" s="15">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="H24" s="14">
+      <c r="H24" s="16">
         <f t="shared" si="1"/>
         <v>-3</v>
       </c>
-      <c r="I24" s="15">
+      <c r="I24" s="17">
         <v>1</v>
       </c>
-      <c r="J24" s="16">
+      <c r="J24" s="18">
         <v>8</v>
       </c>
-      <c r="K24" s="10" t="str">
+      <c r="K24" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Hoàn thành</v>
       </c>
       <c r="L24" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="M24" s="10" t="s">
-        <v>25</v>
+        <v>75</v>
+      </c>
+      <c r="M24" s="13" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A25" s="10" t="s">
-        <v>74</v>
+      <c r="A25" s="13" t="s">
+        <v>76</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="C25" s="12">
+        <v>77</v>
+      </c>
+      <c r="C25" s="14">
         <v>46325</v>
       </c>
-      <c r="D25" s="12">
+      <c r="D25" s="14">
         <v>46325</v>
       </c>
-      <c r="E25" s="12">
+      <c r="E25" s="14">
         <v>46321</v>
       </c>
-      <c r="F25" s="12">
+      <c r="F25" s="14">
         <v>46321</v>
       </c>
-      <c r="G25" s="13">
+      <c r="G25" s="15">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="H25" s="14">
+      <c r="H25" s="16">
         <f t="shared" si="1"/>
         <v>-4</v>
       </c>
-      <c r="I25" s="15">
+      <c r="I25" s="17">
         <v>1</v>
       </c>
-      <c r="J25" s="16">
+      <c r="J25" s="18">
         <v>6</v>
       </c>
-      <c r="K25" s="10" t="str">
+      <c r="K25" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Hoàn thành</v>
       </c>
       <c r="L25" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="M25" s="10" t="s">
-        <v>35</v>
+        <v>78</v>
+      </c>
+      <c r="M25" s="13" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A26" s="10" t="s">
-        <v>77</v>
+      <c r="A26" s="13" t="s">
+        <v>79</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="C26" s="12">
+        <v>80</v>
+      </c>
+      <c r="C26" s="14">
         <v>46326</v>
       </c>
-      <c r="D26" s="12">
+      <c r="D26" s="14">
         <v>46326</v>
       </c>
-      <c r="E26" s="12">
+      <c r="E26" s="14">
         <v>46321</v>
       </c>
-      <c r="F26" s="12">
+      <c r="F26" s="14">
         <v>46321</v>
       </c>
-      <c r="G26" s="13">
+      <c r="G26" s="15">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="H26" s="14">
+      <c r="H26" s="16">
         <f t="shared" si="1"/>
         <v>-5</v>
       </c>
-      <c r="I26" s="15">
+      <c r="I26" s="17">
         <v>1</v>
       </c>
-      <c r="J26" s="16">
+      <c r="J26" s="18">
         <v>8</v>
       </c>
-      <c r="K26" s="10" t="str">
+      <c r="K26" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Hoàn thành</v>
       </c>
       <c r="L26" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="M26" s="10" t="s">
-        <v>35</v>
+        <v>78</v>
+      </c>
+      <c r="M26" s="13" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A27" s="10" t="s">
-        <v>79</v>
+      <c r="A27" s="13" t="s">
+        <v>81</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="C27" s="12">
+        <v>82</v>
+      </c>
+      <c r="C27" s="14">
         <v>46327</v>
       </c>
-      <c r="D27" s="12">
+      <c r="D27" s="14">
         <v>46327</v>
       </c>
-      <c r="E27" s="12">
+      <c r="E27" s="14">
         <v>46321</v>
       </c>
-      <c r="F27" s="12">
+      <c r="F27" s="14">
         <v>46321</v>
       </c>
-      <c r="G27" s="13">
+      <c r="G27" s="15">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="H27" s="14">
+      <c r="H27" s="16">
         <f t="shared" si="1"/>
         <v>-6</v>
       </c>
-      <c r="I27" s="15">
+      <c r="I27" s="17">
         <v>1</v>
       </c>
-      <c r="J27" s="16">
+      <c r="J27" s="18">
         <v>6</v>
       </c>
-      <c r="K27" s="10" t="str">
+      <c r="K27" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Hoàn thành</v>
       </c>
       <c r="L27" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="M27" s="10" t="s">
-        <v>35</v>
+        <v>78</v>
+      </c>
+      <c r="M27" s="13" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A28" s="10" t="s">
-        <v>81</v>
+      <c r="A28" s="13" t="s">
+        <v>83</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="C28" s="12">
+        <v>84</v>
+      </c>
+      <c r="C28" s="14">
         <v>46328</v>
       </c>
-      <c r="D28" s="12">
+      <c r="D28" s="14">
         <v>46328</v>
       </c>
-      <c r="E28" s="12">
+      <c r="E28" s="14">
         <v>46321</v>
       </c>
-      <c r="F28" s="12"/>
-      <c r="G28" s="13">
+      <c r="F28" s="14"/>
+      <c r="G28" s="15">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="H28" s="14" t="str">
+      <c r="H28" s="16" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="I28" s="15">
+      <c r="I28" s="17">
         <v>0.6</v>
       </c>
-      <c r="J28" s="16">
+      <c r="J28" s="18">
         <v>6</v>
       </c>
-      <c r="K28" s="10" t="str">
+      <c r="K28" s="13" t="str">
         <f t="shared" si="2"/>
         <v>Đang làm</v>
       </c>
       <c r="L28" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="M28" s="10" t="s">
-        <v>61</v>
+        <v>85</v>
+      </c>
+      <c r="M28" s="13" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A29" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="C29" s="7">
+      <c r="A29" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="C29" s="8">
         <f>MIN(C30:C32)</f>
         <v>46329</v>
       </c>
-      <c r="D29" s="7">
+      <c r="D29" s="8">
         <f>MAX(D30:D32)</f>
         <v>46330</v>
       </c>
-      <c r="E29" s="6"/>
-      <c r="F29" s="6"/>
-      <c r="G29" s="8">
+      <c r="E29" s="7"/>
+      <c r="F29" s="7"/>
+      <c r="G29" s="9">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="H29" s="6"/>
-      <c r="I29" s="9">
+      <c r="H29" s="7"/>
+      <c r="I29" s="10">
         <f>IFERROR(SUMPRODUCT(I30:I32,J30:J32)/SUM(J30:J32),0)</f>
         <v>0</v>
       </c>
-      <c r="J29" s="8">
+      <c r="J29" s="9">
         <f>SUM(J30:J32)</f>
         <v>7</v>
       </c>
-      <c r="K29" s="6"/>
-      <c r="L29" s="6"/>
-      <c r="M29" s="6"/>
+      <c r="K29" s="7"/>
+      <c r="L29" s="7"/>
+      <c r="M29" s="7"/>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A30" s="10" t="s">
-        <v>86</v>
+      <c r="A30" s="13" t="s">
+        <v>88</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="C30" s="12">
+        <v>89</v>
+      </c>
+      <c r="C30" s="14">
         <v>46329</v>
       </c>
-      <c r="D30" s="12">
+      <c r="D30" s="14">
         <v>46329</v>
       </c>
-      <c r="E30" s="12"/>
-      <c r="F30" s="12"/>
-      <c r="G30" s="13">
+      <c r="E30" s="14"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="15">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="H30" s="14" t="str">
+      <c r="H30" s="16" t="str">
         <f>IF(F30="","",F30-D30)</f>
         <v/>
       </c>
-      <c r="I30" s="15">
+      <c r="I30" s="17">
         <v>0</v>
       </c>
-      <c r="J30" s="16">
+      <c r="J30" s="18">
         <v>4</v>
       </c>
-      <c r="K30" s="10" t="str">
+      <c r="K30" s="13" t="str">
         <f>IF(I30&gt;=1,"Hoàn thành",IF(I30&gt;0,"Đang làm",IF(D30&lt;$B$2,"Trễ hạn","Chưa bắt đầu")))</f>
         <v>Chưa bắt đầu</v>
       </c>
       <c r="L30" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="M30" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
+      </c>
+      <c r="M30" s="13" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A31" s="10" t="s">
-        <v>90</v>
+      <c r="A31" s="13" t="s">
+        <v>92</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="C31" s="12">
+        <v>93</v>
+      </c>
+      <c r="C31" s="14">
         <v>46329</v>
       </c>
-      <c r="D31" s="12">
+      <c r="D31" s="14">
         <v>46329</v>
       </c>
-      <c r="E31" s="12"/>
-      <c r="F31" s="12"/>
-      <c r="G31" s="13">
+      <c r="E31" s="14"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="15">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="H31" s="14" t="str">
+      <c r="H31" s="16" t="str">
         <f>IF(F31="","",F31-D31)</f>
         <v/>
       </c>
-      <c r="I31" s="15">
+      <c r="I31" s="17">
         <v>0</v>
       </c>
-      <c r="J31" s="16">
+      <c r="J31" s="18">
         <v>3</v>
       </c>
-      <c r="K31" s="10" t="str">
+      <c r="K31" s="13" t="str">
         <f>IF(I31&gt;=1,"Hoàn thành",IF(I31&gt;0,"Đang làm",IF(D31&lt;$B$2,"Trễ hạn","Chưa bắt đầu")))</f>
         <v>Chưa bắt đầu</v>
       </c>
       <c r="L31" s="11"/>
-      <c r="M31" s="10" t="s">
-        <v>89</v>
+      <c r="M31" s="13" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A32" s="10" t="s">
-        <v>92</v>
+      <c r="A32" s="13" t="s">
+        <v>94</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="C32" s="12">
+        <v>95</v>
+      </c>
+      <c r="C32" s="14">
         <v>46330</v>
       </c>
-      <c r="D32" s="12">
+      <c r="D32" s="14">
         <v>46330</v>
       </c>
-      <c r="E32" s="12"/>
-      <c r="F32" s="12"/>
-      <c r="G32" s="13">
+      <c r="E32" s="14"/>
+      <c r="F32" s="14"/>
+      <c r="G32" s="15">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="H32" s="14" t="str">
+      <c r="H32" s="16" t="str">
         <f>IF(F32="","",F32-D32)</f>
         <v/>
       </c>
-      <c r="I32" s="15">
+      <c r="I32" s="17">
         <v>0</v>
       </c>
-      <c r="J32" s="16">
+      <c r="J32" s="18">
         <v>0</v>
       </c>
-      <c r="K32" s="10" t="str">
+      <c r="K32" s="13" t="str">
         <f>IF(I32&gt;=1,"Hoàn thành",IF(I32&gt;0,"Đang làm",IF(D32&lt;$B$2,"Trễ hạn","Chưa bắt đầu")))</f>
         <v>Chưa bắt đầu</v>
       </c>
       <c r="L32" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="M32" s="10" t="s">
-        <v>61</v>
+        <v>96</v>
+      </c>
+      <c r="M32" s="13" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A33" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="C33" s="7">
+      <c r="A33" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="C33" s="8">
         <f>MIN(C34:C34)</f>
         <v>46321</v>
       </c>
-      <c r="D33" s="7">
+      <c r="D33" s="8">
         <f>MAX(D34:D34)</f>
         <v>46321</v>
       </c>
-      <c r="E33" s="6"/>
-      <c r="F33" s="6"/>
-      <c r="G33" s="8">
+      <c r="E33" s="7"/>
+      <c r="F33" s="7"/>
+      <c r="G33" s="9">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="H33" s="6"/>
-      <c r="I33" s="9">
+      <c r="H33" s="7"/>
+      <c r="I33" s="10">
         <f>IFERROR(SUMPRODUCT(I34:I34,J34:J34)/SUM(J34:J34),0)</f>
         <v>1</v>
       </c>
-      <c r="J33" s="8">
+      <c r="J33" s="9">
         <f>SUM(J34:J34)</f>
         <v>2</v>
       </c>
-      <c r="K33" s="6"/>
-      <c r="L33" s="6"/>
-      <c r="M33" s="6"/>
+      <c r="K33" s="7"/>
+      <c r="L33" s="7"/>
+      <c r="M33" s="7"/>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A34" s="10" t="s">
-        <v>97</v>
+      <c r="A34" s="13" t="s">
+        <v>99</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="C34" s="12">
+        <v>100</v>
+      </c>
+      <c r="C34" s="14">
         <v>46321</v>
       </c>
-      <c r="D34" s="12">
+      <c r="D34" s="14">
         <v>46321</v>
       </c>
-      <c r="E34" s="12">
+      <c r="E34" s="14">
         <v>46321</v>
       </c>
-      <c r="F34" s="12">
+      <c r="F34" s="14">
         <v>46321</v>
       </c>
-      <c r="G34" s="13">
+      <c r="G34" s="15">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="H34" s="14">
+      <c r="H34" s="16">
         <f>IF(F34="","",F34-D34)</f>
         <v>0</v>
       </c>
-      <c r="I34" s="15">
+      <c r="I34" s="17">
         <v>1</v>
       </c>
-      <c r="J34" s="16">
+      <c r="J34" s="18">
         <v>2</v>
       </c>
-      <c r="K34" s="10" t="str">
+      <c r="K34" s="13" t="str">
         <f>IF(I34&gt;=1,"Hoàn thành",IF(I34&gt;0,"Đang làm",IF(D34&lt;$B$2,"Trễ hạn","Chưa bắt đầu")))</f>
         <v>Hoàn thành</v>
       </c>
       <c r="L34" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="M34" s="10" t="s">
-        <v>35</v>
+        <v>101</v>
+      </c>
+      <c r="M34" s="13" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B36" s="17" t="s">
-        <v>100</v>
-      </c>
-      <c r="I36" s="18">
+      <c r="B36" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="I36" s="20">
         <f>(I6*J6+I9*J9+I13*J13+I19*J19+I29*J29+I33*J33)/(J6+J9+J13+J19+J29+J33)</f>
         <v>0.89702970297029694</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B37" s="17" t="s">
-        <v>101</v>
-      </c>
-      <c r="I37" s="19">
+      <c r="B37" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="I37" s="21">
         <f>COUNTIF(K6:K34,"Trễ hạn")</f>
         <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B38" s="17" t="s">
-        <v>102</v>
-      </c>
-      <c r="I38" s="19">
+      <c r="B38" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="I38" s="21">
         <f>J6+J9+J13+J19+J29+J33</f>
         <v>101</v>
       </c>
@@ -2588,7 +3159,8 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing r:id="rId1"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -2604,20 +3176,20 @@
   <sheetData>
     <row r="1" spans="1:20" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="C3" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" spans="1:20" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2627,2435 +3199,2435 @@
       <c r="B4" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="20">
+      <c r="C4" s="22">
         <v>46313</v>
       </c>
-      <c r="D4" s="20">
+      <c r="D4" s="22">
         <v>46314</v>
       </c>
-      <c r="E4" s="20">
+      <c r="E4" s="22">
         <v>46315</v>
       </c>
-      <c r="F4" s="20">
+      <c r="F4" s="22">
         <v>46316</v>
       </c>
-      <c r="G4" s="20">
+      <c r="G4" s="22">
         <v>46317</v>
       </c>
-      <c r="H4" s="20">
+      <c r="H4" s="22">
         <v>46318</v>
       </c>
-      <c r="I4" s="20">
+      <c r="I4" s="22">
         <v>46319</v>
       </c>
-      <c r="J4" s="20">
+      <c r="J4" s="22">
         <v>46320</v>
       </c>
-      <c r="K4" s="20">
+      <c r="K4" s="22">
         <v>46321</v>
       </c>
-      <c r="L4" s="20">
+      <c r="L4" s="22">
         <v>46322</v>
       </c>
-      <c r="M4" s="20">
+      <c r="M4" s="22">
         <v>46323</v>
       </c>
-      <c r="N4" s="20">
+      <c r="N4" s="22">
         <v>46324</v>
       </c>
-      <c r="O4" s="20">
+      <c r="O4" s="22">
         <v>46325</v>
       </c>
-      <c r="P4" s="20">
+      <c r="P4" s="22">
         <v>46326</v>
       </c>
-      <c r="Q4" s="20">
+      <c r="Q4" s="22">
         <v>46327</v>
       </c>
-      <c r="R4" s="20">
+      <c r="R4" s="22">
         <v>46328</v>
       </c>
-      <c r="S4" s="20">
+      <c r="S4" s="22">
         <v>46329</v>
       </c>
-      <c r="T4" s="20">
+      <c r="T4" s="22">
         <v>46330</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A5" s="21" t="str">
+      <c r="A5" s="23" t="str">
         <f>WBS!A6</f>
         <v>1</v>
       </c>
-      <c r="B5" s="21" t="str">
+      <c r="B5" s="23" t="str">
         <f>WBS!B6</f>
         <v>Khởi động dự án</v>
       </c>
-      <c r="C5" s="22" t="str">
+      <c r="C5" s="24" t="str">
         <f>IF(WBS!$C6="","",IF(AND(WBS!$E6&lt;&gt;"",C$4&gt;=WBS!$E6,C$4&lt;=WBS!$F6),"■",IF(AND(C$4&gt;=WBS!$C6,C$4&lt;=WBS!$D6),"□","")))</f>
         <v>□</v>
       </c>
-      <c r="D5" s="22" t="str">
+      <c r="D5" s="24" t="str">
         <f>IF(WBS!$C6="","",IF(AND(WBS!$E6&lt;&gt;"",D$4&gt;=WBS!$E6,D$4&lt;=WBS!$F6),"■",IF(AND(D$4&gt;=WBS!$C6,D$4&lt;=WBS!$D6),"□","")))</f>
         <v/>
       </c>
-      <c r="E5" s="22" t="str">
+      <c r="E5" s="24" t="str">
         <f>IF(WBS!$C6="","",IF(AND(WBS!$E6&lt;&gt;"",E$4&gt;=WBS!$E6,E$4&lt;=WBS!$F6),"■",IF(AND(E$4&gt;=WBS!$C6,E$4&lt;=WBS!$D6),"□","")))</f>
         <v/>
       </c>
-      <c r="F5" s="22" t="str">
+      <c r="F5" s="24" t="str">
         <f>IF(WBS!$C6="","",IF(AND(WBS!$E6&lt;&gt;"",F$4&gt;=WBS!$E6,F$4&lt;=WBS!$F6),"■",IF(AND(F$4&gt;=WBS!$C6,F$4&lt;=WBS!$D6),"□","")))</f>
         <v/>
       </c>
-      <c r="G5" s="22" t="str">
+      <c r="G5" s="24" t="str">
         <f>IF(WBS!$C6="","",IF(AND(WBS!$E6&lt;&gt;"",G$4&gt;=WBS!$E6,G$4&lt;=WBS!$F6),"■",IF(AND(G$4&gt;=WBS!$C6,G$4&lt;=WBS!$D6),"□","")))</f>
         <v/>
       </c>
-      <c r="H5" s="22" t="str">
+      <c r="H5" s="24" t="str">
         <f>IF(WBS!$C6="","",IF(AND(WBS!$E6&lt;&gt;"",H$4&gt;=WBS!$E6,H$4&lt;=WBS!$F6),"■",IF(AND(H$4&gt;=WBS!$C6,H$4&lt;=WBS!$D6),"□","")))</f>
         <v/>
       </c>
-      <c r="I5" s="22" t="str">
+      <c r="I5" s="24" t="str">
         <f>IF(WBS!$C6="","",IF(AND(WBS!$E6&lt;&gt;"",I$4&gt;=WBS!$E6,I$4&lt;=WBS!$F6),"■",IF(AND(I$4&gt;=WBS!$C6,I$4&lt;=WBS!$D6),"□","")))</f>
         <v/>
       </c>
-      <c r="J5" s="22" t="str">
+      <c r="J5" s="24" t="str">
         <f>IF(WBS!$C6="","",IF(AND(WBS!$E6&lt;&gt;"",J$4&gt;=WBS!$E6,J$4&lt;=WBS!$F6),"■",IF(AND(J$4&gt;=WBS!$C6,J$4&lt;=WBS!$D6),"□","")))</f>
         <v/>
       </c>
-      <c r="K5" s="22" t="str">
+      <c r="K5" s="24" t="str">
         <f>IF(WBS!$C6="","",IF(AND(WBS!$E6&lt;&gt;"",K$4&gt;=WBS!$E6,K$4&lt;=WBS!$F6),"■",IF(AND(K$4&gt;=WBS!$C6,K$4&lt;=WBS!$D6),"□","")))</f>
         <v/>
       </c>
-      <c r="L5" s="22" t="str">
+      <c r="L5" s="24" t="str">
         <f>IF(WBS!$C6="","",IF(AND(WBS!$E6&lt;&gt;"",L$4&gt;=WBS!$E6,L$4&lt;=WBS!$F6),"■",IF(AND(L$4&gt;=WBS!$C6,L$4&lt;=WBS!$D6),"□","")))</f>
         <v/>
       </c>
-      <c r="M5" s="22" t="str">
+      <c r="M5" s="24" t="str">
         <f>IF(WBS!$C6="","",IF(AND(WBS!$E6&lt;&gt;"",M$4&gt;=WBS!$E6,M$4&lt;=WBS!$F6),"■",IF(AND(M$4&gt;=WBS!$C6,M$4&lt;=WBS!$D6),"□","")))</f>
         <v/>
       </c>
-      <c r="N5" s="22" t="str">
+      <c r="N5" s="24" t="str">
         <f>IF(WBS!$C6="","",IF(AND(WBS!$E6&lt;&gt;"",N$4&gt;=WBS!$E6,N$4&lt;=WBS!$F6),"■",IF(AND(N$4&gt;=WBS!$C6,N$4&lt;=WBS!$D6),"□","")))</f>
         <v/>
       </c>
-      <c r="O5" s="22" t="str">
+      <c r="O5" s="24" t="str">
         <f>IF(WBS!$C6="","",IF(AND(WBS!$E6&lt;&gt;"",O$4&gt;=WBS!$E6,O$4&lt;=WBS!$F6),"■",IF(AND(O$4&gt;=WBS!$C6,O$4&lt;=WBS!$D6),"□","")))</f>
         <v/>
       </c>
-      <c r="P5" s="22" t="str">
+      <c r="P5" s="24" t="str">
         <f>IF(WBS!$C6="","",IF(AND(WBS!$E6&lt;&gt;"",P$4&gt;=WBS!$E6,P$4&lt;=WBS!$F6),"■",IF(AND(P$4&gt;=WBS!$C6,P$4&lt;=WBS!$D6),"□","")))</f>
         <v/>
       </c>
-      <c r="Q5" s="22" t="str">
+      <c r="Q5" s="24" t="str">
         <f>IF(WBS!$C6="","",IF(AND(WBS!$E6&lt;&gt;"",Q$4&gt;=WBS!$E6,Q$4&lt;=WBS!$F6),"■",IF(AND(Q$4&gt;=WBS!$C6,Q$4&lt;=WBS!$D6),"□","")))</f>
         <v/>
       </c>
-      <c r="R5" s="22" t="str">
+      <c r="R5" s="24" t="str">
         <f>IF(WBS!$C6="","",IF(AND(WBS!$E6&lt;&gt;"",R$4&gt;=WBS!$E6,R$4&lt;=WBS!$F6),"■",IF(AND(R$4&gt;=WBS!$C6,R$4&lt;=WBS!$D6),"□","")))</f>
         <v/>
       </c>
-      <c r="S5" s="22" t="str">
+      <c r="S5" s="24" t="str">
         <f>IF(WBS!$C6="","",IF(AND(WBS!$E6&lt;&gt;"",S$4&gt;=WBS!$E6,S$4&lt;=WBS!$F6),"■",IF(AND(S$4&gt;=WBS!$C6,S$4&lt;=WBS!$D6),"□","")))</f>
         <v/>
       </c>
-      <c r="T5" s="22" t="str">
+      <c r="T5" s="24" t="str">
         <f>IF(WBS!$C6="","",IF(AND(WBS!$E6&lt;&gt;"",T$4&gt;=WBS!$E6,T$4&lt;=WBS!$F6),"■",IF(AND(T$4&gt;=WBS!$C6,T$4&lt;=WBS!$D6),"□","")))</f>
         <v/>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A6" s="21" t="str">
+      <c r="A6" s="23" t="str">
         <f>WBS!A7</f>
         <v>1.1</v>
       </c>
-      <c r="B6" s="21" t="str">
+      <c r="B6" s="23" t="str">
         <f>WBS!B7</f>
         <v>Tạo repo, kế hoạch, cấu trúc thư mục</v>
       </c>
-      <c r="C6" s="22" t="str">
+      <c r="C6" s="24" t="str">
         <f>IF(WBS!$C7="","",IF(AND(WBS!$E7&lt;&gt;"",C$4&gt;=WBS!$E7,C$4&lt;=WBS!$F7),"■",IF(AND(C$4&gt;=WBS!$C7,C$4&lt;=WBS!$D7),"□","")))</f>
         <v>□</v>
       </c>
-      <c r="D6" s="22" t="str">
+      <c r="D6" s="24" t="str">
         <f>IF(WBS!$C7="","",IF(AND(WBS!$E7&lt;&gt;"",D$4&gt;=WBS!$E7,D$4&lt;=WBS!$F7),"■",IF(AND(D$4&gt;=WBS!$C7,D$4&lt;=WBS!$D7),"□","")))</f>
         <v>■</v>
       </c>
-      <c r="E6" s="22" t="str">
+      <c r="E6" s="24" t="str">
         <f>IF(WBS!$C7="","",IF(AND(WBS!$E7&lt;&gt;"",E$4&gt;=WBS!$E7,E$4&lt;=WBS!$F7),"■",IF(AND(E$4&gt;=WBS!$C7,E$4&lt;=WBS!$D7),"□","")))</f>
         <v/>
       </c>
-      <c r="F6" s="22" t="str">
+      <c r="F6" s="24" t="str">
         <f>IF(WBS!$C7="","",IF(AND(WBS!$E7&lt;&gt;"",F$4&gt;=WBS!$E7,F$4&lt;=WBS!$F7),"■",IF(AND(F$4&gt;=WBS!$C7,F$4&lt;=WBS!$D7),"□","")))</f>
         <v/>
       </c>
-      <c r="G6" s="22" t="str">
+      <c r="G6" s="24" t="str">
         <f>IF(WBS!$C7="","",IF(AND(WBS!$E7&lt;&gt;"",G$4&gt;=WBS!$E7,G$4&lt;=WBS!$F7),"■",IF(AND(G$4&gt;=WBS!$C7,G$4&lt;=WBS!$D7),"□","")))</f>
         <v/>
       </c>
-      <c r="H6" s="22" t="str">
+      <c r="H6" s="24" t="str">
         <f>IF(WBS!$C7="","",IF(AND(WBS!$E7&lt;&gt;"",H$4&gt;=WBS!$E7,H$4&lt;=WBS!$F7),"■",IF(AND(H$4&gt;=WBS!$C7,H$4&lt;=WBS!$D7),"□","")))</f>
         <v/>
       </c>
-      <c r="I6" s="22" t="str">
+      <c r="I6" s="24" t="str">
         <f>IF(WBS!$C7="","",IF(AND(WBS!$E7&lt;&gt;"",I$4&gt;=WBS!$E7,I$4&lt;=WBS!$F7),"■",IF(AND(I$4&gt;=WBS!$C7,I$4&lt;=WBS!$D7),"□","")))</f>
         <v/>
       </c>
-      <c r="J6" s="22" t="str">
+      <c r="J6" s="24" t="str">
         <f>IF(WBS!$C7="","",IF(AND(WBS!$E7&lt;&gt;"",J$4&gt;=WBS!$E7,J$4&lt;=WBS!$F7),"■",IF(AND(J$4&gt;=WBS!$C7,J$4&lt;=WBS!$D7),"□","")))</f>
         <v/>
       </c>
-      <c r="K6" s="22" t="str">
+      <c r="K6" s="24" t="str">
         <f>IF(WBS!$C7="","",IF(AND(WBS!$E7&lt;&gt;"",K$4&gt;=WBS!$E7,K$4&lt;=WBS!$F7),"■",IF(AND(K$4&gt;=WBS!$C7,K$4&lt;=WBS!$D7),"□","")))</f>
         <v/>
       </c>
-      <c r="L6" s="22" t="str">
+      <c r="L6" s="24" t="str">
         <f>IF(WBS!$C7="","",IF(AND(WBS!$E7&lt;&gt;"",L$4&gt;=WBS!$E7,L$4&lt;=WBS!$F7),"■",IF(AND(L$4&gt;=WBS!$C7,L$4&lt;=WBS!$D7),"□","")))</f>
         <v/>
       </c>
-      <c r="M6" s="22" t="str">
+      <c r="M6" s="24" t="str">
         <f>IF(WBS!$C7="","",IF(AND(WBS!$E7&lt;&gt;"",M$4&gt;=WBS!$E7,M$4&lt;=WBS!$F7),"■",IF(AND(M$4&gt;=WBS!$C7,M$4&lt;=WBS!$D7),"□","")))</f>
         <v/>
       </c>
-      <c r="N6" s="22" t="str">
+      <c r="N6" s="24" t="str">
         <f>IF(WBS!$C7="","",IF(AND(WBS!$E7&lt;&gt;"",N$4&gt;=WBS!$E7,N$4&lt;=WBS!$F7),"■",IF(AND(N$4&gt;=WBS!$C7,N$4&lt;=WBS!$D7),"□","")))</f>
         <v/>
       </c>
-      <c r="O6" s="22" t="str">
+      <c r="O6" s="24" t="str">
         <f>IF(WBS!$C7="","",IF(AND(WBS!$E7&lt;&gt;"",O$4&gt;=WBS!$E7,O$4&lt;=WBS!$F7),"■",IF(AND(O$4&gt;=WBS!$C7,O$4&lt;=WBS!$D7),"□","")))</f>
         <v/>
       </c>
-      <c r="P6" s="22" t="str">
+      <c r="P6" s="24" t="str">
         <f>IF(WBS!$C7="","",IF(AND(WBS!$E7&lt;&gt;"",P$4&gt;=WBS!$E7,P$4&lt;=WBS!$F7),"■",IF(AND(P$4&gt;=WBS!$C7,P$4&lt;=WBS!$D7),"□","")))</f>
         <v/>
       </c>
-      <c r="Q6" s="22" t="str">
+      <c r="Q6" s="24" t="str">
         <f>IF(WBS!$C7="","",IF(AND(WBS!$E7&lt;&gt;"",Q$4&gt;=WBS!$E7,Q$4&lt;=WBS!$F7),"■",IF(AND(Q$4&gt;=WBS!$C7,Q$4&lt;=WBS!$D7),"□","")))</f>
         <v/>
       </c>
-      <c r="R6" s="22" t="str">
+      <c r="R6" s="24" t="str">
         <f>IF(WBS!$C7="","",IF(AND(WBS!$E7&lt;&gt;"",R$4&gt;=WBS!$E7,R$4&lt;=WBS!$F7),"■",IF(AND(R$4&gt;=WBS!$C7,R$4&lt;=WBS!$D7),"□","")))</f>
         <v/>
       </c>
-      <c r="S6" s="22" t="str">
+      <c r="S6" s="24" t="str">
         <f>IF(WBS!$C7="","",IF(AND(WBS!$E7&lt;&gt;"",S$4&gt;=WBS!$E7,S$4&lt;=WBS!$F7),"■",IF(AND(S$4&gt;=WBS!$C7,S$4&lt;=WBS!$D7),"□","")))</f>
         <v/>
       </c>
-      <c r="T6" s="22" t="str">
+      <c r="T6" s="24" t="str">
         <f>IF(WBS!$C7="","",IF(AND(WBS!$E7&lt;&gt;"",T$4&gt;=WBS!$E7,T$4&lt;=WBS!$F7),"■",IF(AND(T$4&gt;=WBS!$C7,T$4&lt;=WBS!$D7),"□","")))</f>
         <v/>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A7" s="21" t="str">
+      <c r="A7" s="23" t="str">
         <f>WBS!A8</f>
         <v>1.2</v>
       </c>
-      <c r="B7" s="21" t="str">
+      <c r="B7" s="23" t="str">
         <f>WBS!B8</f>
         <v>Gửi email xin dữ liệu gốc cho tác giả</v>
       </c>
-      <c r="C7" s="22" t="str">
+      <c r="C7" s="24" t="str">
         <f>IF(WBS!$C8="","",IF(AND(WBS!$E8&lt;&gt;"",C$4&gt;=WBS!$E8,C$4&lt;=WBS!$F8),"■",IF(AND(C$4&gt;=WBS!$C8,C$4&lt;=WBS!$D8),"□","")))</f>
         <v>□</v>
       </c>
-      <c r="D7" s="22" t="str">
+      <c r="D7" s="24" t="str">
         <f>IF(WBS!$C8="","",IF(AND(WBS!$E8&lt;&gt;"",D$4&gt;=WBS!$E8,D$4&lt;=WBS!$F8),"■",IF(AND(D$4&gt;=WBS!$C8,D$4&lt;=WBS!$D8),"□","")))</f>
         <v/>
       </c>
-      <c r="E7" s="22" t="str">
+      <c r="E7" s="24" t="str">
         <f>IF(WBS!$C8="","",IF(AND(WBS!$E8&lt;&gt;"",E$4&gt;=WBS!$E8,E$4&lt;=WBS!$F8),"■",IF(AND(E$4&gt;=WBS!$C8,E$4&lt;=WBS!$D8),"□","")))</f>
         <v/>
       </c>
-      <c r="F7" s="22" t="str">
+      <c r="F7" s="24" t="str">
         <f>IF(WBS!$C8="","",IF(AND(WBS!$E8&lt;&gt;"",F$4&gt;=WBS!$E8,F$4&lt;=WBS!$F8),"■",IF(AND(F$4&gt;=WBS!$C8,F$4&lt;=WBS!$D8),"□","")))</f>
         <v/>
       </c>
-      <c r="G7" s="22" t="str">
+      <c r="G7" s="24" t="str">
         <f>IF(WBS!$C8="","",IF(AND(WBS!$E8&lt;&gt;"",G$4&gt;=WBS!$E8,G$4&lt;=WBS!$F8),"■",IF(AND(G$4&gt;=WBS!$C8,G$4&lt;=WBS!$D8),"□","")))</f>
         <v/>
       </c>
-      <c r="H7" s="22" t="str">
+      <c r="H7" s="24" t="str">
         <f>IF(WBS!$C8="","",IF(AND(WBS!$E8&lt;&gt;"",H$4&gt;=WBS!$E8,H$4&lt;=WBS!$F8),"■",IF(AND(H$4&gt;=WBS!$C8,H$4&lt;=WBS!$D8),"□","")))</f>
         <v/>
       </c>
-      <c r="I7" s="22" t="str">
+      <c r="I7" s="24" t="str">
         <f>IF(WBS!$C8="","",IF(AND(WBS!$E8&lt;&gt;"",I$4&gt;=WBS!$E8,I$4&lt;=WBS!$F8),"■",IF(AND(I$4&gt;=WBS!$C8,I$4&lt;=WBS!$D8),"□","")))</f>
         <v/>
       </c>
-      <c r="J7" s="22" t="str">
+      <c r="J7" s="24" t="str">
         <f>IF(WBS!$C8="","",IF(AND(WBS!$E8&lt;&gt;"",J$4&gt;=WBS!$E8,J$4&lt;=WBS!$F8),"■",IF(AND(J$4&gt;=WBS!$C8,J$4&lt;=WBS!$D8),"□","")))</f>
         <v/>
       </c>
-      <c r="K7" s="22" t="str">
+      <c r="K7" s="24" t="str">
         <f>IF(WBS!$C8="","",IF(AND(WBS!$E8&lt;&gt;"",K$4&gt;=WBS!$E8,K$4&lt;=WBS!$F8),"■",IF(AND(K$4&gt;=WBS!$C8,K$4&lt;=WBS!$D8),"□","")))</f>
         <v/>
       </c>
-      <c r="L7" s="22" t="str">
+      <c r="L7" s="24" t="str">
         <f>IF(WBS!$C8="","",IF(AND(WBS!$E8&lt;&gt;"",L$4&gt;=WBS!$E8,L$4&lt;=WBS!$F8),"■",IF(AND(L$4&gt;=WBS!$C8,L$4&lt;=WBS!$D8),"□","")))</f>
         <v/>
       </c>
-      <c r="M7" s="22" t="str">
+      <c r="M7" s="24" t="str">
         <f>IF(WBS!$C8="","",IF(AND(WBS!$E8&lt;&gt;"",M$4&gt;=WBS!$E8,M$4&lt;=WBS!$F8),"■",IF(AND(M$4&gt;=WBS!$C8,M$4&lt;=WBS!$D8),"□","")))</f>
         <v/>
       </c>
-      <c r="N7" s="22" t="str">
+      <c r="N7" s="24" t="str">
         <f>IF(WBS!$C8="","",IF(AND(WBS!$E8&lt;&gt;"",N$4&gt;=WBS!$E8,N$4&lt;=WBS!$F8),"■",IF(AND(N$4&gt;=WBS!$C8,N$4&lt;=WBS!$D8),"□","")))</f>
         <v/>
       </c>
-      <c r="O7" s="22" t="str">
+      <c r="O7" s="24" t="str">
         <f>IF(WBS!$C8="","",IF(AND(WBS!$E8&lt;&gt;"",O$4&gt;=WBS!$E8,O$4&lt;=WBS!$F8),"■",IF(AND(O$4&gt;=WBS!$C8,O$4&lt;=WBS!$D8),"□","")))</f>
         <v/>
       </c>
-      <c r="P7" s="22" t="str">
+      <c r="P7" s="24" t="str">
         <f>IF(WBS!$C8="","",IF(AND(WBS!$E8&lt;&gt;"",P$4&gt;=WBS!$E8,P$4&lt;=WBS!$F8),"■",IF(AND(P$4&gt;=WBS!$C8,P$4&lt;=WBS!$D8),"□","")))</f>
         <v/>
       </c>
-      <c r="Q7" s="22" t="str">
+      <c r="Q7" s="24" t="str">
         <f>IF(WBS!$C8="","",IF(AND(WBS!$E8&lt;&gt;"",Q$4&gt;=WBS!$E8,Q$4&lt;=WBS!$F8),"■",IF(AND(Q$4&gt;=WBS!$C8,Q$4&lt;=WBS!$D8),"□","")))</f>
         <v/>
       </c>
-      <c r="R7" s="22" t="str">
+      <c r="R7" s="24" t="str">
         <f>IF(WBS!$C8="","",IF(AND(WBS!$E8&lt;&gt;"",R$4&gt;=WBS!$E8,R$4&lt;=WBS!$F8),"■",IF(AND(R$4&gt;=WBS!$C8,R$4&lt;=WBS!$D8),"□","")))</f>
         <v/>
       </c>
-      <c r="S7" s="22" t="str">
+      <c r="S7" s="24" t="str">
         <f>IF(WBS!$C8="","",IF(AND(WBS!$E8&lt;&gt;"",S$4&gt;=WBS!$E8,S$4&lt;=WBS!$F8),"■",IF(AND(S$4&gt;=WBS!$C8,S$4&lt;=WBS!$D8),"□","")))</f>
         <v/>
       </c>
-      <c r="T7" s="22" t="str">
+      <c r="T7" s="24" t="str">
         <f>IF(WBS!$C8="","",IF(AND(WBS!$E8&lt;&gt;"",T$4&gt;=WBS!$E8,T$4&lt;=WBS!$F8),"■",IF(AND(T$4&gt;=WBS!$C8,T$4&lt;=WBS!$D8),"□","")))</f>
         <v/>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A8" s="21" t="str">
+      <c r="A8" s="23" t="str">
         <f>WBS!A9</f>
         <v>2</v>
       </c>
-      <c r="B8" s="21" t="str">
+      <c r="B8" s="23" t="str">
         <f>WBS!B9</f>
         <v>Đọc hiểu bài báo</v>
       </c>
-      <c r="C8" s="22" t="str">
+      <c r="C8" s="24" t="str">
         <f>IF(WBS!$C9="","",IF(AND(WBS!$E9&lt;&gt;"",C$4&gt;=WBS!$E9,C$4&lt;=WBS!$F9),"■",IF(AND(C$4&gt;=WBS!$C9,C$4&lt;=WBS!$D9),"□","")))</f>
         <v/>
       </c>
-      <c r="D8" s="22" t="str">
+      <c r="D8" s="24" t="str">
         <f>IF(WBS!$C9="","",IF(AND(WBS!$E9&lt;&gt;"",D$4&gt;=WBS!$E9,D$4&lt;=WBS!$F9),"■",IF(AND(D$4&gt;=WBS!$C9,D$4&lt;=WBS!$D9),"□","")))</f>
         <v>□</v>
       </c>
-      <c r="E8" s="22" t="str">
+      <c r="E8" s="24" t="str">
         <f>IF(WBS!$C9="","",IF(AND(WBS!$E9&lt;&gt;"",E$4&gt;=WBS!$E9,E$4&lt;=WBS!$F9),"■",IF(AND(E$4&gt;=WBS!$C9,E$4&lt;=WBS!$D9),"□","")))</f>
         <v>□</v>
       </c>
-      <c r="F8" s="22" t="str">
+      <c r="F8" s="24" t="str">
         <f>IF(WBS!$C9="","",IF(AND(WBS!$E9&lt;&gt;"",F$4&gt;=WBS!$E9,F$4&lt;=WBS!$F9),"■",IF(AND(F$4&gt;=WBS!$C9,F$4&lt;=WBS!$D9),"□","")))</f>
         <v>□</v>
       </c>
-      <c r="G8" s="22" t="str">
+      <c r="G8" s="24" t="str">
         <f>IF(WBS!$C9="","",IF(AND(WBS!$E9&lt;&gt;"",G$4&gt;=WBS!$E9,G$4&lt;=WBS!$F9),"■",IF(AND(G$4&gt;=WBS!$C9,G$4&lt;=WBS!$D9),"□","")))</f>
         <v/>
       </c>
-      <c r="H8" s="22" t="str">
+      <c r="H8" s="24" t="str">
         <f>IF(WBS!$C9="","",IF(AND(WBS!$E9&lt;&gt;"",H$4&gt;=WBS!$E9,H$4&lt;=WBS!$F9),"■",IF(AND(H$4&gt;=WBS!$C9,H$4&lt;=WBS!$D9),"□","")))</f>
         <v/>
       </c>
-      <c r="I8" s="22" t="str">
+      <c r="I8" s="24" t="str">
         <f>IF(WBS!$C9="","",IF(AND(WBS!$E9&lt;&gt;"",I$4&gt;=WBS!$E9,I$4&lt;=WBS!$F9),"■",IF(AND(I$4&gt;=WBS!$C9,I$4&lt;=WBS!$D9),"□","")))</f>
         <v/>
       </c>
-      <c r="J8" s="22" t="str">
+      <c r="J8" s="24" t="str">
         <f>IF(WBS!$C9="","",IF(AND(WBS!$E9&lt;&gt;"",J$4&gt;=WBS!$E9,J$4&lt;=WBS!$F9),"■",IF(AND(J$4&gt;=WBS!$C9,J$4&lt;=WBS!$D9),"□","")))</f>
         <v/>
       </c>
-      <c r="K8" s="22" t="str">
+      <c r="K8" s="24" t="str">
         <f>IF(WBS!$C9="","",IF(AND(WBS!$E9&lt;&gt;"",K$4&gt;=WBS!$E9,K$4&lt;=WBS!$F9),"■",IF(AND(K$4&gt;=WBS!$C9,K$4&lt;=WBS!$D9),"□","")))</f>
         <v/>
       </c>
-      <c r="L8" s="22" t="str">
+      <c r="L8" s="24" t="str">
         <f>IF(WBS!$C9="","",IF(AND(WBS!$E9&lt;&gt;"",L$4&gt;=WBS!$E9,L$4&lt;=WBS!$F9),"■",IF(AND(L$4&gt;=WBS!$C9,L$4&lt;=WBS!$D9),"□","")))</f>
         <v/>
       </c>
-      <c r="M8" s="22" t="str">
+      <c r="M8" s="24" t="str">
         <f>IF(WBS!$C9="","",IF(AND(WBS!$E9&lt;&gt;"",M$4&gt;=WBS!$E9,M$4&lt;=WBS!$F9),"■",IF(AND(M$4&gt;=WBS!$C9,M$4&lt;=WBS!$D9),"□","")))</f>
         <v/>
       </c>
-      <c r="N8" s="22" t="str">
+      <c r="N8" s="24" t="str">
         <f>IF(WBS!$C9="","",IF(AND(WBS!$E9&lt;&gt;"",N$4&gt;=WBS!$E9,N$4&lt;=WBS!$F9),"■",IF(AND(N$4&gt;=WBS!$C9,N$4&lt;=WBS!$D9),"□","")))</f>
         <v/>
       </c>
-      <c r="O8" s="22" t="str">
+      <c r="O8" s="24" t="str">
         <f>IF(WBS!$C9="","",IF(AND(WBS!$E9&lt;&gt;"",O$4&gt;=WBS!$E9,O$4&lt;=WBS!$F9),"■",IF(AND(O$4&gt;=WBS!$C9,O$4&lt;=WBS!$D9),"□","")))</f>
         <v/>
       </c>
-      <c r="P8" s="22" t="str">
+      <c r="P8" s="24" t="str">
         <f>IF(WBS!$C9="","",IF(AND(WBS!$E9&lt;&gt;"",P$4&gt;=WBS!$E9,P$4&lt;=WBS!$F9),"■",IF(AND(P$4&gt;=WBS!$C9,P$4&lt;=WBS!$D9),"□","")))</f>
         <v/>
       </c>
-      <c r="Q8" s="22" t="str">
+      <c r="Q8" s="24" t="str">
         <f>IF(WBS!$C9="","",IF(AND(WBS!$E9&lt;&gt;"",Q$4&gt;=WBS!$E9,Q$4&lt;=WBS!$F9),"■",IF(AND(Q$4&gt;=WBS!$C9,Q$4&lt;=WBS!$D9),"□","")))</f>
         <v/>
       </c>
-      <c r="R8" s="22" t="str">
+      <c r="R8" s="24" t="str">
         <f>IF(WBS!$C9="","",IF(AND(WBS!$E9&lt;&gt;"",R$4&gt;=WBS!$E9,R$4&lt;=WBS!$F9),"■",IF(AND(R$4&gt;=WBS!$C9,R$4&lt;=WBS!$D9),"□","")))</f>
         <v/>
       </c>
-      <c r="S8" s="22" t="str">
+      <c r="S8" s="24" t="str">
         <f>IF(WBS!$C9="","",IF(AND(WBS!$E9&lt;&gt;"",S$4&gt;=WBS!$E9,S$4&lt;=WBS!$F9),"■",IF(AND(S$4&gt;=WBS!$C9,S$4&lt;=WBS!$D9),"□","")))</f>
         <v/>
       </c>
-      <c r="T8" s="22" t="str">
+      <c r="T8" s="24" t="str">
         <f>IF(WBS!$C9="","",IF(AND(WBS!$E9&lt;&gt;"",T$4&gt;=WBS!$E9,T$4&lt;=WBS!$F9),"■",IF(AND(T$4&gt;=WBS!$C9,T$4&lt;=WBS!$D9),"□","")))</f>
         <v/>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A9" s="21" t="str">
+      <c r="A9" s="23" t="str">
         <f>WBS!A10</f>
         <v>2.1</v>
       </c>
-      <c r="B9" s="21" t="str">
+      <c r="B9" s="23" t="str">
         <f>WBS!B10</f>
         <v>Ghi chú mục 1–3, bảng thuật ngữ</v>
       </c>
-      <c r="C9" s="22" t="str">
+      <c r="C9" s="24" t="str">
         <f>IF(WBS!$C10="","",IF(AND(WBS!$E10&lt;&gt;"",C$4&gt;=WBS!$E10,C$4&lt;=WBS!$F10),"■",IF(AND(C$4&gt;=WBS!$C10,C$4&lt;=WBS!$D10),"□","")))</f>
         <v/>
       </c>
-      <c r="D9" s="22" t="str">
+      <c r="D9" s="24" t="str">
         <f>IF(WBS!$C10="","",IF(AND(WBS!$E10&lt;&gt;"",D$4&gt;=WBS!$E10,D$4&lt;=WBS!$F10),"■",IF(AND(D$4&gt;=WBS!$C10,D$4&lt;=WBS!$D10),"□","")))</f>
         <v>□</v>
       </c>
-      <c r="E9" s="22" t="str">
+      <c r="E9" s="24" t="str">
         <f>IF(WBS!$C10="","",IF(AND(WBS!$E10&lt;&gt;"",E$4&gt;=WBS!$E10,E$4&lt;=WBS!$F10),"■",IF(AND(E$4&gt;=WBS!$C10,E$4&lt;=WBS!$D10),"□","")))</f>
         <v>■</v>
       </c>
-      <c r="F9" s="22" t="str">
+      <c r="F9" s="24" t="str">
         <f>IF(WBS!$C10="","",IF(AND(WBS!$E10&lt;&gt;"",F$4&gt;=WBS!$E10,F$4&lt;=WBS!$F10),"■",IF(AND(F$4&gt;=WBS!$C10,F$4&lt;=WBS!$D10),"□","")))</f>
         <v/>
       </c>
-      <c r="G9" s="22" t="str">
+      <c r="G9" s="24" t="str">
         <f>IF(WBS!$C10="","",IF(AND(WBS!$E10&lt;&gt;"",G$4&gt;=WBS!$E10,G$4&lt;=WBS!$F10),"■",IF(AND(G$4&gt;=WBS!$C10,G$4&lt;=WBS!$D10),"□","")))</f>
         <v/>
       </c>
-      <c r="H9" s="22" t="str">
+      <c r="H9" s="24" t="str">
         <f>IF(WBS!$C10="","",IF(AND(WBS!$E10&lt;&gt;"",H$4&gt;=WBS!$E10,H$4&lt;=WBS!$F10),"■",IF(AND(H$4&gt;=WBS!$C10,H$4&lt;=WBS!$D10),"□","")))</f>
         <v/>
       </c>
-      <c r="I9" s="22" t="str">
+      <c r="I9" s="24" t="str">
         <f>IF(WBS!$C10="","",IF(AND(WBS!$E10&lt;&gt;"",I$4&gt;=WBS!$E10,I$4&lt;=WBS!$F10),"■",IF(AND(I$4&gt;=WBS!$C10,I$4&lt;=WBS!$D10),"□","")))</f>
         <v/>
       </c>
-      <c r="J9" s="22" t="str">
+      <c r="J9" s="24" t="str">
         <f>IF(WBS!$C10="","",IF(AND(WBS!$E10&lt;&gt;"",J$4&gt;=WBS!$E10,J$4&lt;=WBS!$F10),"■",IF(AND(J$4&gt;=WBS!$C10,J$4&lt;=WBS!$D10),"□","")))</f>
         <v/>
       </c>
-      <c r="K9" s="22" t="str">
+      <c r="K9" s="24" t="str">
         <f>IF(WBS!$C10="","",IF(AND(WBS!$E10&lt;&gt;"",K$4&gt;=WBS!$E10,K$4&lt;=WBS!$F10),"■",IF(AND(K$4&gt;=WBS!$C10,K$4&lt;=WBS!$D10),"□","")))</f>
         <v/>
       </c>
-      <c r="L9" s="22" t="str">
+      <c r="L9" s="24" t="str">
         <f>IF(WBS!$C10="","",IF(AND(WBS!$E10&lt;&gt;"",L$4&gt;=WBS!$E10,L$4&lt;=WBS!$F10),"■",IF(AND(L$4&gt;=WBS!$C10,L$4&lt;=WBS!$D10),"□","")))</f>
         <v/>
       </c>
-      <c r="M9" s="22" t="str">
+      <c r="M9" s="24" t="str">
         <f>IF(WBS!$C10="","",IF(AND(WBS!$E10&lt;&gt;"",M$4&gt;=WBS!$E10,M$4&lt;=WBS!$F10),"■",IF(AND(M$4&gt;=WBS!$C10,M$4&lt;=WBS!$D10),"□","")))</f>
         <v/>
       </c>
-      <c r="N9" s="22" t="str">
+      <c r="N9" s="24" t="str">
         <f>IF(WBS!$C10="","",IF(AND(WBS!$E10&lt;&gt;"",N$4&gt;=WBS!$E10,N$4&lt;=WBS!$F10),"■",IF(AND(N$4&gt;=WBS!$C10,N$4&lt;=WBS!$D10),"□","")))</f>
         <v/>
       </c>
-      <c r="O9" s="22" t="str">
+      <c r="O9" s="24" t="str">
         <f>IF(WBS!$C10="","",IF(AND(WBS!$E10&lt;&gt;"",O$4&gt;=WBS!$E10,O$4&lt;=WBS!$F10),"■",IF(AND(O$4&gt;=WBS!$C10,O$4&lt;=WBS!$D10),"□","")))</f>
         <v/>
       </c>
-      <c r="P9" s="22" t="str">
+      <c r="P9" s="24" t="str">
         <f>IF(WBS!$C10="","",IF(AND(WBS!$E10&lt;&gt;"",P$4&gt;=WBS!$E10,P$4&lt;=WBS!$F10),"■",IF(AND(P$4&gt;=WBS!$C10,P$4&lt;=WBS!$D10),"□","")))</f>
         <v/>
       </c>
-      <c r="Q9" s="22" t="str">
+      <c r="Q9" s="24" t="str">
         <f>IF(WBS!$C10="","",IF(AND(WBS!$E10&lt;&gt;"",Q$4&gt;=WBS!$E10,Q$4&lt;=WBS!$F10),"■",IF(AND(Q$4&gt;=WBS!$C10,Q$4&lt;=WBS!$D10),"□","")))</f>
         <v/>
       </c>
-      <c r="R9" s="22" t="str">
+      <c r="R9" s="24" t="str">
         <f>IF(WBS!$C10="","",IF(AND(WBS!$E10&lt;&gt;"",R$4&gt;=WBS!$E10,R$4&lt;=WBS!$F10),"■",IF(AND(R$4&gt;=WBS!$C10,R$4&lt;=WBS!$D10),"□","")))</f>
         <v/>
       </c>
-      <c r="S9" s="22" t="str">
+      <c r="S9" s="24" t="str">
         <f>IF(WBS!$C10="","",IF(AND(WBS!$E10&lt;&gt;"",S$4&gt;=WBS!$E10,S$4&lt;=WBS!$F10),"■",IF(AND(S$4&gt;=WBS!$C10,S$4&lt;=WBS!$D10),"□","")))</f>
         <v/>
       </c>
-      <c r="T9" s="22" t="str">
+      <c r="T9" s="24" t="str">
         <f>IF(WBS!$C10="","",IF(AND(WBS!$E10&lt;&gt;"",T$4&gt;=WBS!$E10,T$4&lt;=WBS!$F10),"■",IF(AND(T$4&gt;=WBS!$C10,T$4&lt;=WBS!$D10),"□","")))</f>
         <v/>
       </c>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A10" s="21" t="str">
+      <c r="A10" s="23" t="str">
         <f>WBS!A11</f>
         <v>2.2</v>
       </c>
-      <c r="B10" s="21" t="str">
+      <c r="B10" s="23" t="str">
         <f>WBS!B11</f>
         <v>Ghi chú kết quả, tổng hợp điểm mâu thuẫn</v>
       </c>
-      <c r="C10" s="22" t="str">
+      <c r="C10" s="24" t="str">
         <f>IF(WBS!$C11="","",IF(AND(WBS!$E11&lt;&gt;"",C$4&gt;=WBS!$E11,C$4&lt;=WBS!$F11),"■",IF(AND(C$4&gt;=WBS!$C11,C$4&lt;=WBS!$D11),"□","")))</f>
         <v/>
       </c>
-      <c r="D10" s="22" t="str">
+      <c r="D10" s="24" t="str">
         <f>IF(WBS!$C11="","",IF(AND(WBS!$E11&lt;&gt;"",D$4&gt;=WBS!$E11,D$4&lt;=WBS!$F11),"■",IF(AND(D$4&gt;=WBS!$C11,D$4&lt;=WBS!$D11),"□","")))</f>
         <v/>
       </c>
-      <c r="E10" s="22" t="str">
+      <c r="E10" s="24" t="str">
         <f>IF(WBS!$C11="","",IF(AND(WBS!$E11&lt;&gt;"",E$4&gt;=WBS!$E11,E$4&lt;=WBS!$F11),"■",IF(AND(E$4&gt;=WBS!$C11,E$4&lt;=WBS!$D11),"□","")))</f>
         <v>■</v>
       </c>
-      <c r="F10" s="22" t="str">
+      <c r="F10" s="24" t="str">
         <f>IF(WBS!$C11="","",IF(AND(WBS!$E11&lt;&gt;"",F$4&gt;=WBS!$E11,F$4&lt;=WBS!$F11),"■",IF(AND(F$4&gt;=WBS!$C11,F$4&lt;=WBS!$D11),"□","")))</f>
         <v>□</v>
       </c>
-      <c r="G10" s="22" t="str">
+      <c r="G10" s="24" t="str">
         <f>IF(WBS!$C11="","",IF(AND(WBS!$E11&lt;&gt;"",G$4&gt;=WBS!$E11,G$4&lt;=WBS!$F11),"■",IF(AND(G$4&gt;=WBS!$C11,G$4&lt;=WBS!$D11),"□","")))</f>
         <v/>
       </c>
-      <c r="H10" s="22" t="str">
+      <c r="H10" s="24" t="str">
         <f>IF(WBS!$C11="","",IF(AND(WBS!$E11&lt;&gt;"",H$4&gt;=WBS!$E11,H$4&lt;=WBS!$F11),"■",IF(AND(H$4&gt;=WBS!$C11,H$4&lt;=WBS!$D11),"□","")))</f>
         <v/>
       </c>
-      <c r="I10" s="22" t="str">
+      <c r="I10" s="24" t="str">
         <f>IF(WBS!$C11="","",IF(AND(WBS!$E11&lt;&gt;"",I$4&gt;=WBS!$E11,I$4&lt;=WBS!$F11),"■",IF(AND(I$4&gt;=WBS!$C11,I$4&lt;=WBS!$D11),"□","")))</f>
         <v/>
       </c>
-      <c r="J10" s="22" t="str">
+      <c r="J10" s="24" t="str">
         <f>IF(WBS!$C11="","",IF(AND(WBS!$E11&lt;&gt;"",J$4&gt;=WBS!$E11,J$4&lt;=WBS!$F11),"■",IF(AND(J$4&gt;=WBS!$C11,J$4&lt;=WBS!$D11),"□","")))</f>
         <v/>
       </c>
-      <c r="K10" s="22" t="str">
+      <c r="K10" s="24" t="str">
         <f>IF(WBS!$C11="","",IF(AND(WBS!$E11&lt;&gt;"",K$4&gt;=WBS!$E11,K$4&lt;=WBS!$F11),"■",IF(AND(K$4&gt;=WBS!$C11,K$4&lt;=WBS!$D11),"□","")))</f>
         <v/>
       </c>
-      <c r="L10" s="22" t="str">
+      <c r="L10" s="24" t="str">
         <f>IF(WBS!$C11="","",IF(AND(WBS!$E11&lt;&gt;"",L$4&gt;=WBS!$E11,L$4&lt;=WBS!$F11),"■",IF(AND(L$4&gt;=WBS!$C11,L$4&lt;=WBS!$D11),"□","")))</f>
         <v/>
       </c>
-      <c r="M10" s="22" t="str">
+      <c r="M10" s="24" t="str">
         <f>IF(WBS!$C11="","",IF(AND(WBS!$E11&lt;&gt;"",M$4&gt;=WBS!$E11,M$4&lt;=WBS!$F11),"■",IF(AND(M$4&gt;=WBS!$C11,M$4&lt;=WBS!$D11),"□","")))</f>
         <v/>
       </c>
-      <c r="N10" s="22" t="str">
+      <c r="N10" s="24" t="str">
         <f>IF(WBS!$C11="","",IF(AND(WBS!$E11&lt;&gt;"",N$4&gt;=WBS!$E11,N$4&lt;=WBS!$F11),"■",IF(AND(N$4&gt;=WBS!$C11,N$4&lt;=WBS!$D11),"□","")))</f>
         <v/>
       </c>
-      <c r="O10" s="22" t="str">
+      <c r="O10" s="24" t="str">
         <f>IF(WBS!$C11="","",IF(AND(WBS!$E11&lt;&gt;"",O$4&gt;=WBS!$E11,O$4&lt;=WBS!$F11),"■",IF(AND(O$4&gt;=WBS!$C11,O$4&lt;=WBS!$D11),"□","")))</f>
         <v/>
       </c>
-      <c r="P10" s="22" t="str">
+      <c r="P10" s="24" t="str">
         <f>IF(WBS!$C11="","",IF(AND(WBS!$E11&lt;&gt;"",P$4&gt;=WBS!$E11,P$4&lt;=WBS!$F11),"■",IF(AND(P$4&gt;=WBS!$C11,P$4&lt;=WBS!$D11),"□","")))</f>
         <v/>
       </c>
-      <c r="Q10" s="22" t="str">
+      <c r="Q10" s="24" t="str">
         <f>IF(WBS!$C11="","",IF(AND(WBS!$E11&lt;&gt;"",Q$4&gt;=WBS!$E11,Q$4&lt;=WBS!$F11),"■",IF(AND(Q$4&gt;=WBS!$C11,Q$4&lt;=WBS!$D11),"□","")))</f>
         <v/>
       </c>
-      <c r="R10" s="22" t="str">
+      <c r="R10" s="24" t="str">
         <f>IF(WBS!$C11="","",IF(AND(WBS!$E11&lt;&gt;"",R$4&gt;=WBS!$E11,R$4&lt;=WBS!$F11),"■",IF(AND(R$4&gt;=WBS!$C11,R$4&lt;=WBS!$D11),"□","")))</f>
         <v/>
       </c>
-      <c r="S10" s="22" t="str">
+      <c r="S10" s="24" t="str">
         <f>IF(WBS!$C11="","",IF(AND(WBS!$E11&lt;&gt;"",S$4&gt;=WBS!$E11,S$4&lt;=WBS!$F11),"■",IF(AND(S$4&gt;=WBS!$C11,S$4&lt;=WBS!$D11),"□","")))</f>
         <v/>
       </c>
-      <c r="T10" s="22" t="str">
+      <c r="T10" s="24" t="str">
         <f>IF(WBS!$C11="","",IF(AND(WBS!$E11&lt;&gt;"",T$4&gt;=WBS!$E11,T$4&lt;=WBS!$F11),"■",IF(AND(T$4&gt;=WBS!$C11,T$4&lt;=WBS!$D11),"□","")))</f>
         <v/>
       </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A11" s="21" t="str">
+      <c r="A11" s="23" t="str">
         <f>WBS!A12</f>
         <v>2.3</v>
       </c>
-      <c r="B11" s="21" t="str">
+      <c r="B11" s="23" t="str">
         <f>WBS!B12</f>
         <v>Lập danh sách tài liệu tham khảo</v>
       </c>
-      <c r="C11" s="22" t="str">
+      <c r="C11" s="24" t="str">
         <f>IF(WBS!$C12="","",IF(AND(WBS!$E12&lt;&gt;"",C$4&gt;=WBS!$E12,C$4&lt;=WBS!$F12),"■",IF(AND(C$4&gt;=WBS!$C12,C$4&lt;=WBS!$D12),"□","")))</f>
         <v/>
       </c>
-      <c r="D11" s="22" t="str">
+      <c r="D11" s="24" t="str">
         <f>IF(WBS!$C12="","",IF(AND(WBS!$E12&lt;&gt;"",D$4&gt;=WBS!$E12,D$4&lt;=WBS!$F12),"■",IF(AND(D$4&gt;=WBS!$C12,D$4&lt;=WBS!$D12),"□","")))</f>
         <v/>
       </c>
-      <c r="E11" s="22" t="str">
+      <c r="E11" s="24" t="str">
         <f>IF(WBS!$C12="","",IF(AND(WBS!$E12&lt;&gt;"",E$4&gt;=WBS!$E12,E$4&lt;=WBS!$F12),"■",IF(AND(E$4&gt;=WBS!$C12,E$4&lt;=WBS!$D12),"□","")))</f>
         <v>■</v>
       </c>
-      <c r="F11" s="22" t="str">
+      <c r="F11" s="24" t="str">
         <f>IF(WBS!$C12="","",IF(AND(WBS!$E12&lt;&gt;"",F$4&gt;=WBS!$E12,F$4&lt;=WBS!$F12),"■",IF(AND(F$4&gt;=WBS!$C12,F$4&lt;=WBS!$D12),"□","")))</f>
         <v>□</v>
       </c>
-      <c r="G11" s="22" t="str">
+      <c r="G11" s="24" t="str">
         <f>IF(WBS!$C12="","",IF(AND(WBS!$E12&lt;&gt;"",G$4&gt;=WBS!$E12,G$4&lt;=WBS!$F12),"■",IF(AND(G$4&gt;=WBS!$C12,G$4&lt;=WBS!$D12),"□","")))</f>
         <v/>
       </c>
-      <c r="H11" s="22" t="str">
+      <c r="H11" s="24" t="str">
         <f>IF(WBS!$C12="","",IF(AND(WBS!$E12&lt;&gt;"",H$4&gt;=WBS!$E12,H$4&lt;=WBS!$F12),"■",IF(AND(H$4&gt;=WBS!$C12,H$4&lt;=WBS!$D12),"□","")))</f>
         <v/>
       </c>
-      <c r="I11" s="22" t="str">
+      <c r="I11" s="24" t="str">
         <f>IF(WBS!$C12="","",IF(AND(WBS!$E12&lt;&gt;"",I$4&gt;=WBS!$E12,I$4&lt;=WBS!$F12),"■",IF(AND(I$4&gt;=WBS!$C12,I$4&lt;=WBS!$D12),"□","")))</f>
         <v/>
       </c>
-      <c r="J11" s="22" t="str">
+      <c r="J11" s="24" t="str">
         <f>IF(WBS!$C12="","",IF(AND(WBS!$E12&lt;&gt;"",J$4&gt;=WBS!$E12,J$4&lt;=WBS!$F12),"■",IF(AND(J$4&gt;=WBS!$C12,J$4&lt;=WBS!$D12),"□","")))</f>
         <v/>
       </c>
-      <c r="K11" s="22" t="str">
+      <c r="K11" s="24" t="str">
         <f>IF(WBS!$C12="","",IF(AND(WBS!$E12&lt;&gt;"",K$4&gt;=WBS!$E12,K$4&lt;=WBS!$F12),"■",IF(AND(K$4&gt;=WBS!$C12,K$4&lt;=WBS!$D12),"□","")))</f>
         <v/>
       </c>
-      <c r="L11" s="22" t="str">
+      <c r="L11" s="24" t="str">
         <f>IF(WBS!$C12="","",IF(AND(WBS!$E12&lt;&gt;"",L$4&gt;=WBS!$E12,L$4&lt;=WBS!$F12),"■",IF(AND(L$4&gt;=WBS!$C12,L$4&lt;=WBS!$D12),"□","")))</f>
         <v/>
       </c>
-      <c r="M11" s="22" t="str">
+      <c r="M11" s="24" t="str">
         <f>IF(WBS!$C12="","",IF(AND(WBS!$E12&lt;&gt;"",M$4&gt;=WBS!$E12,M$4&lt;=WBS!$F12),"■",IF(AND(M$4&gt;=WBS!$C12,M$4&lt;=WBS!$D12),"□","")))</f>
         <v/>
       </c>
-      <c r="N11" s="22" t="str">
+      <c r="N11" s="24" t="str">
         <f>IF(WBS!$C12="","",IF(AND(WBS!$E12&lt;&gt;"",N$4&gt;=WBS!$E12,N$4&lt;=WBS!$F12),"■",IF(AND(N$4&gt;=WBS!$C12,N$4&lt;=WBS!$D12),"□","")))</f>
         <v/>
       </c>
-      <c r="O11" s="22" t="str">
+      <c r="O11" s="24" t="str">
         <f>IF(WBS!$C12="","",IF(AND(WBS!$E12&lt;&gt;"",O$4&gt;=WBS!$E12,O$4&lt;=WBS!$F12),"■",IF(AND(O$4&gt;=WBS!$C12,O$4&lt;=WBS!$D12),"□","")))</f>
         <v/>
       </c>
-      <c r="P11" s="22" t="str">
+      <c r="P11" s="24" t="str">
         <f>IF(WBS!$C12="","",IF(AND(WBS!$E12&lt;&gt;"",P$4&gt;=WBS!$E12,P$4&lt;=WBS!$F12),"■",IF(AND(P$4&gt;=WBS!$C12,P$4&lt;=WBS!$D12),"□","")))</f>
         <v/>
       </c>
-      <c r="Q11" s="22" t="str">
+      <c r="Q11" s="24" t="str">
         <f>IF(WBS!$C12="","",IF(AND(WBS!$E12&lt;&gt;"",Q$4&gt;=WBS!$E12,Q$4&lt;=WBS!$F12),"■",IF(AND(Q$4&gt;=WBS!$C12,Q$4&lt;=WBS!$D12),"□","")))</f>
         <v/>
       </c>
-      <c r="R11" s="22" t="str">
+      <c r="R11" s="24" t="str">
         <f>IF(WBS!$C12="","",IF(AND(WBS!$E12&lt;&gt;"",R$4&gt;=WBS!$E12,R$4&lt;=WBS!$F12),"■",IF(AND(R$4&gt;=WBS!$C12,R$4&lt;=WBS!$D12),"□","")))</f>
         <v/>
       </c>
-      <c r="S11" s="22" t="str">
+      <c r="S11" s="24" t="str">
         <f>IF(WBS!$C12="","",IF(AND(WBS!$E12&lt;&gt;"",S$4&gt;=WBS!$E12,S$4&lt;=WBS!$F12),"■",IF(AND(S$4&gt;=WBS!$C12,S$4&lt;=WBS!$D12),"□","")))</f>
         <v/>
       </c>
-      <c r="T11" s="22" t="str">
+      <c r="T11" s="24" t="str">
         <f>IF(WBS!$C12="","",IF(AND(WBS!$E12&lt;&gt;"",T$4&gt;=WBS!$E12,T$4&lt;=WBS!$F12),"■",IF(AND(T$4&gt;=WBS!$C12,T$4&lt;=WBS!$D12),"□","")))</f>
         <v/>
       </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A12" s="21" t="str">
+      <c r="A12" s="23" t="str">
         <f>WBS!A13</f>
         <v>3</v>
       </c>
-      <c r="B12" s="21" t="str">
+      <c r="B12" s="23" t="str">
         <f>WBS!B13</f>
         <v>Tái hiện thực nghiệm</v>
       </c>
-      <c r="C12" s="22" t="str">
+      <c r="C12" s="24" t="str">
         <f>IF(WBS!$C13="","",IF(AND(WBS!$E13&lt;&gt;"",C$4&gt;=WBS!$E13,C$4&lt;=WBS!$F13),"■",IF(AND(C$4&gt;=WBS!$C13,C$4&lt;=WBS!$D13),"□","")))</f>
         <v/>
       </c>
-      <c r="D12" s="22" t="str">
+      <c r="D12" s="24" t="str">
         <f>IF(WBS!$C13="","",IF(AND(WBS!$E13&lt;&gt;"",D$4&gt;=WBS!$E13,D$4&lt;=WBS!$F13),"■",IF(AND(D$4&gt;=WBS!$C13,D$4&lt;=WBS!$D13),"□","")))</f>
         <v/>
       </c>
-      <c r="E12" s="22" t="str">
+      <c r="E12" s="24" t="str">
         <f>IF(WBS!$C13="","",IF(AND(WBS!$E13&lt;&gt;"",E$4&gt;=WBS!$E13,E$4&lt;=WBS!$F13),"■",IF(AND(E$4&gt;=WBS!$C13,E$4&lt;=WBS!$D13),"□","")))</f>
         <v/>
       </c>
-      <c r="F12" s="22" t="str">
+      <c r="F12" s="24" t="str">
         <f>IF(WBS!$C13="","",IF(AND(WBS!$E13&lt;&gt;"",F$4&gt;=WBS!$E13,F$4&lt;=WBS!$F13),"■",IF(AND(F$4&gt;=WBS!$C13,F$4&lt;=WBS!$D13),"□","")))</f>
         <v/>
       </c>
-      <c r="G12" s="22" t="str">
+      <c r="G12" s="24" t="str">
         <f>IF(WBS!$C13="","",IF(AND(WBS!$E13&lt;&gt;"",G$4&gt;=WBS!$E13,G$4&lt;=WBS!$F13),"■",IF(AND(G$4&gt;=WBS!$C13,G$4&lt;=WBS!$D13),"□","")))</f>
         <v>□</v>
       </c>
-      <c r="H12" s="22" t="str">
+      <c r="H12" s="24" t="str">
         <f>IF(WBS!$C13="","",IF(AND(WBS!$E13&lt;&gt;"",H$4&gt;=WBS!$E13,H$4&lt;=WBS!$F13),"■",IF(AND(H$4&gt;=WBS!$C13,H$4&lt;=WBS!$D13),"□","")))</f>
         <v>□</v>
       </c>
-      <c r="I12" s="22" t="str">
+      <c r="I12" s="24" t="str">
         <f>IF(WBS!$C13="","",IF(AND(WBS!$E13&lt;&gt;"",I$4&gt;=WBS!$E13,I$4&lt;=WBS!$F13),"■",IF(AND(I$4&gt;=WBS!$C13,I$4&lt;=WBS!$D13),"□","")))</f>
         <v>□</v>
       </c>
-      <c r="J12" s="22" t="str">
+      <c r="J12" s="24" t="str">
         <f>IF(WBS!$C13="","",IF(AND(WBS!$E13&lt;&gt;"",J$4&gt;=WBS!$E13,J$4&lt;=WBS!$F13),"■",IF(AND(J$4&gt;=WBS!$C13,J$4&lt;=WBS!$D13),"□","")))</f>
         <v>□</v>
       </c>
-      <c r="K12" s="22" t="str">
+      <c r="K12" s="24" t="str">
         <f>IF(WBS!$C13="","",IF(AND(WBS!$E13&lt;&gt;"",K$4&gt;=WBS!$E13,K$4&lt;=WBS!$F13),"■",IF(AND(K$4&gt;=WBS!$C13,K$4&lt;=WBS!$D13),"□","")))</f>
         <v>□</v>
       </c>
-      <c r="L12" s="22" t="str">
+      <c r="L12" s="24" t="str">
         <f>IF(WBS!$C13="","",IF(AND(WBS!$E13&lt;&gt;"",L$4&gt;=WBS!$E13,L$4&lt;=WBS!$F13),"■",IF(AND(L$4&gt;=WBS!$C13,L$4&lt;=WBS!$D13),"□","")))</f>
         <v>□</v>
       </c>
-      <c r="M12" s="22" t="str">
+      <c r="M12" s="24" t="str">
         <f>IF(WBS!$C13="","",IF(AND(WBS!$E13&lt;&gt;"",M$4&gt;=WBS!$E13,M$4&lt;=WBS!$F13),"■",IF(AND(M$4&gt;=WBS!$C13,M$4&lt;=WBS!$D13),"□","")))</f>
         <v>□</v>
       </c>
-      <c r="N12" s="22" t="str">
+      <c r="N12" s="24" t="str">
         <f>IF(WBS!$C13="","",IF(AND(WBS!$E13&lt;&gt;"",N$4&gt;=WBS!$E13,N$4&lt;=WBS!$F13),"■",IF(AND(N$4&gt;=WBS!$C13,N$4&lt;=WBS!$D13),"□","")))</f>
         <v/>
       </c>
-      <c r="O12" s="22" t="str">
+      <c r="O12" s="24" t="str">
         <f>IF(WBS!$C13="","",IF(AND(WBS!$E13&lt;&gt;"",O$4&gt;=WBS!$E13,O$4&lt;=WBS!$F13),"■",IF(AND(O$4&gt;=WBS!$C13,O$4&lt;=WBS!$D13),"□","")))</f>
         <v/>
       </c>
-      <c r="P12" s="22" t="str">
+      <c r="P12" s="24" t="str">
         <f>IF(WBS!$C13="","",IF(AND(WBS!$E13&lt;&gt;"",P$4&gt;=WBS!$E13,P$4&lt;=WBS!$F13),"■",IF(AND(P$4&gt;=WBS!$C13,P$4&lt;=WBS!$D13),"□","")))</f>
         <v/>
       </c>
-      <c r="Q12" s="22" t="str">
+      <c r="Q12" s="24" t="str">
         <f>IF(WBS!$C13="","",IF(AND(WBS!$E13&lt;&gt;"",Q$4&gt;=WBS!$E13,Q$4&lt;=WBS!$F13),"■",IF(AND(Q$4&gt;=WBS!$C13,Q$4&lt;=WBS!$D13),"□","")))</f>
         <v/>
       </c>
-      <c r="R12" s="22" t="str">
+      <c r="R12" s="24" t="str">
         <f>IF(WBS!$C13="","",IF(AND(WBS!$E13&lt;&gt;"",R$4&gt;=WBS!$E13,R$4&lt;=WBS!$F13),"■",IF(AND(R$4&gt;=WBS!$C13,R$4&lt;=WBS!$D13),"□","")))</f>
         <v/>
       </c>
-      <c r="S12" s="22" t="str">
+      <c r="S12" s="24" t="str">
         <f>IF(WBS!$C13="","",IF(AND(WBS!$E13&lt;&gt;"",S$4&gt;=WBS!$E13,S$4&lt;=WBS!$F13),"■",IF(AND(S$4&gt;=WBS!$C13,S$4&lt;=WBS!$D13),"□","")))</f>
         <v/>
       </c>
-      <c r="T12" s="22" t="str">
+      <c r="T12" s="24" t="str">
         <f>IF(WBS!$C13="","",IF(AND(WBS!$E13&lt;&gt;"",T$4&gt;=WBS!$E13,T$4&lt;=WBS!$F13),"■",IF(AND(T$4&gt;=WBS!$C13,T$4&lt;=WBS!$D13),"□","")))</f>
         <v/>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A13" s="21" t="str">
+      <c r="A13" s="23" t="str">
         <f>WBS!A14</f>
         <v>3.1</v>
       </c>
-      <c r="B13" s="21" t="str">
+      <c r="B13" s="23" t="str">
         <f>WBS!B14</f>
         <v>Nhập số liệu các bảng của bài báo</v>
       </c>
-      <c r="C13" s="22" t="str">
+      <c r="C13" s="24" t="str">
         <f>IF(WBS!$C14="","",IF(AND(WBS!$E14&lt;&gt;"",C$4&gt;=WBS!$E14,C$4&lt;=WBS!$F14),"■",IF(AND(C$4&gt;=WBS!$C14,C$4&lt;=WBS!$D14),"□","")))</f>
         <v/>
       </c>
-      <c r="D13" s="22" t="str">
+      <c r="D13" s="24" t="str">
         <f>IF(WBS!$C14="","",IF(AND(WBS!$E14&lt;&gt;"",D$4&gt;=WBS!$E14,D$4&lt;=WBS!$F14),"■",IF(AND(D$4&gt;=WBS!$C14,D$4&lt;=WBS!$D14),"□","")))</f>
         <v/>
       </c>
-      <c r="E13" s="22" t="str">
+      <c r="E13" s="24" t="str">
         <f>IF(WBS!$C14="","",IF(AND(WBS!$E14&lt;&gt;"",E$4&gt;=WBS!$E14,E$4&lt;=WBS!$F14),"■",IF(AND(E$4&gt;=WBS!$C14,E$4&lt;=WBS!$D14),"□","")))</f>
         <v/>
       </c>
-      <c r="F13" s="22" t="str">
+      <c r="F13" s="24" t="str">
         <f>IF(WBS!$C14="","",IF(AND(WBS!$E14&lt;&gt;"",F$4&gt;=WBS!$E14,F$4&lt;=WBS!$F14),"■",IF(AND(F$4&gt;=WBS!$C14,F$4&lt;=WBS!$D14),"□","")))</f>
         <v/>
       </c>
-      <c r="G13" s="22" t="str">
+      <c r="G13" s="24" t="str">
         <f>IF(WBS!$C14="","",IF(AND(WBS!$E14&lt;&gt;"",G$4&gt;=WBS!$E14,G$4&lt;=WBS!$F14),"■",IF(AND(G$4&gt;=WBS!$C14,G$4&lt;=WBS!$D14),"□","")))</f>
         <v>□</v>
       </c>
-      <c r="H13" s="22" t="str">
+      <c r="H13" s="24" t="str">
         <f>IF(WBS!$C14="","",IF(AND(WBS!$E14&lt;&gt;"",H$4&gt;=WBS!$E14,H$4&lt;=WBS!$F14),"■",IF(AND(H$4&gt;=WBS!$C14,H$4&lt;=WBS!$D14),"□","")))</f>
         <v>□</v>
       </c>
-      <c r="I13" s="22" t="str">
+      <c r="I13" s="24" t="str">
         <f>IF(WBS!$C14="","",IF(AND(WBS!$E14&lt;&gt;"",I$4&gt;=WBS!$E14,I$4&lt;=WBS!$F14),"■",IF(AND(I$4&gt;=WBS!$C14,I$4&lt;=WBS!$D14),"□","")))</f>
         <v/>
       </c>
-      <c r="J13" s="22" t="str">
+      <c r="J13" s="24" t="str">
         <f>IF(WBS!$C14="","",IF(AND(WBS!$E14&lt;&gt;"",J$4&gt;=WBS!$E14,J$4&lt;=WBS!$F14),"■",IF(AND(J$4&gt;=WBS!$C14,J$4&lt;=WBS!$D14),"□","")))</f>
         <v/>
       </c>
-      <c r="K13" s="22" t="str">
+      <c r="K13" s="24" t="str">
         <f>IF(WBS!$C14="","",IF(AND(WBS!$E14&lt;&gt;"",K$4&gt;=WBS!$E14,K$4&lt;=WBS!$F14),"■",IF(AND(K$4&gt;=WBS!$C14,K$4&lt;=WBS!$D14),"□","")))</f>
         <v>■</v>
       </c>
-      <c r="L13" s="22" t="str">
+      <c r="L13" s="24" t="str">
         <f>IF(WBS!$C14="","",IF(AND(WBS!$E14&lt;&gt;"",L$4&gt;=WBS!$E14,L$4&lt;=WBS!$F14),"■",IF(AND(L$4&gt;=WBS!$C14,L$4&lt;=WBS!$D14),"□","")))</f>
         <v/>
       </c>
-      <c r="M13" s="22" t="str">
+      <c r="M13" s="24" t="str">
         <f>IF(WBS!$C14="","",IF(AND(WBS!$E14&lt;&gt;"",M$4&gt;=WBS!$E14,M$4&lt;=WBS!$F14),"■",IF(AND(M$4&gt;=WBS!$C14,M$4&lt;=WBS!$D14),"□","")))</f>
         <v/>
       </c>
-      <c r="N13" s="22" t="str">
+      <c r="N13" s="24" t="str">
         <f>IF(WBS!$C14="","",IF(AND(WBS!$E14&lt;&gt;"",N$4&gt;=WBS!$E14,N$4&lt;=WBS!$F14),"■",IF(AND(N$4&gt;=WBS!$C14,N$4&lt;=WBS!$D14),"□","")))</f>
         <v/>
       </c>
-      <c r="O13" s="22" t="str">
+      <c r="O13" s="24" t="str">
         <f>IF(WBS!$C14="","",IF(AND(WBS!$E14&lt;&gt;"",O$4&gt;=WBS!$E14,O$4&lt;=WBS!$F14),"■",IF(AND(O$4&gt;=WBS!$C14,O$4&lt;=WBS!$D14),"□","")))</f>
         <v/>
       </c>
-      <c r="P13" s="22" t="str">
+      <c r="P13" s="24" t="str">
         <f>IF(WBS!$C14="","",IF(AND(WBS!$E14&lt;&gt;"",P$4&gt;=WBS!$E14,P$4&lt;=WBS!$F14),"■",IF(AND(P$4&gt;=WBS!$C14,P$4&lt;=WBS!$D14),"□","")))</f>
         <v/>
       </c>
-      <c r="Q13" s="22" t="str">
+      <c r="Q13" s="24" t="str">
         <f>IF(WBS!$C14="","",IF(AND(WBS!$E14&lt;&gt;"",Q$4&gt;=WBS!$E14,Q$4&lt;=WBS!$F14),"■",IF(AND(Q$4&gt;=WBS!$C14,Q$4&lt;=WBS!$D14),"□","")))</f>
         <v/>
       </c>
-      <c r="R13" s="22" t="str">
+      <c r="R13" s="24" t="str">
         <f>IF(WBS!$C14="","",IF(AND(WBS!$E14&lt;&gt;"",R$4&gt;=WBS!$E14,R$4&lt;=WBS!$F14),"■",IF(AND(R$4&gt;=WBS!$C14,R$4&lt;=WBS!$D14),"□","")))</f>
         <v/>
       </c>
-      <c r="S13" s="22" t="str">
+      <c r="S13" s="24" t="str">
         <f>IF(WBS!$C14="","",IF(AND(WBS!$E14&lt;&gt;"",S$4&gt;=WBS!$E14,S$4&lt;=WBS!$F14),"■",IF(AND(S$4&gt;=WBS!$C14,S$4&lt;=WBS!$D14),"□","")))</f>
         <v/>
       </c>
-      <c r="T13" s="22" t="str">
+      <c r="T13" s="24" t="str">
         <f>IF(WBS!$C14="","",IF(AND(WBS!$E14&lt;&gt;"",T$4&gt;=WBS!$E14,T$4&lt;=WBS!$F14),"■",IF(AND(T$4&gt;=WBS!$C14,T$4&lt;=WBS!$D14),"□","")))</f>
         <v/>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A14" s="21" t="str">
+      <c r="A14" s="23" t="str">
         <f>WBS!A15</f>
         <v>3.2</v>
       </c>
-      <c r="B14" s="21" t="str">
+      <c r="B14" s="23" t="str">
         <f>WBS!B15</f>
         <v>Kiểm tra lại số liệu đã công bố</v>
       </c>
-      <c r="C14" s="22" t="str">
+      <c r="C14" s="24" t="str">
         <f>IF(WBS!$C15="","",IF(AND(WBS!$E15&lt;&gt;"",C$4&gt;=WBS!$E15,C$4&lt;=WBS!$F15),"■",IF(AND(C$4&gt;=WBS!$C15,C$4&lt;=WBS!$D15),"□","")))</f>
         <v/>
       </c>
-      <c r="D14" s="22" t="str">
+      <c r="D14" s="24" t="str">
         <f>IF(WBS!$C15="","",IF(AND(WBS!$E15&lt;&gt;"",D$4&gt;=WBS!$E15,D$4&lt;=WBS!$F15),"■",IF(AND(D$4&gt;=WBS!$C15,D$4&lt;=WBS!$D15),"□","")))</f>
         <v/>
       </c>
-      <c r="E14" s="22" t="str">
+      <c r="E14" s="24" t="str">
         <f>IF(WBS!$C15="","",IF(AND(WBS!$E15&lt;&gt;"",E$4&gt;=WBS!$E15,E$4&lt;=WBS!$F15),"■",IF(AND(E$4&gt;=WBS!$C15,E$4&lt;=WBS!$D15),"□","")))</f>
         <v/>
       </c>
-      <c r="F14" s="22" t="str">
+      <c r="F14" s="24" t="str">
         <f>IF(WBS!$C15="","",IF(AND(WBS!$E15&lt;&gt;"",F$4&gt;=WBS!$E15,F$4&lt;=WBS!$F15),"■",IF(AND(F$4&gt;=WBS!$C15,F$4&lt;=WBS!$D15),"□","")))</f>
         <v/>
       </c>
-      <c r="G14" s="22" t="str">
+      <c r="G14" s="24" t="str">
         <f>IF(WBS!$C15="","",IF(AND(WBS!$E15&lt;&gt;"",G$4&gt;=WBS!$E15,G$4&lt;=WBS!$F15),"■",IF(AND(G$4&gt;=WBS!$C15,G$4&lt;=WBS!$D15),"□","")))</f>
         <v/>
       </c>
-      <c r="H14" s="22" t="str">
+      <c r="H14" s="24" t="str">
         <f>IF(WBS!$C15="","",IF(AND(WBS!$E15&lt;&gt;"",H$4&gt;=WBS!$E15,H$4&lt;=WBS!$F15),"■",IF(AND(H$4&gt;=WBS!$C15,H$4&lt;=WBS!$D15),"□","")))</f>
         <v>□</v>
       </c>
-      <c r="I14" s="22" t="str">
+      <c r="I14" s="24" t="str">
         <f>IF(WBS!$C15="","",IF(AND(WBS!$E15&lt;&gt;"",I$4&gt;=WBS!$E15,I$4&lt;=WBS!$F15),"■",IF(AND(I$4&gt;=WBS!$C15,I$4&lt;=WBS!$D15),"□","")))</f>
         <v/>
       </c>
-      <c r="J14" s="22" t="str">
+      <c r="J14" s="24" t="str">
         <f>IF(WBS!$C15="","",IF(AND(WBS!$E15&lt;&gt;"",J$4&gt;=WBS!$E15,J$4&lt;=WBS!$F15),"■",IF(AND(J$4&gt;=WBS!$C15,J$4&lt;=WBS!$D15),"□","")))</f>
         <v/>
       </c>
-      <c r="K14" s="22" t="str">
+      <c r="K14" s="24" t="str">
         <f>IF(WBS!$C15="","",IF(AND(WBS!$E15&lt;&gt;"",K$4&gt;=WBS!$E15,K$4&lt;=WBS!$F15),"■",IF(AND(K$4&gt;=WBS!$C15,K$4&lt;=WBS!$D15),"□","")))</f>
         <v>■</v>
       </c>
-      <c r="L14" s="22" t="str">
+      <c r="L14" s="24" t="str">
         <f>IF(WBS!$C15="","",IF(AND(WBS!$E15&lt;&gt;"",L$4&gt;=WBS!$E15,L$4&lt;=WBS!$F15),"■",IF(AND(L$4&gt;=WBS!$C15,L$4&lt;=WBS!$D15),"□","")))</f>
         <v/>
       </c>
-      <c r="M14" s="22" t="str">
+      <c r="M14" s="24" t="str">
         <f>IF(WBS!$C15="","",IF(AND(WBS!$E15&lt;&gt;"",M$4&gt;=WBS!$E15,M$4&lt;=WBS!$F15),"■",IF(AND(M$4&gt;=WBS!$C15,M$4&lt;=WBS!$D15),"□","")))</f>
         <v/>
       </c>
-      <c r="N14" s="22" t="str">
+      <c r="N14" s="24" t="str">
         <f>IF(WBS!$C15="","",IF(AND(WBS!$E15&lt;&gt;"",N$4&gt;=WBS!$E15,N$4&lt;=WBS!$F15),"■",IF(AND(N$4&gt;=WBS!$C15,N$4&lt;=WBS!$D15),"□","")))</f>
         <v/>
       </c>
-      <c r="O14" s="22" t="str">
+      <c r="O14" s="24" t="str">
         <f>IF(WBS!$C15="","",IF(AND(WBS!$E15&lt;&gt;"",O$4&gt;=WBS!$E15,O$4&lt;=WBS!$F15),"■",IF(AND(O$4&gt;=WBS!$C15,O$4&lt;=WBS!$D15),"□","")))</f>
         <v/>
       </c>
-      <c r="P14" s="22" t="str">
+      <c r="P14" s="24" t="str">
         <f>IF(WBS!$C15="","",IF(AND(WBS!$E15&lt;&gt;"",P$4&gt;=WBS!$E15,P$4&lt;=WBS!$F15),"■",IF(AND(P$4&gt;=WBS!$C15,P$4&lt;=WBS!$D15),"□","")))</f>
         <v/>
       </c>
-      <c r="Q14" s="22" t="str">
+      <c r="Q14" s="24" t="str">
         <f>IF(WBS!$C15="","",IF(AND(WBS!$E15&lt;&gt;"",Q$4&gt;=WBS!$E15,Q$4&lt;=WBS!$F15),"■",IF(AND(Q$4&gt;=WBS!$C15,Q$4&lt;=WBS!$D15),"□","")))</f>
         <v/>
       </c>
-      <c r="R14" s="22" t="str">
+      <c r="R14" s="24" t="str">
         <f>IF(WBS!$C15="","",IF(AND(WBS!$E15&lt;&gt;"",R$4&gt;=WBS!$E15,R$4&lt;=WBS!$F15),"■",IF(AND(R$4&gt;=WBS!$C15,R$4&lt;=WBS!$D15),"□","")))</f>
         <v/>
       </c>
-      <c r="S14" s="22" t="str">
+      <c r="S14" s="24" t="str">
         <f>IF(WBS!$C15="","",IF(AND(WBS!$E15&lt;&gt;"",S$4&gt;=WBS!$E15,S$4&lt;=WBS!$F15),"■",IF(AND(S$4&gt;=WBS!$C15,S$4&lt;=WBS!$D15),"□","")))</f>
         <v/>
       </c>
-      <c r="T14" s="22" t="str">
+      <c r="T14" s="24" t="str">
         <f>IF(WBS!$C15="","",IF(AND(WBS!$E15&lt;&gt;"",T$4&gt;=WBS!$E15,T$4&lt;=WBS!$F15),"■",IF(AND(T$4&gt;=WBS!$C15,T$4&lt;=WBS!$D15),"□","")))</f>
         <v/>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A15" s="21" t="str">
+      <c r="A15" s="23" t="str">
         <f>WBS!A16</f>
         <v>3.3</v>
       </c>
-      <c r="B15" s="21" t="str">
+      <c r="B15" s="23" t="str">
         <f>WBS!B16</f>
         <v>Sinh dữ liệu mô phỏng 314 phiếu</v>
       </c>
-      <c r="C15" s="22" t="str">
+      <c r="C15" s="24" t="str">
         <f>IF(WBS!$C16="","",IF(AND(WBS!$E16&lt;&gt;"",C$4&gt;=WBS!$E16,C$4&lt;=WBS!$F16),"■",IF(AND(C$4&gt;=WBS!$C16,C$4&lt;=WBS!$D16),"□","")))</f>
         <v/>
       </c>
-      <c r="D15" s="22" t="str">
+      <c r="D15" s="24" t="str">
         <f>IF(WBS!$C16="","",IF(AND(WBS!$E16&lt;&gt;"",D$4&gt;=WBS!$E16,D$4&lt;=WBS!$F16),"■",IF(AND(D$4&gt;=WBS!$C16,D$4&lt;=WBS!$D16),"□","")))</f>
         <v/>
       </c>
-      <c r="E15" s="22" t="str">
+      <c r="E15" s="24" t="str">
         <f>IF(WBS!$C16="","",IF(AND(WBS!$E16&lt;&gt;"",E$4&gt;=WBS!$E16,E$4&lt;=WBS!$F16),"■",IF(AND(E$4&gt;=WBS!$C16,E$4&lt;=WBS!$D16),"□","")))</f>
         <v/>
       </c>
-      <c r="F15" s="22" t="str">
+      <c r="F15" s="24" t="str">
         <f>IF(WBS!$C16="","",IF(AND(WBS!$E16&lt;&gt;"",F$4&gt;=WBS!$E16,F$4&lt;=WBS!$F16),"■",IF(AND(F$4&gt;=WBS!$C16,F$4&lt;=WBS!$D16),"□","")))</f>
         <v/>
       </c>
-      <c r="G15" s="22" t="str">
+      <c r="G15" s="24" t="str">
         <f>IF(WBS!$C16="","",IF(AND(WBS!$E16&lt;&gt;"",G$4&gt;=WBS!$E16,G$4&lt;=WBS!$F16),"■",IF(AND(G$4&gt;=WBS!$C16,G$4&lt;=WBS!$D16),"□","")))</f>
         <v/>
       </c>
-      <c r="H15" s="22" t="str">
+      <c r="H15" s="24" t="str">
         <f>IF(WBS!$C16="","",IF(AND(WBS!$E16&lt;&gt;"",H$4&gt;=WBS!$E16,H$4&lt;=WBS!$F16),"■",IF(AND(H$4&gt;=WBS!$C16,H$4&lt;=WBS!$D16),"□","")))</f>
         <v/>
       </c>
-      <c r="I15" s="22" t="str">
+      <c r="I15" s="24" t="str">
         <f>IF(WBS!$C16="","",IF(AND(WBS!$E16&lt;&gt;"",I$4&gt;=WBS!$E16,I$4&lt;=WBS!$F16),"■",IF(AND(I$4&gt;=WBS!$C16,I$4&lt;=WBS!$D16),"□","")))</f>
         <v/>
       </c>
-      <c r="J15" s="22" t="str">
+      <c r="J15" s="24" t="str">
         <f>IF(WBS!$C16="","",IF(AND(WBS!$E16&lt;&gt;"",J$4&gt;=WBS!$E16,J$4&lt;=WBS!$F16),"■",IF(AND(J$4&gt;=WBS!$C16,J$4&lt;=WBS!$D16),"□","")))</f>
         <v/>
       </c>
-      <c r="K15" s="22" t="str">
+      <c r="K15" s="24" t="str">
         <f>IF(WBS!$C16="","",IF(AND(WBS!$E16&lt;&gt;"",K$4&gt;=WBS!$E16,K$4&lt;=WBS!$F16),"■",IF(AND(K$4&gt;=WBS!$C16,K$4&lt;=WBS!$D16),"□","")))</f>
         <v>■</v>
       </c>
-      <c r="L15" s="22" t="str">
+      <c r="L15" s="24" t="str">
         <f>IF(WBS!$C16="","",IF(AND(WBS!$E16&lt;&gt;"",L$4&gt;=WBS!$E16,L$4&lt;=WBS!$F16),"■",IF(AND(L$4&gt;=WBS!$C16,L$4&lt;=WBS!$D16),"□","")))</f>
         <v>□</v>
       </c>
-      <c r="M15" s="22" t="str">
+      <c r="M15" s="24" t="str">
         <f>IF(WBS!$C16="","",IF(AND(WBS!$E16&lt;&gt;"",M$4&gt;=WBS!$E16,M$4&lt;=WBS!$F16),"■",IF(AND(M$4&gt;=WBS!$C16,M$4&lt;=WBS!$D16),"□","")))</f>
         <v/>
       </c>
-      <c r="N15" s="22" t="str">
+      <c r="N15" s="24" t="str">
         <f>IF(WBS!$C16="","",IF(AND(WBS!$E16&lt;&gt;"",N$4&gt;=WBS!$E16,N$4&lt;=WBS!$F16),"■",IF(AND(N$4&gt;=WBS!$C16,N$4&lt;=WBS!$D16),"□","")))</f>
         <v/>
       </c>
-      <c r="O15" s="22" t="str">
+      <c r="O15" s="24" t="str">
         <f>IF(WBS!$C16="","",IF(AND(WBS!$E16&lt;&gt;"",O$4&gt;=WBS!$E16,O$4&lt;=WBS!$F16),"■",IF(AND(O$4&gt;=WBS!$C16,O$4&lt;=WBS!$D16),"□","")))</f>
         <v/>
       </c>
-      <c r="P15" s="22" t="str">
+      <c r="P15" s="24" t="str">
         <f>IF(WBS!$C16="","",IF(AND(WBS!$E16&lt;&gt;"",P$4&gt;=WBS!$E16,P$4&lt;=WBS!$F16),"■",IF(AND(P$4&gt;=WBS!$C16,P$4&lt;=WBS!$D16),"□","")))</f>
         <v/>
       </c>
-      <c r="Q15" s="22" t="str">
+      <c r="Q15" s="24" t="str">
         <f>IF(WBS!$C16="","",IF(AND(WBS!$E16&lt;&gt;"",Q$4&gt;=WBS!$E16,Q$4&lt;=WBS!$F16),"■",IF(AND(Q$4&gt;=WBS!$C16,Q$4&lt;=WBS!$D16),"□","")))</f>
         <v/>
       </c>
-      <c r="R15" s="22" t="str">
+      <c r="R15" s="24" t="str">
         <f>IF(WBS!$C16="","",IF(AND(WBS!$E16&lt;&gt;"",R$4&gt;=WBS!$E16,R$4&lt;=WBS!$F16),"■",IF(AND(R$4&gt;=WBS!$C16,R$4&lt;=WBS!$D16),"□","")))</f>
         <v/>
       </c>
-      <c r="S15" s="22" t="str">
+      <c r="S15" s="24" t="str">
         <f>IF(WBS!$C16="","",IF(AND(WBS!$E16&lt;&gt;"",S$4&gt;=WBS!$E16,S$4&lt;=WBS!$F16),"■",IF(AND(S$4&gt;=WBS!$C16,S$4&lt;=WBS!$D16),"□","")))</f>
         <v/>
       </c>
-      <c r="T15" s="22" t="str">
+      <c r="T15" s="24" t="str">
         <f>IF(WBS!$C16="","",IF(AND(WBS!$E16&lt;&gt;"",T$4&gt;=WBS!$E16,T$4&lt;=WBS!$F16),"■",IF(AND(T$4&gt;=WBS!$C16,T$4&lt;=WBS!$D16),"□","")))</f>
         <v/>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A16" s="21" t="str">
+      <c r="A16" s="23" t="str">
         <f>WBS!A17</f>
         <v>3.4</v>
       </c>
-      <c r="B16" s="21" t="str">
+      <c r="B16" s="23" t="str">
         <f>WBS!B17</f>
         <v>Cronbach, RII, PIM trên dữ liệu mô phỏng</v>
       </c>
-      <c r="C16" s="22" t="str">
+      <c r="C16" s="24" t="str">
         <f>IF(WBS!$C17="","",IF(AND(WBS!$E17&lt;&gt;"",C$4&gt;=WBS!$E17,C$4&lt;=WBS!$F17),"■",IF(AND(C$4&gt;=WBS!$C17,C$4&lt;=WBS!$D17),"□","")))</f>
         <v/>
       </c>
-      <c r="D16" s="22" t="str">
+      <c r="D16" s="24" t="str">
         <f>IF(WBS!$C17="","",IF(AND(WBS!$E17&lt;&gt;"",D$4&gt;=WBS!$E17,D$4&lt;=WBS!$F17),"■",IF(AND(D$4&gt;=WBS!$C17,D$4&lt;=WBS!$D17),"□","")))</f>
         <v/>
       </c>
-      <c r="E16" s="22" t="str">
+      <c r="E16" s="24" t="str">
         <f>IF(WBS!$C17="","",IF(AND(WBS!$E17&lt;&gt;"",E$4&gt;=WBS!$E17,E$4&lt;=WBS!$F17),"■",IF(AND(E$4&gt;=WBS!$C17,E$4&lt;=WBS!$D17),"□","")))</f>
         <v/>
       </c>
-      <c r="F16" s="22" t="str">
+      <c r="F16" s="24" t="str">
         <f>IF(WBS!$C17="","",IF(AND(WBS!$E17&lt;&gt;"",F$4&gt;=WBS!$E17,F$4&lt;=WBS!$F17),"■",IF(AND(F$4&gt;=WBS!$C17,F$4&lt;=WBS!$D17),"□","")))</f>
         <v/>
       </c>
-      <c r="G16" s="22" t="str">
+      <c r="G16" s="24" t="str">
         <f>IF(WBS!$C17="","",IF(AND(WBS!$E17&lt;&gt;"",G$4&gt;=WBS!$E17,G$4&lt;=WBS!$F17),"■",IF(AND(G$4&gt;=WBS!$C17,G$4&lt;=WBS!$D17),"□","")))</f>
         <v/>
       </c>
-      <c r="H16" s="22" t="str">
+      <c r="H16" s="24" t="str">
         <f>IF(WBS!$C17="","",IF(AND(WBS!$E17&lt;&gt;"",H$4&gt;=WBS!$E17,H$4&lt;=WBS!$F17),"■",IF(AND(H$4&gt;=WBS!$C17,H$4&lt;=WBS!$D17),"□","")))</f>
         <v/>
       </c>
-      <c r="I16" s="22" t="str">
+      <c r="I16" s="24" t="str">
         <f>IF(WBS!$C17="","",IF(AND(WBS!$E17&lt;&gt;"",I$4&gt;=WBS!$E17,I$4&lt;=WBS!$F17),"■",IF(AND(I$4&gt;=WBS!$C17,I$4&lt;=WBS!$D17),"□","")))</f>
         <v/>
       </c>
-      <c r="J16" s="22" t="str">
+      <c r="J16" s="24" t="str">
         <f>IF(WBS!$C17="","",IF(AND(WBS!$E17&lt;&gt;"",J$4&gt;=WBS!$E17,J$4&lt;=WBS!$F17),"■",IF(AND(J$4&gt;=WBS!$C17,J$4&lt;=WBS!$D17),"□","")))</f>
         <v/>
       </c>
-      <c r="K16" s="22" t="str">
+      <c r="K16" s="24" t="str">
         <f>IF(WBS!$C17="","",IF(AND(WBS!$E17&lt;&gt;"",K$4&gt;=WBS!$E17,K$4&lt;=WBS!$F17),"■",IF(AND(K$4&gt;=WBS!$C17,K$4&lt;=WBS!$D17),"□","")))</f>
         <v>■</v>
       </c>
-      <c r="L16" s="22" t="str">
+      <c r="L16" s="24" t="str">
         <f>IF(WBS!$C17="","",IF(AND(WBS!$E17&lt;&gt;"",L$4&gt;=WBS!$E17,L$4&lt;=WBS!$F17),"■",IF(AND(L$4&gt;=WBS!$C17,L$4&lt;=WBS!$D17),"□","")))</f>
         <v>□</v>
       </c>
-      <c r="M16" s="22" t="str">
+      <c r="M16" s="24" t="str">
         <f>IF(WBS!$C17="","",IF(AND(WBS!$E17&lt;&gt;"",M$4&gt;=WBS!$E17,M$4&lt;=WBS!$F17),"■",IF(AND(M$4&gt;=WBS!$C17,M$4&lt;=WBS!$D17),"□","")))</f>
         <v/>
       </c>
-      <c r="N16" s="22" t="str">
+      <c r="N16" s="24" t="str">
         <f>IF(WBS!$C17="","",IF(AND(WBS!$E17&lt;&gt;"",N$4&gt;=WBS!$E17,N$4&lt;=WBS!$F17),"■",IF(AND(N$4&gt;=WBS!$C17,N$4&lt;=WBS!$D17),"□","")))</f>
         <v/>
       </c>
-      <c r="O16" s="22" t="str">
+      <c r="O16" s="24" t="str">
         <f>IF(WBS!$C17="","",IF(AND(WBS!$E17&lt;&gt;"",O$4&gt;=WBS!$E17,O$4&lt;=WBS!$F17),"■",IF(AND(O$4&gt;=WBS!$C17,O$4&lt;=WBS!$D17),"□","")))</f>
         <v/>
       </c>
-      <c r="P16" s="22" t="str">
+      <c r="P16" s="24" t="str">
         <f>IF(WBS!$C17="","",IF(AND(WBS!$E17&lt;&gt;"",P$4&gt;=WBS!$E17,P$4&lt;=WBS!$F17),"■",IF(AND(P$4&gt;=WBS!$C17,P$4&lt;=WBS!$D17),"□","")))</f>
         <v/>
       </c>
-      <c r="Q16" s="22" t="str">
+      <c r="Q16" s="24" t="str">
         <f>IF(WBS!$C17="","",IF(AND(WBS!$E17&lt;&gt;"",Q$4&gt;=WBS!$E17,Q$4&lt;=WBS!$F17),"■",IF(AND(Q$4&gt;=WBS!$C17,Q$4&lt;=WBS!$D17),"□","")))</f>
         <v/>
       </c>
-      <c r="R16" s="22" t="str">
+      <c r="R16" s="24" t="str">
         <f>IF(WBS!$C17="","",IF(AND(WBS!$E17&lt;&gt;"",R$4&gt;=WBS!$E17,R$4&lt;=WBS!$F17),"■",IF(AND(R$4&gt;=WBS!$C17,R$4&lt;=WBS!$D17),"□","")))</f>
         <v/>
       </c>
-      <c r="S16" s="22" t="str">
+      <c r="S16" s="24" t="str">
         <f>IF(WBS!$C17="","",IF(AND(WBS!$E17&lt;&gt;"",S$4&gt;=WBS!$E17,S$4&lt;=WBS!$F17),"■",IF(AND(S$4&gt;=WBS!$C17,S$4&lt;=WBS!$D17),"□","")))</f>
         <v/>
       </c>
-      <c r="T16" s="22" t="str">
+      <c r="T16" s="24" t="str">
         <f>IF(WBS!$C17="","",IF(AND(WBS!$E17&lt;&gt;"",T$4&gt;=WBS!$E17,T$4&lt;=WBS!$F17),"■",IF(AND(T$4&gt;=WBS!$C17,T$4&lt;=WBS!$D17),"□","")))</f>
         <v/>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A17" s="21" t="str">
+      <c r="A17" s="23" t="str">
         <f>WBS!A18</f>
         <v>3.5</v>
       </c>
-      <c r="B17" s="21" t="str">
+      <c r="B17" s="23" t="str">
         <f>WBS!B18</f>
         <v>PLS-SEM, bootstrapping, HTMT</v>
       </c>
-      <c r="C17" s="22" t="str">
+      <c r="C17" s="24" t="str">
         <f>IF(WBS!$C18="","",IF(AND(WBS!$E18&lt;&gt;"",C$4&gt;=WBS!$E18,C$4&lt;=WBS!$F18),"■",IF(AND(C$4&gt;=WBS!$C18,C$4&lt;=WBS!$D18),"□","")))</f>
         <v/>
       </c>
-      <c r="D17" s="22" t="str">
+      <c r="D17" s="24" t="str">
         <f>IF(WBS!$C18="","",IF(AND(WBS!$E18&lt;&gt;"",D$4&gt;=WBS!$E18,D$4&lt;=WBS!$F18),"■",IF(AND(D$4&gt;=WBS!$C18,D$4&lt;=WBS!$D18),"□","")))</f>
         <v/>
       </c>
-      <c r="E17" s="22" t="str">
+      <c r="E17" s="24" t="str">
         <f>IF(WBS!$C18="","",IF(AND(WBS!$E18&lt;&gt;"",E$4&gt;=WBS!$E18,E$4&lt;=WBS!$F18),"■",IF(AND(E$4&gt;=WBS!$C18,E$4&lt;=WBS!$D18),"□","")))</f>
         <v/>
       </c>
-      <c r="F17" s="22" t="str">
+      <c r="F17" s="24" t="str">
         <f>IF(WBS!$C18="","",IF(AND(WBS!$E18&lt;&gt;"",F$4&gt;=WBS!$E18,F$4&lt;=WBS!$F18),"■",IF(AND(F$4&gt;=WBS!$C18,F$4&lt;=WBS!$D18),"□","")))</f>
         <v/>
       </c>
-      <c r="G17" s="22" t="str">
+      <c r="G17" s="24" t="str">
         <f>IF(WBS!$C18="","",IF(AND(WBS!$E18&lt;&gt;"",G$4&gt;=WBS!$E18,G$4&lt;=WBS!$F18),"■",IF(AND(G$4&gt;=WBS!$C18,G$4&lt;=WBS!$D18),"□","")))</f>
         <v/>
       </c>
-      <c r="H17" s="22" t="str">
+      <c r="H17" s="24" t="str">
         <f>IF(WBS!$C18="","",IF(AND(WBS!$E18&lt;&gt;"",H$4&gt;=WBS!$E18,H$4&lt;=WBS!$F18),"■",IF(AND(H$4&gt;=WBS!$C18,H$4&lt;=WBS!$D18),"□","")))</f>
         <v/>
       </c>
-      <c r="I17" s="22" t="str">
+      <c r="I17" s="24" t="str">
         <f>IF(WBS!$C18="","",IF(AND(WBS!$E18&lt;&gt;"",I$4&gt;=WBS!$E18,I$4&lt;=WBS!$F18),"■",IF(AND(I$4&gt;=WBS!$C18,I$4&lt;=WBS!$D18),"□","")))</f>
         <v/>
       </c>
-      <c r="J17" s="22" t="str">
+      <c r="J17" s="24" t="str">
         <f>IF(WBS!$C18="","",IF(AND(WBS!$E18&lt;&gt;"",J$4&gt;=WBS!$E18,J$4&lt;=WBS!$F18),"■",IF(AND(J$4&gt;=WBS!$C18,J$4&lt;=WBS!$D18),"□","")))</f>
         <v/>
       </c>
-      <c r="K17" s="22" t="str">
+      <c r="K17" s="24" t="str">
         <f>IF(WBS!$C18="","",IF(AND(WBS!$E18&lt;&gt;"",K$4&gt;=WBS!$E18,K$4&lt;=WBS!$F18),"■",IF(AND(K$4&gt;=WBS!$C18,K$4&lt;=WBS!$D18),"□","")))</f>
         <v>■</v>
       </c>
-      <c r="L17" s="22" t="str">
+      <c r="L17" s="24" t="str">
         <f>IF(WBS!$C18="","",IF(AND(WBS!$E18&lt;&gt;"",L$4&gt;=WBS!$E18,L$4&lt;=WBS!$F18),"■",IF(AND(L$4&gt;=WBS!$C18,L$4&lt;=WBS!$D18),"□","")))</f>
         <v/>
       </c>
-      <c r="M17" s="22" t="str">
+      <c r="M17" s="24" t="str">
         <f>IF(WBS!$C18="","",IF(AND(WBS!$E18&lt;&gt;"",M$4&gt;=WBS!$E18,M$4&lt;=WBS!$F18),"■",IF(AND(M$4&gt;=WBS!$C18,M$4&lt;=WBS!$D18),"□","")))</f>
         <v>□</v>
       </c>
-      <c r="N17" s="22" t="str">
+      <c r="N17" s="24" t="str">
         <f>IF(WBS!$C18="","",IF(AND(WBS!$E18&lt;&gt;"",N$4&gt;=WBS!$E18,N$4&lt;=WBS!$F18),"■",IF(AND(N$4&gt;=WBS!$C18,N$4&lt;=WBS!$D18),"□","")))</f>
         <v/>
       </c>
-      <c r="O17" s="22" t="str">
+      <c r="O17" s="24" t="str">
         <f>IF(WBS!$C18="","",IF(AND(WBS!$E18&lt;&gt;"",O$4&gt;=WBS!$E18,O$4&lt;=WBS!$F18),"■",IF(AND(O$4&gt;=WBS!$C18,O$4&lt;=WBS!$D18),"□","")))</f>
         <v/>
       </c>
-      <c r="P17" s="22" t="str">
+      <c r="P17" s="24" t="str">
         <f>IF(WBS!$C18="","",IF(AND(WBS!$E18&lt;&gt;"",P$4&gt;=WBS!$E18,P$4&lt;=WBS!$F18),"■",IF(AND(P$4&gt;=WBS!$C18,P$4&lt;=WBS!$D18),"□","")))</f>
         <v/>
       </c>
-      <c r="Q17" s="22" t="str">
+      <c r="Q17" s="24" t="str">
         <f>IF(WBS!$C18="","",IF(AND(WBS!$E18&lt;&gt;"",Q$4&gt;=WBS!$E18,Q$4&lt;=WBS!$F18),"■",IF(AND(Q$4&gt;=WBS!$C18,Q$4&lt;=WBS!$D18),"□","")))</f>
         <v/>
       </c>
-      <c r="R17" s="22" t="str">
+      <c r="R17" s="24" t="str">
         <f>IF(WBS!$C18="","",IF(AND(WBS!$E18&lt;&gt;"",R$4&gt;=WBS!$E18,R$4&lt;=WBS!$F18),"■",IF(AND(R$4&gt;=WBS!$C18,R$4&lt;=WBS!$D18),"□","")))</f>
         <v/>
       </c>
-      <c r="S17" s="22" t="str">
+      <c r="S17" s="24" t="str">
         <f>IF(WBS!$C18="","",IF(AND(WBS!$E18&lt;&gt;"",S$4&gt;=WBS!$E18,S$4&lt;=WBS!$F18),"■",IF(AND(S$4&gt;=WBS!$C18,S$4&lt;=WBS!$D18),"□","")))</f>
         <v/>
       </c>
-      <c r="T17" s="22" t="str">
+      <c r="T17" s="24" t="str">
         <f>IF(WBS!$C18="","",IF(AND(WBS!$E18&lt;&gt;"",T$4&gt;=WBS!$E18,T$4&lt;=WBS!$F18),"■",IF(AND(T$4&gt;=WBS!$C18,T$4&lt;=WBS!$D18),"□","")))</f>
         <v/>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A18" s="21" t="str">
+      <c r="A18" s="23" t="str">
         <f>WBS!A19</f>
         <v>4</v>
       </c>
-      <c r="B18" s="21" t="str">
+      <c r="B18" s="23" t="str">
         <f>WBS!B19</f>
         <v>Viết báo cáo</v>
       </c>
-      <c r="C18" s="22" t="str">
+      <c r="C18" s="24" t="str">
         <f>IF(WBS!$C19="","",IF(AND(WBS!$E19&lt;&gt;"",C$4&gt;=WBS!$E19,C$4&lt;=WBS!$F19),"■",IF(AND(C$4&gt;=WBS!$C19,C$4&lt;=WBS!$D19),"□","")))</f>
         <v/>
       </c>
-      <c r="D18" s="22" t="str">
+      <c r="D18" s="24" t="str">
         <f>IF(WBS!$C19="","",IF(AND(WBS!$E19&lt;&gt;"",D$4&gt;=WBS!$E19,D$4&lt;=WBS!$F19),"■",IF(AND(D$4&gt;=WBS!$C19,D$4&lt;=WBS!$D19),"□","")))</f>
         <v/>
       </c>
-      <c r="E18" s="22" t="str">
+      <c r="E18" s="24" t="str">
         <f>IF(WBS!$C19="","",IF(AND(WBS!$E19&lt;&gt;"",E$4&gt;=WBS!$E19,E$4&lt;=WBS!$F19),"■",IF(AND(E$4&gt;=WBS!$C19,E$4&lt;=WBS!$D19),"□","")))</f>
         <v/>
       </c>
-      <c r="F18" s="22" t="str">
+      <c r="F18" s="24" t="str">
         <f>IF(WBS!$C19="","",IF(AND(WBS!$E19&lt;&gt;"",F$4&gt;=WBS!$E19,F$4&lt;=WBS!$F19),"■",IF(AND(F$4&gt;=WBS!$C19,F$4&lt;=WBS!$D19),"□","")))</f>
         <v/>
       </c>
-      <c r="G18" s="22" t="str">
+      <c r="G18" s="24" t="str">
         <f>IF(WBS!$C19="","",IF(AND(WBS!$E19&lt;&gt;"",G$4&gt;=WBS!$E19,G$4&lt;=WBS!$F19),"■",IF(AND(G$4&gt;=WBS!$C19,G$4&lt;=WBS!$D19),"□","")))</f>
         <v>□</v>
       </c>
-      <c r="H18" s="22" t="str">
+      <c r="H18" s="24" t="str">
         <f>IF(WBS!$C19="","",IF(AND(WBS!$E19&lt;&gt;"",H$4&gt;=WBS!$E19,H$4&lt;=WBS!$F19),"■",IF(AND(H$4&gt;=WBS!$C19,H$4&lt;=WBS!$D19),"□","")))</f>
         <v>□</v>
       </c>
-      <c r="I18" s="22" t="str">
+      <c r="I18" s="24" t="str">
         <f>IF(WBS!$C19="","",IF(AND(WBS!$E19&lt;&gt;"",I$4&gt;=WBS!$E19,I$4&lt;=WBS!$F19),"■",IF(AND(I$4&gt;=WBS!$C19,I$4&lt;=WBS!$D19),"□","")))</f>
         <v>□</v>
       </c>
-      <c r="J18" s="22" t="str">
+      <c r="J18" s="24" t="str">
         <f>IF(WBS!$C19="","",IF(AND(WBS!$E19&lt;&gt;"",J$4&gt;=WBS!$E19,J$4&lt;=WBS!$F19),"■",IF(AND(J$4&gt;=WBS!$C19,J$4&lt;=WBS!$D19),"□","")))</f>
         <v>□</v>
       </c>
-      <c r="K18" s="22" t="str">
+      <c r="K18" s="24" t="str">
         <f>IF(WBS!$C19="","",IF(AND(WBS!$E19&lt;&gt;"",K$4&gt;=WBS!$E19,K$4&lt;=WBS!$F19),"■",IF(AND(K$4&gt;=WBS!$C19,K$4&lt;=WBS!$D19),"□","")))</f>
         <v>□</v>
       </c>
-      <c r="L18" s="22" t="str">
+      <c r="L18" s="24" t="str">
         <f>IF(WBS!$C19="","",IF(AND(WBS!$E19&lt;&gt;"",L$4&gt;=WBS!$E19,L$4&lt;=WBS!$F19),"■",IF(AND(L$4&gt;=WBS!$C19,L$4&lt;=WBS!$D19),"□","")))</f>
         <v>□</v>
       </c>
-      <c r="M18" s="22" t="str">
+      <c r="M18" s="24" t="str">
         <f>IF(WBS!$C19="","",IF(AND(WBS!$E19&lt;&gt;"",M$4&gt;=WBS!$E19,M$4&lt;=WBS!$F19),"■",IF(AND(M$4&gt;=WBS!$C19,M$4&lt;=WBS!$D19),"□","")))</f>
         <v>□</v>
       </c>
-      <c r="N18" s="22" t="str">
+      <c r="N18" s="24" t="str">
         <f>IF(WBS!$C19="","",IF(AND(WBS!$E19&lt;&gt;"",N$4&gt;=WBS!$E19,N$4&lt;=WBS!$F19),"■",IF(AND(N$4&gt;=WBS!$C19,N$4&lt;=WBS!$D19),"□","")))</f>
         <v>□</v>
       </c>
-      <c r="O18" s="22" t="str">
+      <c r="O18" s="24" t="str">
         <f>IF(WBS!$C19="","",IF(AND(WBS!$E19&lt;&gt;"",O$4&gt;=WBS!$E19,O$4&lt;=WBS!$F19),"■",IF(AND(O$4&gt;=WBS!$C19,O$4&lt;=WBS!$D19),"□","")))</f>
         <v>□</v>
       </c>
-      <c r="P18" s="22" t="str">
+      <c r="P18" s="24" t="str">
         <f>IF(WBS!$C19="","",IF(AND(WBS!$E19&lt;&gt;"",P$4&gt;=WBS!$E19,P$4&lt;=WBS!$F19),"■",IF(AND(P$4&gt;=WBS!$C19,P$4&lt;=WBS!$D19),"□","")))</f>
         <v>□</v>
       </c>
-      <c r="Q18" s="22" t="str">
+      <c r="Q18" s="24" t="str">
         <f>IF(WBS!$C19="","",IF(AND(WBS!$E19&lt;&gt;"",Q$4&gt;=WBS!$E19,Q$4&lt;=WBS!$F19),"■",IF(AND(Q$4&gt;=WBS!$C19,Q$4&lt;=WBS!$D19),"□","")))</f>
         <v>□</v>
       </c>
-      <c r="R18" s="22" t="str">
+      <c r="R18" s="24" t="str">
         <f>IF(WBS!$C19="","",IF(AND(WBS!$E19&lt;&gt;"",R$4&gt;=WBS!$E19,R$4&lt;=WBS!$F19),"■",IF(AND(R$4&gt;=WBS!$C19,R$4&lt;=WBS!$D19),"□","")))</f>
         <v>□</v>
       </c>
-      <c r="S18" s="22" t="str">
+      <c r="S18" s="24" t="str">
         <f>IF(WBS!$C19="","",IF(AND(WBS!$E19&lt;&gt;"",S$4&gt;=WBS!$E19,S$4&lt;=WBS!$F19),"■",IF(AND(S$4&gt;=WBS!$C19,S$4&lt;=WBS!$D19),"□","")))</f>
         <v/>
       </c>
-      <c r="T18" s="22" t="str">
+      <c r="T18" s="24" t="str">
         <f>IF(WBS!$C19="","",IF(AND(WBS!$E19&lt;&gt;"",T$4&gt;=WBS!$E19,T$4&lt;=WBS!$F19),"■",IF(AND(T$4&gt;=WBS!$C19,T$4&lt;=WBS!$D19),"□","")))</f>
         <v/>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A19" s="21" t="str">
+      <c r="A19" s="23" t="str">
         <f>WBS!A20</f>
         <v>4.1</v>
       </c>
-      <c r="B19" s="21" t="str">
+      <c r="B19" s="23" t="str">
         <f>WBS!B20</f>
         <v>Dựng khung LaTeX theo mẫu KLTN</v>
       </c>
-      <c r="C19" s="22" t="str">
+      <c r="C19" s="24" t="str">
         <f>IF(WBS!$C20="","",IF(AND(WBS!$E20&lt;&gt;"",C$4&gt;=WBS!$E20,C$4&lt;=WBS!$F20),"■",IF(AND(C$4&gt;=WBS!$C20,C$4&lt;=WBS!$D20),"□","")))</f>
         <v/>
       </c>
-      <c r="D19" s="22" t="str">
+      <c r="D19" s="24" t="str">
         <f>IF(WBS!$C20="","",IF(AND(WBS!$E20&lt;&gt;"",D$4&gt;=WBS!$E20,D$4&lt;=WBS!$F20),"■",IF(AND(D$4&gt;=WBS!$C20,D$4&lt;=WBS!$D20),"□","")))</f>
         <v/>
       </c>
-      <c r="E19" s="22" t="str">
+      <c r="E19" s="24" t="str">
         <f>IF(WBS!$C20="","",IF(AND(WBS!$E20&lt;&gt;"",E$4&gt;=WBS!$E20,E$4&lt;=WBS!$F20),"■",IF(AND(E$4&gt;=WBS!$C20,E$4&lt;=WBS!$D20),"□","")))</f>
         <v/>
       </c>
-      <c r="F19" s="22" t="str">
+      <c r="F19" s="24" t="str">
         <f>IF(WBS!$C20="","",IF(AND(WBS!$E20&lt;&gt;"",F$4&gt;=WBS!$E20,F$4&lt;=WBS!$F20),"■",IF(AND(F$4&gt;=WBS!$C20,F$4&lt;=WBS!$D20),"□","")))</f>
         <v/>
       </c>
-      <c r="G19" s="22" t="str">
+      <c r="G19" s="24" t="str">
         <f>IF(WBS!$C20="","",IF(AND(WBS!$E20&lt;&gt;"",G$4&gt;=WBS!$E20,G$4&lt;=WBS!$F20),"■",IF(AND(G$4&gt;=WBS!$C20,G$4&lt;=WBS!$D20),"□","")))</f>
         <v>□</v>
       </c>
-      <c r="H19" s="22" t="str">
+      <c r="H19" s="24" t="str">
         <f>IF(WBS!$C20="","",IF(AND(WBS!$E20&lt;&gt;"",H$4&gt;=WBS!$E20,H$4&lt;=WBS!$F20),"■",IF(AND(H$4&gt;=WBS!$C20,H$4&lt;=WBS!$D20),"□","")))</f>
         <v/>
       </c>
-      <c r="I19" s="22" t="str">
+      <c r="I19" s="24" t="str">
         <f>IF(WBS!$C20="","",IF(AND(WBS!$E20&lt;&gt;"",I$4&gt;=WBS!$E20,I$4&lt;=WBS!$F20),"■",IF(AND(I$4&gt;=WBS!$C20,I$4&lt;=WBS!$D20),"□","")))</f>
         <v/>
       </c>
-      <c r="J19" s="22" t="str">
+      <c r="J19" s="24" t="str">
         <f>IF(WBS!$C20="","",IF(AND(WBS!$E20&lt;&gt;"",J$4&gt;=WBS!$E20,J$4&lt;=WBS!$F20),"■",IF(AND(J$4&gt;=WBS!$C20,J$4&lt;=WBS!$D20),"□","")))</f>
         <v/>
       </c>
-      <c r="K19" s="22" t="str">
+      <c r="K19" s="24" t="str">
         <f>IF(WBS!$C20="","",IF(AND(WBS!$E20&lt;&gt;"",K$4&gt;=WBS!$E20,K$4&lt;=WBS!$F20),"■",IF(AND(K$4&gt;=WBS!$C20,K$4&lt;=WBS!$D20),"□","")))</f>
         <v>■</v>
       </c>
-      <c r="L19" s="22" t="str">
+      <c r="L19" s="24" t="str">
         <f>IF(WBS!$C20="","",IF(AND(WBS!$E20&lt;&gt;"",L$4&gt;=WBS!$E20,L$4&lt;=WBS!$F20),"■",IF(AND(L$4&gt;=WBS!$C20,L$4&lt;=WBS!$D20),"□","")))</f>
         <v/>
       </c>
-      <c r="M19" s="22" t="str">
+      <c r="M19" s="24" t="str">
         <f>IF(WBS!$C20="","",IF(AND(WBS!$E20&lt;&gt;"",M$4&gt;=WBS!$E20,M$4&lt;=WBS!$F20),"■",IF(AND(M$4&gt;=WBS!$C20,M$4&lt;=WBS!$D20),"□","")))</f>
         <v/>
       </c>
-      <c r="N19" s="22" t="str">
+      <c r="N19" s="24" t="str">
         <f>IF(WBS!$C20="","",IF(AND(WBS!$E20&lt;&gt;"",N$4&gt;=WBS!$E20,N$4&lt;=WBS!$F20),"■",IF(AND(N$4&gt;=WBS!$C20,N$4&lt;=WBS!$D20),"□","")))</f>
         <v/>
       </c>
-      <c r="O19" s="22" t="str">
+      <c r="O19" s="24" t="str">
         <f>IF(WBS!$C20="","",IF(AND(WBS!$E20&lt;&gt;"",O$4&gt;=WBS!$E20,O$4&lt;=WBS!$F20),"■",IF(AND(O$4&gt;=WBS!$C20,O$4&lt;=WBS!$D20),"□","")))</f>
         <v/>
       </c>
-      <c r="P19" s="22" t="str">
+      <c r="P19" s="24" t="str">
         <f>IF(WBS!$C20="","",IF(AND(WBS!$E20&lt;&gt;"",P$4&gt;=WBS!$E20,P$4&lt;=WBS!$F20),"■",IF(AND(P$4&gt;=WBS!$C20,P$4&lt;=WBS!$D20),"□","")))</f>
         <v/>
       </c>
-      <c r="Q19" s="22" t="str">
+      <c r="Q19" s="24" t="str">
         <f>IF(WBS!$C20="","",IF(AND(WBS!$E20&lt;&gt;"",Q$4&gt;=WBS!$E20,Q$4&lt;=WBS!$F20),"■",IF(AND(Q$4&gt;=WBS!$C20,Q$4&lt;=WBS!$D20),"□","")))</f>
         <v/>
       </c>
-      <c r="R19" s="22" t="str">
+      <c r="R19" s="24" t="str">
         <f>IF(WBS!$C20="","",IF(AND(WBS!$E20&lt;&gt;"",R$4&gt;=WBS!$E20,R$4&lt;=WBS!$F20),"■",IF(AND(R$4&gt;=WBS!$C20,R$4&lt;=WBS!$D20),"□","")))</f>
         <v/>
       </c>
-      <c r="S19" s="22" t="str">
+      <c r="S19" s="24" t="str">
         <f>IF(WBS!$C20="","",IF(AND(WBS!$E20&lt;&gt;"",S$4&gt;=WBS!$E20,S$4&lt;=WBS!$F20),"■",IF(AND(S$4&gt;=WBS!$C20,S$4&lt;=WBS!$D20),"□","")))</f>
         <v/>
       </c>
-      <c r="T19" s="22" t="str">
+      <c r="T19" s="24" t="str">
         <f>IF(WBS!$C20="","",IF(AND(WBS!$E20&lt;&gt;"",T$4&gt;=WBS!$E20,T$4&lt;=WBS!$F20),"■",IF(AND(T$4&gt;=WBS!$C20,T$4&lt;=WBS!$D20),"□","")))</f>
         <v/>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A20" s="21" t="str">
+      <c r="A20" s="23" t="str">
         <f>WBS!A21</f>
         <v>4.2</v>
       </c>
-      <c r="B20" s="21" t="str">
+      <c r="B20" s="23" t="str">
         <f>WBS!B21</f>
         <v>Viết Chương 1 – Tổng quan</v>
       </c>
-      <c r="C20" s="22" t="str">
+      <c r="C20" s="24" t="str">
         <f>IF(WBS!$C21="","",IF(AND(WBS!$E21&lt;&gt;"",C$4&gt;=WBS!$E21,C$4&lt;=WBS!$F21),"■",IF(AND(C$4&gt;=WBS!$C21,C$4&lt;=WBS!$D21),"□","")))</f>
         <v/>
       </c>
-      <c r="D20" s="22" t="str">
+      <c r="D20" s="24" t="str">
         <f>IF(WBS!$C21="","",IF(AND(WBS!$E21&lt;&gt;"",D$4&gt;=WBS!$E21,D$4&lt;=WBS!$F21),"■",IF(AND(D$4&gt;=WBS!$C21,D$4&lt;=WBS!$D21),"□","")))</f>
         <v/>
       </c>
-      <c r="E20" s="22" t="str">
+      <c r="E20" s="24" t="str">
         <f>IF(WBS!$C21="","",IF(AND(WBS!$E21&lt;&gt;"",E$4&gt;=WBS!$E21,E$4&lt;=WBS!$F21),"■",IF(AND(E$4&gt;=WBS!$C21,E$4&lt;=WBS!$D21),"□","")))</f>
         <v/>
       </c>
-      <c r="F20" s="22" t="str">
+      <c r="F20" s="24" t="str">
         <f>IF(WBS!$C21="","",IF(AND(WBS!$E21&lt;&gt;"",F$4&gt;=WBS!$E21,F$4&lt;=WBS!$F21),"■",IF(AND(F$4&gt;=WBS!$C21,F$4&lt;=WBS!$D21),"□","")))</f>
         <v/>
       </c>
-      <c r="G20" s="22" t="str">
+      <c r="G20" s="24" t="str">
         <f>IF(WBS!$C21="","",IF(AND(WBS!$E21&lt;&gt;"",G$4&gt;=WBS!$E21,G$4&lt;=WBS!$F21),"■",IF(AND(G$4&gt;=WBS!$C21,G$4&lt;=WBS!$D21),"□","")))</f>
         <v/>
       </c>
-      <c r="H20" s="22" t="str">
+      <c r="H20" s="24" t="str">
         <f>IF(WBS!$C21="","",IF(AND(WBS!$E21&lt;&gt;"",H$4&gt;=WBS!$E21,H$4&lt;=WBS!$F21),"■",IF(AND(H$4&gt;=WBS!$C21,H$4&lt;=WBS!$D21),"□","")))</f>
         <v/>
       </c>
-      <c r="I20" s="22" t="str">
+      <c r="I20" s="24" t="str">
         <f>IF(WBS!$C21="","",IF(AND(WBS!$E21&lt;&gt;"",I$4&gt;=WBS!$E21,I$4&lt;=WBS!$F21),"■",IF(AND(I$4&gt;=WBS!$C21,I$4&lt;=WBS!$D21),"□","")))</f>
         <v>□</v>
       </c>
-      <c r="J20" s="22" t="str">
+      <c r="J20" s="24" t="str">
         <f>IF(WBS!$C21="","",IF(AND(WBS!$E21&lt;&gt;"",J$4&gt;=WBS!$E21,J$4&lt;=WBS!$F21),"■",IF(AND(J$4&gt;=WBS!$C21,J$4&lt;=WBS!$D21),"□","")))</f>
         <v/>
       </c>
-      <c r="K20" s="22" t="str">
+      <c r="K20" s="24" t="str">
         <f>IF(WBS!$C21="","",IF(AND(WBS!$E21&lt;&gt;"",K$4&gt;=WBS!$E21,K$4&lt;=WBS!$F21),"■",IF(AND(K$4&gt;=WBS!$C21,K$4&lt;=WBS!$D21),"□","")))</f>
         <v>■</v>
       </c>
-      <c r="L20" s="22" t="str">
+      <c r="L20" s="24" t="str">
         <f>IF(WBS!$C21="","",IF(AND(WBS!$E21&lt;&gt;"",L$4&gt;=WBS!$E21,L$4&lt;=WBS!$F21),"■",IF(AND(L$4&gt;=WBS!$C21,L$4&lt;=WBS!$D21),"□","")))</f>
         <v/>
       </c>
-      <c r="M20" s="22" t="str">
+      <c r="M20" s="24" t="str">
         <f>IF(WBS!$C21="","",IF(AND(WBS!$E21&lt;&gt;"",M$4&gt;=WBS!$E21,M$4&lt;=WBS!$F21),"■",IF(AND(M$4&gt;=WBS!$C21,M$4&lt;=WBS!$D21),"□","")))</f>
         <v/>
       </c>
-      <c r="N20" s="22" t="str">
+      <c r="N20" s="24" t="str">
         <f>IF(WBS!$C21="","",IF(AND(WBS!$E21&lt;&gt;"",N$4&gt;=WBS!$E21,N$4&lt;=WBS!$F21),"■",IF(AND(N$4&gt;=WBS!$C21,N$4&lt;=WBS!$D21),"□","")))</f>
         <v/>
       </c>
-      <c r="O20" s="22" t="str">
+      <c r="O20" s="24" t="str">
         <f>IF(WBS!$C21="","",IF(AND(WBS!$E21&lt;&gt;"",O$4&gt;=WBS!$E21,O$4&lt;=WBS!$F21),"■",IF(AND(O$4&gt;=WBS!$C21,O$4&lt;=WBS!$D21),"□","")))</f>
         <v/>
       </c>
-      <c r="P20" s="22" t="str">
+      <c r="P20" s="24" t="str">
         <f>IF(WBS!$C21="","",IF(AND(WBS!$E21&lt;&gt;"",P$4&gt;=WBS!$E21,P$4&lt;=WBS!$F21),"■",IF(AND(P$4&gt;=WBS!$C21,P$4&lt;=WBS!$D21),"□","")))</f>
         <v/>
       </c>
-      <c r="Q20" s="22" t="str">
+      <c r="Q20" s="24" t="str">
         <f>IF(WBS!$C21="","",IF(AND(WBS!$E21&lt;&gt;"",Q$4&gt;=WBS!$E21,Q$4&lt;=WBS!$F21),"■",IF(AND(Q$4&gt;=WBS!$C21,Q$4&lt;=WBS!$D21),"□","")))</f>
         <v/>
       </c>
-      <c r="R20" s="22" t="str">
+      <c r="R20" s="24" t="str">
         <f>IF(WBS!$C21="","",IF(AND(WBS!$E21&lt;&gt;"",R$4&gt;=WBS!$E21,R$4&lt;=WBS!$F21),"■",IF(AND(R$4&gt;=WBS!$C21,R$4&lt;=WBS!$D21),"□","")))</f>
         <v/>
       </c>
-      <c r="S20" s="22" t="str">
+      <c r="S20" s="24" t="str">
         <f>IF(WBS!$C21="","",IF(AND(WBS!$E21&lt;&gt;"",S$4&gt;=WBS!$E21,S$4&lt;=WBS!$F21),"■",IF(AND(S$4&gt;=WBS!$C21,S$4&lt;=WBS!$D21),"□","")))</f>
         <v/>
       </c>
-      <c r="T20" s="22" t="str">
+      <c r="T20" s="24" t="str">
         <f>IF(WBS!$C21="","",IF(AND(WBS!$E21&lt;&gt;"",T$4&gt;=WBS!$E21,T$4&lt;=WBS!$F21),"■",IF(AND(T$4&gt;=WBS!$C21,T$4&lt;=WBS!$D21),"□","")))</f>
         <v/>
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A21" s="21" t="str">
+      <c r="A21" s="23" t="str">
         <f>WBS!A22</f>
         <v>4.3</v>
       </c>
-      <c r="B21" s="21" t="str">
+      <c r="B21" s="23" t="str">
         <f>WBS!B22</f>
         <v>Vẽ sơ đồ tư duy và sơ đồ mô hình</v>
       </c>
-      <c r="C21" s="22" t="str">
+      <c r="C21" s="24" t="str">
         <f>IF(WBS!$C22="","",IF(AND(WBS!$E22&lt;&gt;"",C$4&gt;=WBS!$E22,C$4&lt;=WBS!$F22),"■",IF(AND(C$4&gt;=WBS!$C22,C$4&lt;=WBS!$D22),"□","")))</f>
         <v/>
       </c>
-      <c r="D21" s="22" t="str">
+      <c r="D21" s="24" t="str">
         <f>IF(WBS!$C22="","",IF(AND(WBS!$E22&lt;&gt;"",D$4&gt;=WBS!$E22,D$4&lt;=WBS!$F22),"■",IF(AND(D$4&gt;=WBS!$C22,D$4&lt;=WBS!$D22),"□","")))</f>
         <v/>
       </c>
-      <c r="E21" s="22" t="str">
+      <c r="E21" s="24" t="str">
         <f>IF(WBS!$C22="","",IF(AND(WBS!$E22&lt;&gt;"",E$4&gt;=WBS!$E22,E$4&lt;=WBS!$F22),"■",IF(AND(E$4&gt;=WBS!$C22,E$4&lt;=WBS!$D22),"□","")))</f>
         <v/>
       </c>
-      <c r="F21" s="22" t="str">
+      <c r="F21" s="24" t="str">
         <f>IF(WBS!$C22="","",IF(AND(WBS!$E22&lt;&gt;"",F$4&gt;=WBS!$E22,F$4&lt;=WBS!$F22),"■",IF(AND(F$4&gt;=WBS!$C22,F$4&lt;=WBS!$D22),"□","")))</f>
         <v/>
       </c>
-      <c r="G21" s="22" t="str">
+      <c r="G21" s="24" t="str">
         <f>IF(WBS!$C22="","",IF(AND(WBS!$E22&lt;&gt;"",G$4&gt;=WBS!$E22,G$4&lt;=WBS!$F22),"■",IF(AND(G$4&gt;=WBS!$C22,G$4&lt;=WBS!$D22),"□","")))</f>
         <v/>
       </c>
-      <c r="H21" s="22" t="str">
+      <c r="H21" s="24" t="str">
         <f>IF(WBS!$C22="","",IF(AND(WBS!$E22&lt;&gt;"",H$4&gt;=WBS!$E22,H$4&lt;=WBS!$F22),"■",IF(AND(H$4&gt;=WBS!$C22,H$4&lt;=WBS!$D22),"□","")))</f>
         <v/>
       </c>
-      <c r="I21" s="22" t="str">
+      <c r="I21" s="24" t="str">
         <f>IF(WBS!$C22="","",IF(AND(WBS!$E22&lt;&gt;"",I$4&gt;=WBS!$E22,I$4&lt;=WBS!$F22),"■",IF(AND(I$4&gt;=WBS!$C22,I$4&lt;=WBS!$D22),"□","")))</f>
         <v/>
       </c>
-      <c r="J21" s="22" t="str">
+      <c r="J21" s="24" t="str">
         <f>IF(WBS!$C22="","",IF(AND(WBS!$E22&lt;&gt;"",J$4&gt;=WBS!$E22,J$4&lt;=WBS!$F22),"■",IF(AND(J$4&gt;=WBS!$C22,J$4&lt;=WBS!$D22),"□","")))</f>
         <v>□</v>
       </c>
-      <c r="K21" s="22" t="str">
+      <c r="K21" s="24" t="str">
         <f>IF(WBS!$C22="","",IF(AND(WBS!$E22&lt;&gt;"",K$4&gt;=WBS!$E22,K$4&lt;=WBS!$F22),"■",IF(AND(K$4&gt;=WBS!$C22,K$4&lt;=WBS!$D22),"□","")))</f>
         <v>■</v>
       </c>
-      <c r="L21" s="22" t="str">
+      <c r="L21" s="24" t="str">
         <f>IF(WBS!$C22="","",IF(AND(WBS!$E22&lt;&gt;"",L$4&gt;=WBS!$E22,L$4&lt;=WBS!$F22),"■",IF(AND(L$4&gt;=WBS!$C22,L$4&lt;=WBS!$D22),"□","")))</f>
         <v/>
       </c>
-      <c r="M21" s="22" t="str">
+      <c r="M21" s="24" t="str">
         <f>IF(WBS!$C22="","",IF(AND(WBS!$E22&lt;&gt;"",M$4&gt;=WBS!$E22,M$4&lt;=WBS!$F22),"■",IF(AND(M$4&gt;=WBS!$C22,M$4&lt;=WBS!$D22),"□","")))</f>
         <v/>
       </c>
-      <c r="N21" s="22" t="str">
+      <c r="N21" s="24" t="str">
         <f>IF(WBS!$C22="","",IF(AND(WBS!$E22&lt;&gt;"",N$4&gt;=WBS!$E22,N$4&lt;=WBS!$F22),"■",IF(AND(N$4&gt;=WBS!$C22,N$4&lt;=WBS!$D22),"□","")))</f>
         <v/>
       </c>
-      <c r="O21" s="22" t="str">
+      <c r="O21" s="24" t="str">
         <f>IF(WBS!$C22="","",IF(AND(WBS!$E22&lt;&gt;"",O$4&gt;=WBS!$E22,O$4&lt;=WBS!$F22),"■",IF(AND(O$4&gt;=WBS!$C22,O$4&lt;=WBS!$D22),"□","")))</f>
         <v/>
       </c>
-      <c r="P21" s="22" t="str">
+      <c r="P21" s="24" t="str">
         <f>IF(WBS!$C22="","",IF(AND(WBS!$E22&lt;&gt;"",P$4&gt;=WBS!$E22,P$4&lt;=WBS!$F22),"■",IF(AND(P$4&gt;=WBS!$C22,P$4&lt;=WBS!$D22),"□","")))</f>
         <v/>
       </c>
-      <c r="Q21" s="22" t="str">
+      <c r="Q21" s="24" t="str">
         <f>IF(WBS!$C22="","",IF(AND(WBS!$E22&lt;&gt;"",Q$4&gt;=WBS!$E22,Q$4&lt;=WBS!$F22),"■",IF(AND(Q$4&gt;=WBS!$C22,Q$4&lt;=WBS!$D22),"□","")))</f>
         <v/>
       </c>
-      <c r="R21" s="22" t="str">
+      <c r="R21" s="24" t="str">
         <f>IF(WBS!$C22="","",IF(AND(WBS!$E22&lt;&gt;"",R$4&gt;=WBS!$E22,R$4&lt;=WBS!$F22),"■",IF(AND(R$4&gt;=WBS!$C22,R$4&lt;=WBS!$D22),"□","")))</f>
         <v/>
       </c>
-      <c r="S21" s="22" t="str">
+      <c r="S21" s="24" t="str">
         <f>IF(WBS!$C22="","",IF(AND(WBS!$E22&lt;&gt;"",S$4&gt;=WBS!$E22,S$4&lt;=WBS!$F22),"■",IF(AND(S$4&gt;=WBS!$C22,S$4&lt;=WBS!$D22),"□","")))</f>
         <v/>
       </c>
-      <c r="T21" s="22" t="str">
+      <c r="T21" s="24" t="str">
         <f>IF(WBS!$C22="","",IF(AND(WBS!$E22&lt;&gt;"",T$4&gt;=WBS!$E22,T$4&lt;=WBS!$F22),"■",IF(AND(T$4&gt;=WBS!$C22,T$4&lt;=WBS!$D22),"□","")))</f>
         <v/>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A22" s="21" t="str">
+      <c r="A22" s="23" t="str">
         <f>WBS!A23</f>
         <v>4.4</v>
       </c>
-      <c r="B22" s="21" t="str">
+      <c r="B22" s="23" t="str">
         <f>WBS!B23</f>
         <v>Viết Chương 2 – Phương pháp và mô hình</v>
       </c>
-      <c r="C22" s="22" t="str">
+      <c r="C22" s="24" t="str">
         <f>IF(WBS!$C23="","",IF(AND(WBS!$E23&lt;&gt;"",C$4&gt;=WBS!$E23,C$4&lt;=WBS!$F23),"■",IF(AND(C$4&gt;=WBS!$C23,C$4&lt;=WBS!$D23),"□","")))</f>
         <v/>
       </c>
-      <c r="D22" s="22" t="str">
+      <c r="D22" s="24" t="str">
         <f>IF(WBS!$C23="","",IF(AND(WBS!$E23&lt;&gt;"",D$4&gt;=WBS!$E23,D$4&lt;=WBS!$F23),"■",IF(AND(D$4&gt;=WBS!$C23,D$4&lt;=WBS!$D23),"□","")))</f>
         <v/>
       </c>
-      <c r="E22" s="22" t="str">
+      <c r="E22" s="24" t="str">
         <f>IF(WBS!$C23="","",IF(AND(WBS!$E23&lt;&gt;"",E$4&gt;=WBS!$E23,E$4&lt;=WBS!$F23),"■",IF(AND(E$4&gt;=WBS!$C23,E$4&lt;=WBS!$D23),"□","")))</f>
         <v/>
       </c>
-      <c r="F22" s="22" t="str">
+      <c r="F22" s="24" t="str">
         <f>IF(WBS!$C23="","",IF(AND(WBS!$E23&lt;&gt;"",F$4&gt;=WBS!$E23,F$4&lt;=WBS!$F23),"■",IF(AND(F$4&gt;=WBS!$C23,F$4&lt;=WBS!$D23),"□","")))</f>
         <v/>
       </c>
-      <c r="G22" s="22" t="str">
+      <c r="G22" s="24" t="str">
         <f>IF(WBS!$C23="","",IF(AND(WBS!$E23&lt;&gt;"",G$4&gt;=WBS!$E23,G$4&lt;=WBS!$F23),"■",IF(AND(G$4&gt;=WBS!$C23,G$4&lt;=WBS!$D23),"□","")))</f>
         <v/>
       </c>
-      <c r="H22" s="22" t="str">
+      <c r="H22" s="24" t="str">
         <f>IF(WBS!$C23="","",IF(AND(WBS!$E23&lt;&gt;"",H$4&gt;=WBS!$E23,H$4&lt;=WBS!$F23),"■",IF(AND(H$4&gt;=WBS!$C23,H$4&lt;=WBS!$D23),"□","")))</f>
         <v/>
       </c>
-      <c r="I22" s="22" t="str">
+      <c r="I22" s="24" t="str">
         <f>IF(WBS!$C23="","",IF(AND(WBS!$E23&lt;&gt;"",I$4&gt;=WBS!$E23,I$4&lt;=WBS!$F23),"■",IF(AND(I$4&gt;=WBS!$C23,I$4&lt;=WBS!$D23),"□","")))</f>
         <v/>
       </c>
-      <c r="J22" s="22" t="str">
+      <c r="J22" s="24" t="str">
         <f>IF(WBS!$C23="","",IF(AND(WBS!$E23&lt;&gt;"",J$4&gt;=WBS!$E23,J$4&lt;=WBS!$F23),"■",IF(AND(J$4&gt;=WBS!$C23,J$4&lt;=WBS!$D23),"□","")))</f>
         <v>□</v>
       </c>
-      <c r="K22" s="22" t="str">
+      <c r="K22" s="24" t="str">
         <f>IF(WBS!$C23="","",IF(AND(WBS!$E23&lt;&gt;"",K$4&gt;=WBS!$E23,K$4&lt;=WBS!$F23),"■",IF(AND(K$4&gt;=WBS!$C23,K$4&lt;=WBS!$D23),"□","")))</f>
         <v>■</v>
       </c>
-      <c r="L22" s="22" t="str">
+      <c r="L22" s="24" t="str">
         <f>IF(WBS!$C23="","",IF(AND(WBS!$E23&lt;&gt;"",L$4&gt;=WBS!$E23,L$4&lt;=WBS!$F23),"■",IF(AND(L$4&gt;=WBS!$C23,L$4&lt;=WBS!$D23),"□","")))</f>
         <v/>
       </c>
-      <c r="M22" s="22" t="str">
+      <c r="M22" s="24" t="str">
         <f>IF(WBS!$C23="","",IF(AND(WBS!$E23&lt;&gt;"",M$4&gt;=WBS!$E23,M$4&lt;=WBS!$F23),"■",IF(AND(M$4&gt;=WBS!$C23,M$4&lt;=WBS!$D23),"□","")))</f>
         <v/>
       </c>
-      <c r="N22" s="22" t="str">
+      <c r="N22" s="24" t="str">
         <f>IF(WBS!$C23="","",IF(AND(WBS!$E23&lt;&gt;"",N$4&gt;=WBS!$E23,N$4&lt;=WBS!$F23),"■",IF(AND(N$4&gt;=WBS!$C23,N$4&lt;=WBS!$D23),"□","")))</f>
         <v/>
       </c>
-      <c r="O22" s="22" t="str">
+      <c r="O22" s="24" t="str">
         <f>IF(WBS!$C23="","",IF(AND(WBS!$E23&lt;&gt;"",O$4&gt;=WBS!$E23,O$4&lt;=WBS!$F23),"■",IF(AND(O$4&gt;=WBS!$C23,O$4&lt;=WBS!$D23),"□","")))</f>
         <v/>
       </c>
-      <c r="P22" s="22" t="str">
+      <c r="P22" s="24" t="str">
         <f>IF(WBS!$C23="","",IF(AND(WBS!$E23&lt;&gt;"",P$4&gt;=WBS!$E23,P$4&lt;=WBS!$F23),"■",IF(AND(P$4&gt;=WBS!$C23,P$4&lt;=WBS!$D23),"□","")))</f>
         <v/>
       </c>
-      <c r="Q22" s="22" t="str">
+      <c r="Q22" s="24" t="str">
         <f>IF(WBS!$C23="","",IF(AND(WBS!$E23&lt;&gt;"",Q$4&gt;=WBS!$E23,Q$4&lt;=WBS!$F23),"■",IF(AND(Q$4&gt;=WBS!$C23,Q$4&lt;=WBS!$D23),"□","")))</f>
         <v/>
       </c>
-      <c r="R22" s="22" t="str">
+      <c r="R22" s="24" t="str">
         <f>IF(WBS!$C23="","",IF(AND(WBS!$E23&lt;&gt;"",R$4&gt;=WBS!$E23,R$4&lt;=WBS!$F23),"■",IF(AND(R$4&gt;=WBS!$C23,R$4&lt;=WBS!$D23),"□","")))</f>
         <v/>
       </c>
-      <c r="S22" s="22" t="str">
+      <c r="S22" s="24" t="str">
         <f>IF(WBS!$C23="","",IF(AND(WBS!$E23&lt;&gt;"",S$4&gt;=WBS!$E23,S$4&lt;=WBS!$F23),"■",IF(AND(S$4&gt;=WBS!$C23,S$4&lt;=WBS!$D23),"□","")))</f>
         <v/>
       </c>
-      <c r="T22" s="22" t="str">
+      <c r="T22" s="24" t="str">
         <f>IF(WBS!$C23="","",IF(AND(WBS!$E23&lt;&gt;"",T$4&gt;=WBS!$E23,T$4&lt;=WBS!$F23),"■",IF(AND(T$4&gt;=WBS!$C23,T$4&lt;=WBS!$D23),"□","")))</f>
         <v/>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A23" s="21" t="str">
+      <c r="A23" s="23" t="str">
         <f>WBS!A24</f>
         <v>4.5</v>
       </c>
-      <c r="B23" s="21" t="str">
+      <c r="B23" s="23" t="str">
         <f>WBS!B24</f>
         <v>Viết Chương 3 – Tái hiện thực nghiệm</v>
       </c>
-      <c r="C23" s="22" t="str">
+      <c r="C23" s="24" t="str">
         <f>IF(WBS!$C24="","",IF(AND(WBS!$E24&lt;&gt;"",C$4&gt;=WBS!$E24,C$4&lt;=WBS!$F24),"■",IF(AND(C$4&gt;=WBS!$C24,C$4&lt;=WBS!$D24),"□","")))</f>
         <v/>
       </c>
-      <c r="D23" s="22" t="str">
+      <c r="D23" s="24" t="str">
         <f>IF(WBS!$C24="","",IF(AND(WBS!$E24&lt;&gt;"",D$4&gt;=WBS!$E24,D$4&lt;=WBS!$F24),"■",IF(AND(D$4&gt;=WBS!$C24,D$4&lt;=WBS!$D24),"□","")))</f>
         <v/>
       </c>
-      <c r="E23" s="22" t="str">
+      <c r="E23" s="24" t="str">
         <f>IF(WBS!$C24="","",IF(AND(WBS!$E24&lt;&gt;"",E$4&gt;=WBS!$E24,E$4&lt;=WBS!$F24),"■",IF(AND(E$4&gt;=WBS!$C24,E$4&lt;=WBS!$D24),"□","")))</f>
         <v/>
       </c>
-      <c r="F23" s="22" t="str">
+      <c r="F23" s="24" t="str">
         <f>IF(WBS!$C24="","",IF(AND(WBS!$E24&lt;&gt;"",F$4&gt;=WBS!$E24,F$4&lt;=WBS!$F24),"■",IF(AND(F$4&gt;=WBS!$C24,F$4&lt;=WBS!$D24),"□","")))</f>
         <v/>
       </c>
-      <c r="G23" s="22" t="str">
+      <c r="G23" s="24" t="str">
         <f>IF(WBS!$C24="","",IF(AND(WBS!$E24&lt;&gt;"",G$4&gt;=WBS!$E24,G$4&lt;=WBS!$F24),"■",IF(AND(G$4&gt;=WBS!$C24,G$4&lt;=WBS!$D24),"□","")))</f>
         <v/>
       </c>
-      <c r="H23" s="22" t="str">
+      <c r="H23" s="24" t="str">
         <f>IF(WBS!$C24="","",IF(AND(WBS!$E24&lt;&gt;"",H$4&gt;=WBS!$E24,H$4&lt;=WBS!$F24),"■",IF(AND(H$4&gt;=WBS!$C24,H$4&lt;=WBS!$D24),"□","")))</f>
         <v/>
       </c>
-      <c r="I23" s="22" t="str">
+      <c r="I23" s="24" t="str">
         <f>IF(WBS!$C24="","",IF(AND(WBS!$E24&lt;&gt;"",I$4&gt;=WBS!$E24,I$4&lt;=WBS!$F24),"■",IF(AND(I$4&gt;=WBS!$C24,I$4&lt;=WBS!$D24),"□","")))</f>
         <v/>
       </c>
-      <c r="J23" s="22" t="str">
+      <c r="J23" s="24" t="str">
         <f>IF(WBS!$C24="","",IF(AND(WBS!$E24&lt;&gt;"",J$4&gt;=WBS!$E24,J$4&lt;=WBS!$F24),"■",IF(AND(J$4&gt;=WBS!$C24,J$4&lt;=WBS!$D24),"□","")))</f>
         <v/>
       </c>
-      <c r="K23" s="22" t="str">
+      <c r="K23" s="24" t="str">
         <f>IF(WBS!$C24="","",IF(AND(WBS!$E24&lt;&gt;"",K$4&gt;=WBS!$E24,K$4&lt;=WBS!$F24),"■",IF(AND(K$4&gt;=WBS!$C24,K$4&lt;=WBS!$D24),"□","")))</f>
         <v>■</v>
       </c>
-      <c r="L23" s="22" t="str">
+      <c r="L23" s="24" t="str">
         <f>IF(WBS!$C24="","",IF(AND(WBS!$E24&lt;&gt;"",L$4&gt;=WBS!$E24,L$4&lt;=WBS!$F24),"■",IF(AND(L$4&gt;=WBS!$C24,L$4&lt;=WBS!$D24),"□","")))</f>
         <v/>
       </c>
-      <c r="M23" s="22" t="str">
+      <c r="M23" s="24" t="str">
         <f>IF(WBS!$C24="","",IF(AND(WBS!$E24&lt;&gt;"",M$4&gt;=WBS!$E24,M$4&lt;=WBS!$F24),"■",IF(AND(M$4&gt;=WBS!$C24,M$4&lt;=WBS!$D24),"□","")))</f>
         <v/>
       </c>
-      <c r="N23" s="22" t="str">
+      <c r="N23" s="24" t="str">
         <f>IF(WBS!$C24="","",IF(AND(WBS!$E24&lt;&gt;"",N$4&gt;=WBS!$E24,N$4&lt;=WBS!$F24),"■",IF(AND(N$4&gt;=WBS!$C24,N$4&lt;=WBS!$D24),"□","")))</f>
         <v>□</v>
       </c>
-      <c r="O23" s="22" t="str">
+      <c r="O23" s="24" t="str">
         <f>IF(WBS!$C24="","",IF(AND(WBS!$E24&lt;&gt;"",O$4&gt;=WBS!$E24,O$4&lt;=WBS!$F24),"■",IF(AND(O$4&gt;=WBS!$C24,O$4&lt;=WBS!$D24),"□","")))</f>
         <v/>
       </c>
-      <c r="P23" s="22" t="str">
+      <c r="P23" s="24" t="str">
         <f>IF(WBS!$C24="","",IF(AND(WBS!$E24&lt;&gt;"",P$4&gt;=WBS!$E24,P$4&lt;=WBS!$F24),"■",IF(AND(P$4&gt;=WBS!$C24,P$4&lt;=WBS!$D24),"□","")))</f>
         <v/>
       </c>
-      <c r="Q23" s="22" t="str">
+      <c r="Q23" s="24" t="str">
         <f>IF(WBS!$C24="","",IF(AND(WBS!$E24&lt;&gt;"",Q$4&gt;=WBS!$E24,Q$4&lt;=WBS!$F24),"■",IF(AND(Q$4&gt;=WBS!$C24,Q$4&lt;=WBS!$D24),"□","")))</f>
         <v/>
       </c>
-      <c r="R23" s="22" t="str">
+      <c r="R23" s="24" t="str">
         <f>IF(WBS!$C24="","",IF(AND(WBS!$E24&lt;&gt;"",R$4&gt;=WBS!$E24,R$4&lt;=WBS!$F24),"■",IF(AND(R$4&gt;=WBS!$C24,R$4&lt;=WBS!$D24),"□","")))</f>
         <v/>
       </c>
-      <c r="S23" s="22" t="str">
+      <c r="S23" s="24" t="str">
         <f>IF(WBS!$C24="","",IF(AND(WBS!$E24&lt;&gt;"",S$4&gt;=WBS!$E24,S$4&lt;=WBS!$F24),"■",IF(AND(S$4&gt;=WBS!$C24,S$4&lt;=WBS!$D24),"□","")))</f>
         <v/>
       </c>
-      <c r="T23" s="22" t="str">
+      <c r="T23" s="24" t="str">
         <f>IF(WBS!$C24="","",IF(AND(WBS!$E24&lt;&gt;"",T$4&gt;=WBS!$E24,T$4&lt;=WBS!$F24),"■",IF(AND(T$4&gt;=WBS!$C24,T$4&lt;=WBS!$D24),"□","")))</f>
         <v/>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A24" s="21" t="str">
+      <c r="A24" s="23" t="str">
         <f>WBS!A25</f>
         <v>4.6</v>
       </c>
-      <c r="B24" s="21" t="str">
+      <c r="B24" s="23" t="str">
         <f>WBS!B25</f>
         <v>Ví dụ thực tế 1: dự án dầu khí Việt Nam</v>
       </c>
-      <c r="C24" s="22" t="str">
+      <c r="C24" s="24" t="str">
         <f>IF(WBS!$C25="","",IF(AND(WBS!$E25&lt;&gt;"",C$4&gt;=WBS!$E25,C$4&lt;=WBS!$F25),"■",IF(AND(C$4&gt;=WBS!$C25,C$4&lt;=WBS!$D25),"□","")))</f>
         <v/>
       </c>
-      <c r="D24" s="22" t="str">
+      <c r="D24" s="24" t="str">
         <f>IF(WBS!$C25="","",IF(AND(WBS!$E25&lt;&gt;"",D$4&gt;=WBS!$E25,D$4&lt;=WBS!$F25),"■",IF(AND(D$4&gt;=WBS!$C25,D$4&lt;=WBS!$D25),"□","")))</f>
         <v/>
       </c>
-      <c r="E24" s="22" t="str">
+      <c r="E24" s="24" t="str">
         <f>IF(WBS!$C25="","",IF(AND(WBS!$E25&lt;&gt;"",E$4&gt;=WBS!$E25,E$4&lt;=WBS!$F25),"■",IF(AND(E$4&gt;=WBS!$C25,E$4&lt;=WBS!$D25),"□","")))</f>
         <v/>
       </c>
-      <c r="F24" s="22" t="str">
+      <c r="F24" s="24" t="str">
         <f>IF(WBS!$C25="","",IF(AND(WBS!$E25&lt;&gt;"",F$4&gt;=WBS!$E25,F$4&lt;=WBS!$F25),"■",IF(AND(F$4&gt;=WBS!$C25,F$4&lt;=WBS!$D25),"□","")))</f>
         <v/>
       </c>
-      <c r="G24" s="22" t="str">
+      <c r="G24" s="24" t="str">
         <f>IF(WBS!$C25="","",IF(AND(WBS!$E25&lt;&gt;"",G$4&gt;=WBS!$E25,G$4&lt;=WBS!$F25),"■",IF(AND(G$4&gt;=WBS!$C25,G$4&lt;=WBS!$D25),"□","")))</f>
         <v/>
       </c>
-      <c r="H24" s="22" t="str">
+      <c r="H24" s="24" t="str">
         <f>IF(WBS!$C25="","",IF(AND(WBS!$E25&lt;&gt;"",H$4&gt;=WBS!$E25,H$4&lt;=WBS!$F25),"■",IF(AND(H$4&gt;=WBS!$C25,H$4&lt;=WBS!$D25),"□","")))</f>
         <v/>
       </c>
-      <c r="I24" s="22" t="str">
+      <c r="I24" s="24" t="str">
         <f>IF(WBS!$C25="","",IF(AND(WBS!$E25&lt;&gt;"",I$4&gt;=WBS!$E25,I$4&lt;=WBS!$F25),"■",IF(AND(I$4&gt;=WBS!$C25,I$4&lt;=WBS!$D25),"□","")))</f>
         <v/>
       </c>
-      <c r="J24" s="22" t="str">
+      <c r="J24" s="24" t="str">
         <f>IF(WBS!$C25="","",IF(AND(WBS!$E25&lt;&gt;"",J$4&gt;=WBS!$E25,J$4&lt;=WBS!$F25),"■",IF(AND(J$4&gt;=WBS!$C25,J$4&lt;=WBS!$D25),"□","")))</f>
         <v/>
       </c>
-      <c r="K24" s="22" t="str">
+      <c r="K24" s="24" t="str">
         <f>IF(WBS!$C25="","",IF(AND(WBS!$E25&lt;&gt;"",K$4&gt;=WBS!$E25,K$4&lt;=WBS!$F25),"■",IF(AND(K$4&gt;=WBS!$C25,K$4&lt;=WBS!$D25),"□","")))</f>
         <v>■</v>
       </c>
-      <c r="L24" s="22" t="str">
+      <c r="L24" s="24" t="str">
         <f>IF(WBS!$C25="","",IF(AND(WBS!$E25&lt;&gt;"",L$4&gt;=WBS!$E25,L$4&lt;=WBS!$F25),"■",IF(AND(L$4&gt;=WBS!$C25,L$4&lt;=WBS!$D25),"□","")))</f>
         <v/>
       </c>
-      <c r="M24" s="22" t="str">
+      <c r="M24" s="24" t="str">
         <f>IF(WBS!$C25="","",IF(AND(WBS!$E25&lt;&gt;"",M$4&gt;=WBS!$E25,M$4&lt;=WBS!$F25),"■",IF(AND(M$4&gt;=WBS!$C25,M$4&lt;=WBS!$D25),"□","")))</f>
         <v/>
       </c>
-      <c r="N24" s="22" t="str">
+      <c r="N24" s="24" t="str">
         <f>IF(WBS!$C25="","",IF(AND(WBS!$E25&lt;&gt;"",N$4&gt;=WBS!$E25,N$4&lt;=WBS!$F25),"■",IF(AND(N$4&gt;=WBS!$C25,N$4&lt;=WBS!$D25),"□","")))</f>
         <v/>
       </c>
-      <c r="O24" s="22" t="str">
+      <c r="O24" s="24" t="str">
         <f>IF(WBS!$C25="","",IF(AND(WBS!$E25&lt;&gt;"",O$4&gt;=WBS!$E25,O$4&lt;=WBS!$F25),"■",IF(AND(O$4&gt;=WBS!$C25,O$4&lt;=WBS!$D25),"□","")))</f>
         <v>□</v>
       </c>
-      <c r="P24" s="22" t="str">
+      <c r="P24" s="24" t="str">
         <f>IF(WBS!$C25="","",IF(AND(WBS!$E25&lt;&gt;"",P$4&gt;=WBS!$E25,P$4&lt;=WBS!$F25),"■",IF(AND(P$4&gt;=WBS!$C25,P$4&lt;=WBS!$D25),"□","")))</f>
         <v/>
       </c>
-      <c r="Q24" s="22" t="str">
+      <c r="Q24" s="24" t="str">
         <f>IF(WBS!$C25="","",IF(AND(WBS!$E25&lt;&gt;"",Q$4&gt;=WBS!$E25,Q$4&lt;=WBS!$F25),"■",IF(AND(Q$4&gt;=WBS!$C25,Q$4&lt;=WBS!$D25),"□","")))</f>
         <v/>
       </c>
-      <c r="R24" s="22" t="str">
+      <c r="R24" s="24" t="str">
         <f>IF(WBS!$C25="","",IF(AND(WBS!$E25&lt;&gt;"",R$4&gt;=WBS!$E25,R$4&lt;=WBS!$F25),"■",IF(AND(R$4&gt;=WBS!$C25,R$4&lt;=WBS!$D25),"□","")))</f>
         <v/>
       </c>
-      <c r="S24" s="22" t="str">
+      <c r="S24" s="24" t="str">
         <f>IF(WBS!$C25="","",IF(AND(WBS!$E25&lt;&gt;"",S$4&gt;=WBS!$E25,S$4&lt;=WBS!$F25),"■",IF(AND(S$4&gt;=WBS!$C25,S$4&lt;=WBS!$D25),"□","")))</f>
         <v/>
       </c>
-      <c r="T24" s="22" t="str">
+      <c r="T24" s="24" t="str">
         <f>IF(WBS!$C25="","",IF(AND(WBS!$E25&lt;&gt;"",T$4&gt;=WBS!$E25,T$4&lt;=WBS!$F25),"■",IF(AND(T$4&gt;=WBS!$C25,T$4&lt;=WBS!$D25),"□","")))</f>
         <v/>
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A25" s="21" t="str">
+      <c r="A25" s="23" t="str">
         <f>WBS!A26</f>
         <v>4.7</v>
       </c>
-      <c r="B25" s="21" t="str">
+      <c r="B25" s="23" t="str">
         <f>WBS!B26</f>
         <v>Ví dụ thực tế 2: dự án HTTT (MS Project, Excel)</v>
       </c>
-      <c r="C25" s="22" t="str">
+      <c r="C25" s="24" t="str">
         <f>IF(WBS!$C26="","",IF(AND(WBS!$E26&lt;&gt;"",C$4&gt;=WBS!$E26,C$4&lt;=WBS!$F26),"■",IF(AND(C$4&gt;=WBS!$C26,C$4&lt;=WBS!$D26),"□","")))</f>
         <v/>
       </c>
-      <c r="D25" s="22" t="str">
+      <c r="D25" s="24" t="str">
         <f>IF(WBS!$C26="","",IF(AND(WBS!$E26&lt;&gt;"",D$4&gt;=WBS!$E26,D$4&lt;=WBS!$F26),"■",IF(AND(D$4&gt;=WBS!$C26,D$4&lt;=WBS!$D26),"□","")))</f>
         <v/>
       </c>
-      <c r="E25" s="22" t="str">
+      <c r="E25" s="24" t="str">
         <f>IF(WBS!$C26="","",IF(AND(WBS!$E26&lt;&gt;"",E$4&gt;=WBS!$E26,E$4&lt;=WBS!$F26),"■",IF(AND(E$4&gt;=WBS!$C26,E$4&lt;=WBS!$D26),"□","")))</f>
         <v/>
       </c>
-      <c r="F25" s="22" t="str">
+      <c r="F25" s="24" t="str">
         <f>IF(WBS!$C26="","",IF(AND(WBS!$E26&lt;&gt;"",F$4&gt;=WBS!$E26,F$4&lt;=WBS!$F26),"■",IF(AND(F$4&gt;=WBS!$C26,F$4&lt;=WBS!$D26),"□","")))</f>
         <v/>
       </c>
-      <c r="G25" s="22" t="str">
+      <c r="G25" s="24" t="str">
         <f>IF(WBS!$C26="","",IF(AND(WBS!$E26&lt;&gt;"",G$4&gt;=WBS!$E26,G$4&lt;=WBS!$F26),"■",IF(AND(G$4&gt;=WBS!$C26,G$4&lt;=WBS!$D26),"□","")))</f>
         <v/>
       </c>
-      <c r="H25" s="22" t="str">
+      <c r="H25" s="24" t="str">
         <f>IF(WBS!$C26="","",IF(AND(WBS!$E26&lt;&gt;"",H$4&gt;=WBS!$E26,H$4&lt;=WBS!$F26),"■",IF(AND(H$4&gt;=WBS!$C26,H$4&lt;=WBS!$D26),"□","")))</f>
         <v/>
       </c>
-      <c r="I25" s="22" t="str">
+      <c r="I25" s="24" t="str">
         <f>IF(WBS!$C26="","",IF(AND(WBS!$E26&lt;&gt;"",I$4&gt;=WBS!$E26,I$4&lt;=WBS!$F26),"■",IF(AND(I$4&gt;=WBS!$C26,I$4&lt;=WBS!$D26),"□","")))</f>
         <v/>
       </c>
-      <c r="J25" s="22" t="str">
+      <c r="J25" s="24" t="str">
         <f>IF(WBS!$C26="","",IF(AND(WBS!$E26&lt;&gt;"",J$4&gt;=WBS!$E26,J$4&lt;=WBS!$F26),"■",IF(AND(J$4&gt;=WBS!$C26,J$4&lt;=WBS!$D26),"□","")))</f>
         <v/>
       </c>
-      <c r="K25" s="22" t="str">
+      <c r="K25" s="24" t="str">
         <f>IF(WBS!$C26="","",IF(AND(WBS!$E26&lt;&gt;"",K$4&gt;=WBS!$E26,K$4&lt;=WBS!$F26),"■",IF(AND(K$4&gt;=WBS!$C26,K$4&lt;=WBS!$D26),"□","")))</f>
         <v>■</v>
       </c>
-      <c r="L25" s="22" t="str">
+      <c r="L25" s="24" t="str">
         <f>IF(WBS!$C26="","",IF(AND(WBS!$E26&lt;&gt;"",L$4&gt;=WBS!$E26,L$4&lt;=WBS!$F26),"■",IF(AND(L$4&gt;=WBS!$C26,L$4&lt;=WBS!$D26),"□","")))</f>
         <v/>
       </c>
-      <c r="M25" s="22" t="str">
+      <c r="M25" s="24" t="str">
         <f>IF(WBS!$C26="","",IF(AND(WBS!$E26&lt;&gt;"",M$4&gt;=WBS!$E26,M$4&lt;=WBS!$F26),"■",IF(AND(M$4&gt;=WBS!$C26,M$4&lt;=WBS!$D26),"□","")))</f>
         <v/>
       </c>
-      <c r="N25" s="22" t="str">
+      <c r="N25" s="24" t="str">
         <f>IF(WBS!$C26="","",IF(AND(WBS!$E26&lt;&gt;"",N$4&gt;=WBS!$E26,N$4&lt;=WBS!$F26),"■",IF(AND(N$4&gt;=WBS!$C26,N$4&lt;=WBS!$D26),"□","")))</f>
         <v/>
       </c>
-      <c r="O25" s="22" t="str">
+      <c r="O25" s="24" t="str">
         <f>IF(WBS!$C26="","",IF(AND(WBS!$E26&lt;&gt;"",O$4&gt;=WBS!$E26,O$4&lt;=WBS!$F26),"■",IF(AND(O$4&gt;=WBS!$C26,O$4&lt;=WBS!$D26),"□","")))</f>
         <v/>
       </c>
-      <c r="P25" s="22" t="str">
+      <c r="P25" s="24" t="str">
         <f>IF(WBS!$C26="","",IF(AND(WBS!$E26&lt;&gt;"",P$4&gt;=WBS!$E26,P$4&lt;=WBS!$F26),"■",IF(AND(P$4&gt;=WBS!$C26,P$4&lt;=WBS!$D26),"□","")))</f>
         <v>□</v>
       </c>
-      <c r="Q25" s="22" t="str">
+      <c r="Q25" s="24" t="str">
         <f>IF(WBS!$C26="","",IF(AND(WBS!$E26&lt;&gt;"",Q$4&gt;=WBS!$E26,Q$4&lt;=WBS!$F26),"■",IF(AND(Q$4&gt;=WBS!$C26,Q$4&lt;=WBS!$D26),"□","")))</f>
         <v/>
       </c>
-      <c r="R25" s="22" t="str">
+      <c r="R25" s="24" t="str">
         <f>IF(WBS!$C26="","",IF(AND(WBS!$E26&lt;&gt;"",R$4&gt;=WBS!$E26,R$4&lt;=WBS!$F26),"■",IF(AND(R$4&gt;=WBS!$C26,R$4&lt;=WBS!$D26),"□","")))</f>
         <v/>
       </c>
-      <c r="S25" s="22" t="str">
+      <c r="S25" s="24" t="str">
         <f>IF(WBS!$C26="","",IF(AND(WBS!$E26&lt;&gt;"",S$4&gt;=WBS!$E26,S$4&lt;=WBS!$F26),"■",IF(AND(S$4&gt;=WBS!$C26,S$4&lt;=WBS!$D26),"□","")))</f>
         <v/>
       </c>
-      <c r="T25" s="22" t="str">
+      <c r="T25" s="24" t="str">
         <f>IF(WBS!$C26="","",IF(AND(WBS!$E26&lt;&gt;"",T$4&gt;=WBS!$E26,T$4&lt;=WBS!$F26),"■",IF(AND(T$4&gt;=WBS!$C26,T$4&lt;=WBS!$D26),"□","")))</f>
         <v/>
       </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A26" s="21" t="str">
+      <c r="A26" s="23" t="str">
         <f>WBS!A27</f>
         <v>4.8</v>
       </c>
-      <c r="B26" s="21" t="str">
+      <c r="B26" s="23" t="str">
         <f>WBS!B27</f>
         <v>Mô phỏng Monte Carlo, phản biện bài báo</v>
       </c>
-      <c r="C26" s="22" t="str">
+      <c r="C26" s="24" t="str">
         <f>IF(WBS!$C27="","",IF(AND(WBS!$E27&lt;&gt;"",C$4&gt;=WBS!$E27,C$4&lt;=WBS!$F27),"■",IF(AND(C$4&gt;=WBS!$C27,C$4&lt;=WBS!$D27),"□","")))</f>
         <v/>
       </c>
-      <c r="D26" s="22" t="str">
+      <c r="D26" s="24" t="str">
         <f>IF(WBS!$C27="","",IF(AND(WBS!$E27&lt;&gt;"",D$4&gt;=WBS!$E27,D$4&lt;=WBS!$F27),"■",IF(AND(D$4&gt;=WBS!$C27,D$4&lt;=WBS!$D27),"□","")))</f>
         <v/>
       </c>
-      <c r="E26" s="22" t="str">
+      <c r="E26" s="24" t="str">
         <f>IF(WBS!$C27="","",IF(AND(WBS!$E27&lt;&gt;"",E$4&gt;=WBS!$E27,E$4&lt;=WBS!$F27),"■",IF(AND(E$4&gt;=WBS!$C27,E$4&lt;=WBS!$D27),"□","")))</f>
         <v/>
       </c>
-      <c r="F26" s="22" t="str">
+      <c r="F26" s="24" t="str">
         <f>IF(WBS!$C27="","",IF(AND(WBS!$E27&lt;&gt;"",F$4&gt;=WBS!$E27,F$4&lt;=WBS!$F27),"■",IF(AND(F$4&gt;=WBS!$C27,F$4&lt;=WBS!$D27),"□","")))</f>
         <v/>
       </c>
-      <c r="G26" s="22" t="str">
+      <c r="G26" s="24" t="str">
         <f>IF(WBS!$C27="","",IF(AND(WBS!$E27&lt;&gt;"",G$4&gt;=WBS!$E27,G$4&lt;=WBS!$F27),"■",IF(AND(G$4&gt;=WBS!$C27,G$4&lt;=WBS!$D27),"□","")))</f>
         <v/>
       </c>
-      <c r="H26" s="22" t="str">
+      <c r="H26" s="24" t="str">
         <f>IF(WBS!$C27="","",IF(AND(WBS!$E27&lt;&gt;"",H$4&gt;=WBS!$E27,H$4&lt;=WBS!$F27),"■",IF(AND(H$4&gt;=WBS!$C27,H$4&lt;=WBS!$D27),"□","")))</f>
         <v/>
       </c>
-      <c r="I26" s="22" t="str">
+      <c r="I26" s="24" t="str">
         <f>IF(WBS!$C27="","",IF(AND(WBS!$E27&lt;&gt;"",I$4&gt;=WBS!$E27,I$4&lt;=WBS!$F27),"■",IF(AND(I$4&gt;=WBS!$C27,I$4&lt;=WBS!$D27),"□","")))</f>
         <v/>
       </c>
-      <c r="J26" s="22" t="str">
+      <c r="J26" s="24" t="str">
         <f>IF(WBS!$C27="","",IF(AND(WBS!$E27&lt;&gt;"",J$4&gt;=WBS!$E27,J$4&lt;=WBS!$F27),"■",IF(AND(J$4&gt;=WBS!$C27,J$4&lt;=WBS!$D27),"□","")))</f>
         <v/>
       </c>
-      <c r="K26" s="22" t="str">
+      <c r="K26" s="24" t="str">
         <f>IF(WBS!$C27="","",IF(AND(WBS!$E27&lt;&gt;"",K$4&gt;=WBS!$E27,K$4&lt;=WBS!$F27),"■",IF(AND(K$4&gt;=WBS!$C27,K$4&lt;=WBS!$D27),"□","")))</f>
         <v>■</v>
       </c>
-      <c r="L26" s="22" t="str">
+      <c r="L26" s="24" t="str">
         <f>IF(WBS!$C27="","",IF(AND(WBS!$E27&lt;&gt;"",L$4&gt;=WBS!$E27,L$4&lt;=WBS!$F27),"■",IF(AND(L$4&gt;=WBS!$C27,L$4&lt;=WBS!$D27),"□","")))</f>
         <v/>
       </c>
-      <c r="M26" s="22" t="str">
+      <c r="M26" s="24" t="str">
         <f>IF(WBS!$C27="","",IF(AND(WBS!$E27&lt;&gt;"",M$4&gt;=WBS!$E27,M$4&lt;=WBS!$F27),"■",IF(AND(M$4&gt;=WBS!$C27,M$4&lt;=WBS!$D27),"□","")))</f>
         <v/>
       </c>
-      <c r="N26" s="22" t="str">
+      <c r="N26" s="24" t="str">
         <f>IF(WBS!$C27="","",IF(AND(WBS!$E27&lt;&gt;"",N$4&gt;=WBS!$E27,N$4&lt;=WBS!$F27),"■",IF(AND(N$4&gt;=WBS!$C27,N$4&lt;=WBS!$D27),"□","")))</f>
         <v/>
       </c>
-      <c r="O26" s="22" t="str">
+      <c r="O26" s="24" t="str">
         <f>IF(WBS!$C27="","",IF(AND(WBS!$E27&lt;&gt;"",O$4&gt;=WBS!$E27,O$4&lt;=WBS!$F27),"■",IF(AND(O$4&gt;=WBS!$C27,O$4&lt;=WBS!$D27),"□","")))</f>
         <v/>
       </c>
-      <c r="P26" s="22" t="str">
+      <c r="P26" s="24" t="str">
         <f>IF(WBS!$C27="","",IF(AND(WBS!$E27&lt;&gt;"",P$4&gt;=WBS!$E27,P$4&lt;=WBS!$F27),"■",IF(AND(P$4&gt;=WBS!$C27,P$4&lt;=WBS!$D27),"□","")))</f>
         <v/>
       </c>
-      <c r="Q26" s="22" t="str">
+      <c r="Q26" s="24" t="str">
         <f>IF(WBS!$C27="","",IF(AND(WBS!$E27&lt;&gt;"",Q$4&gt;=WBS!$E27,Q$4&lt;=WBS!$F27),"■",IF(AND(Q$4&gt;=WBS!$C27,Q$4&lt;=WBS!$D27),"□","")))</f>
         <v>□</v>
       </c>
-      <c r="R26" s="22" t="str">
+      <c r="R26" s="24" t="str">
         <f>IF(WBS!$C27="","",IF(AND(WBS!$E27&lt;&gt;"",R$4&gt;=WBS!$E27,R$4&lt;=WBS!$F27),"■",IF(AND(R$4&gt;=WBS!$C27,R$4&lt;=WBS!$D27),"□","")))</f>
         <v/>
       </c>
-      <c r="S26" s="22" t="str">
+      <c r="S26" s="24" t="str">
         <f>IF(WBS!$C27="","",IF(AND(WBS!$E27&lt;&gt;"",S$4&gt;=WBS!$E27,S$4&lt;=WBS!$F27),"■",IF(AND(S$4&gt;=WBS!$C27,S$4&lt;=WBS!$D27),"□","")))</f>
         <v/>
       </c>
-      <c r="T26" s="22" t="str">
+      <c r="T26" s="24" t="str">
         <f>IF(WBS!$C27="","",IF(AND(WBS!$E27&lt;&gt;"",T$4&gt;=WBS!$E27,T$4&lt;=WBS!$F27),"■",IF(AND(T$4&gt;=WBS!$C27,T$4&lt;=WBS!$D27),"□","")))</f>
         <v/>
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A27" s="21" t="str">
+      <c r="A27" s="23" t="str">
         <f>WBS!A28</f>
         <v>4.9</v>
       </c>
-      <c r="B27" s="21" t="str">
+      <c r="B27" s="23" t="str">
         <f>WBS!B28</f>
         <v>Mở đầu, kết luận, rà soát, xuất PDF</v>
       </c>
-      <c r="C27" s="22" t="str">
+      <c r="C27" s="24" t="str">
         <f>IF(WBS!$C28="","",IF(AND(WBS!$E28&lt;&gt;"",C$4&gt;=WBS!$E28,C$4&lt;=WBS!$F28),"■",IF(AND(C$4&gt;=WBS!$C28,C$4&lt;=WBS!$D28),"□","")))</f>
         <v/>
       </c>
-      <c r="D27" s="22" t="str">
+      <c r="D27" s="24" t="str">
         <f>IF(WBS!$C28="","",IF(AND(WBS!$E28&lt;&gt;"",D$4&gt;=WBS!$E28,D$4&lt;=WBS!$F28),"■",IF(AND(D$4&gt;=WBS!$C28,D$4&lt;=WBS!$D28),"□","")))</f>
         <v/>
       </c>
-      <c r="E27" s="22" t="str">
+      <c r="E27" s="24" t="str">
         <f>IF(WBS!$C28="","",IF(AND(WBS!$E28&lt;&gt;"",E$4&gt;=WBS!$E28,E$4&lt;=WBS!$F28),"■",IF(AND(E$4&gt;=WBS!$C28,E$4&lt;=WBS!$D28),"□","")))</f>
         <v/>
       </c>
-      <c r="F27" s="22" t="str">
+      <c r="F27" s="24" t="str">
         <f>IF(WBS!$C28="","",IF(AND(WBS!$E28&lt;&gt;"",F$4&gt;=WBS!$E28,F$4&lt;=WBS!$F28),"■",IF(AND(F$4&gt;=WBS!$C28,F$4&lt;=WBS!$D28),"□","")))</f>
         <v/>
       </c>
-      <c r="G27" s="22" t="str">
+      <c r="G27" s="24" t="str">
         <f>IF(WBS!$C28="","",IF(AND(WBS!$E28&lt;&gt;"",G$4&gt;=WBS!$E28,G$4&lt;=WBS!$F28),"■",IF(AND(G$4&gt;=WBS!$C28,G$4&lt;=WBS!$D28),"□","")))</f>
         <v/>
       </c>
-      <c r="H27" s="22" t="str">
+      <c r="H27" s="24" t="str">
         <f>IF(WBS!$C28="","",IF(AND(WBS!$E28&lt;&gt;"",H$4&gt;=WBS!$E28,H$4&lt;=WBS!$F28),"■",IF(AND(H$4&gt;=WBS!$C28,H$4&lt;=WBS!$D28),"□","")))</f>
         <v/>
       </c>
-      <c r="I27" s="22" t="str">
+      <c r="I27" s="24" t="str">
         <f>IF(WBS!$C28="","",IF(AND(WBS!$E28&lt;&gt;"",I$4&gt;=WBS!$E28,I$4&lt;=WBS!$F28),"■",IF(AND(I$4&gt;=WBS!$C28,I$4&lt;=WBS!$D28),"□","")))</f>
         <v/>
       </c>
-      <c r="J27" s="22" t="str">
+      <c r="J27" s="24" t="str">
         <f>IF(WBS!$C28="","",IF(AND(WBS!$E28&lt;&gt;"",J$4&gt;=WBS!$E28,J$4&lt;=WBS!$F28),"■",IF(AND(J$4&gt;=WBS!$C28,J$4&lt;=WBS!$D28),"□","")))</f>
         <v/>
       </c>
-      <c r="K27" s="22" t="str">
+      <c r="K27" s="24" t="str">
         <f>IF(WBS!$C28="","",IF(AND(WBS!$E28&lt;&gt;"",K$4&gt;=WBS!$E28,K$4&lt;=WBS!$F28),"■",IF(AND(K$4&gt;=WBS!$C28,K$4&lt;=WBS!$D28),"□","")))</f>
         <v/>
       </c>
-      <c r="L27" s="22" t="str">
+      <c r="L27" s="24" t="str">
         <f>IF(WBS!$C28="","",IF(AND(WBS!$E28&lt;&gt;"",L$4&gt;=WBS!$E28,L$4&lt;=WBS!$F28),"■",IF(AND(L$4&gt;=WBS!$C28,L$4&lt;=WBS!$D28),"□","")))</f>
         <v/>
       </c>
-      <c r="M27" s="22" t="str">
+      <c r="M27" s="24" t="str">
         <f>IF(WBS!$C28="","",IF(AND(WBS!$E28&lt;&gt;"",M$4&gt;=WBS!$E28,M$4&lt;=WBS!$F28),"■",IF(AND(M$4&gt;=WBS!$C28,M$4&lt;=WBS!$D28),"□","")))</f>
         <v/>
       </c>
-      <c r="N27" s="22" t="str">
+      <c r="N27" s="24" t="str">
         <f>IF(WBS!$C28="","",IF(AND(WBS!$E28&lt;&gt;"",N$4&gt;=WBS!$E28,N$4&lt;=WBS!$F28),"■",IF(AND(N$4&gt;=WBS!$C28,N$4&lt;=WBS!$D28),"□","")))</f>
         <v/>
       </c>
-      <c r="O27" s="22" t="str">
+      <c r="O27" s="24" t="str">
         <f>IF(WBS!$C28="","",IF(AND(WBS!$E28&lt;&gt;"",O$4&gt;=WBS!$E28,O$4&lt;=WBS!$F28),"■",IF(AND(O$4&gt;=WBS!$C28,O$4&lt;=WBS!$D28),"□","")))</f>
         <v/>
       </c>
-      <c r="P27" s="22" t="str">
+      <c r="P27" s="24" t="str">
         <f>IF(WBS!$C28="","",IF(AND(WBS!$E28&lt;&gt;"",P$4&gt;=WBS!$E28,P$4&lt;=WBS!$F28),"■",IF(AND(P$4&gt;=WBS!$C28,P$4&lt;=WBS!$D28),"□","")))</f>
         <v/>
       </c>
-      <c r="Q27" s="22" t="str">
+      <c r="Q27" s="24" t="str">
         <f>IF(WBS!$C28="","",IF(AND(WBS!$E28&lt;&gt;"",Q$4&gt;=WBS!$E28,Q$4&lt;=WBS!$F28),"■",IF(AND(Q$4&gt;=WBS!$C28,Q$4&lt;=WBS!$D28),"□","")))</f>
         <v/>
       </c>
-      <c r="R27" s="22" t="str">
+      <c r="R27" s="24" t="str">
         <f>IF(WBS!$C28="","",IF(AND(WBS!$E28&lt;&gt;"",R$4&gt;=WBS!$E28,R$4&lt;=WBS!$F28),"■",IF(AND(R$4&gt;=WBS!$C28,R$4&lt;=WBS!$D28),"□","")))</f>
         <v>□</v>
       </c>
-      <c r="S27" s="22" t="str">
+      <c r="S27" s="24" t="str">
         <f>IF(WBS!$C28="","",IF(AND(WBS!$E28&lt;&gt;"",S$4&gt;=WBS!$E28,S$4&lt;=WBS!$F28),"■",IF(AND(S$4&gt;=WBS!$C28,S$4&lt;=WBS!$D28),"□","")))</f>
         <v/>
       </c>
-      <c r="T27" s="22" t="str">
+      <c r="T27" s="24" t="str">
         <f>IF(WBS!$C28="","",IF(AND(WBS!$E28&lt;&gt;"",T$4&gt;=WBS!$E28,T$4&lt;=WBS!$F28),"■",IF(AND(T$4&gt;=WBS!$C28,T$4&lt;=WBS!$D28),"□","")))</f>
         <v/>
       </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A28" s="21" t="str">
+      <c r="A28" s="23" t="str">
         <f>WBS!A29</f>
         <v>5</v>
       </c>
-      <c r="B28" s="21" t="str">
+      <c r="B28" s="23" t="str">
         <f>WBS!B29</f>
         <v>Thuyết trình và nộp bài</v>
       </c>
-      <c r="C28" s="22" t="str">
+      <c r="C28" s="24" t="str">
         <f>IF(WBS!$C29="","",IF(AND(WBS!$E29&lt;&gt;"",C$4&gt;=WBS!$E29,C$4&lt;=WBS!$F29),"■",IF(AND(C$4&gt;=WBS!$C29,C$4&lt;=WBS!$D29),"□","")))</f>
         <v/>
       </c>
-      <c r="D28" s="22" t="str">
+      <c r="D28" s="24" t="str">
         <f>IF(WBS!$C29="","",IF(AND(WBS!$E29&lt;&gt;"",D$4&gt;=WBS!$E29,D$4&lt;=WBS!$F29),"■",IF(AND(D$4&gt;=WBS!$C29,D$4&lt;=WBS!$D29),"□","")))</f>
         <v/>
       </c>
-      <c r="E28" s="22" t="str">
+      <c r="E28" s="24" t="str">
         <f>IF(WBS!$C29="","",IF(AND(WBS!$E29&lt;&gt;"",E$4&gt;=WBS!$E29,E$4&lt;=WBS!$F29),"■",IF(AND(E$4&gt;=WBS!$C29,E$4&lt;=WBS!$D29),"□","")))</f>
         <v/>
       </c>
-      <c r="F28" s="22" t="str">
+      <c r="F28" s="24" t="str">
         <f>IF(WBS!$C29="","",IF(AND(WBS!$E29&lt;&gt;"",F$4&gt;=WBS!$E29,F$4&lt;=WBS!$F29),"■",IF(AND(F$4&gt;=WBS!$C29,F$4&lt;=WBS!$D29),"□","")))</f>
         <v/>
       </c>
-      <c r="G28" s="22" t="str">
+      <c r="G28" s="24" t="str">
         <f>IF(WBS!$C29="","",IF(AND(WBS!$E29&lt;&gt;"",G$4&gt;=WBS!$E29,G$4&lt;=WBS!$F29),"■",IF(AND(G$4&gt;=WBS!$C29,G$4&lt;=WBS!$D29),"□","")))</f>
         <v/>
       </c>
-      <c r="H28" s="22" t="str">
+      <c r="H28" s="24" t="str">
         <f>IF(WBS!$C29="","",IF(AND(WBS!$E29&lt;&gt;"",H$4&gt;=WBS!$E29,H$4&lt;=WBS!$F29),"■",IF(AND(H$4&gt;=WBS!$C29,H$4&lt;=WBS!$D29),"□","")))</f>
         <v/>
       </c>
-      <c r="I28" s="22" t="str">
+      <c r="I28" s="24" t="str">
         <f>IF(WBS!$C29="","",IF(AND(WBS!$E29&lt;&gt;"",I$4&gt;=WBS!$E29,I$4&lt;=WBS!$F29),"■",IF(AND(I$4&gt;=WBS!$C29,I$4&lt;=WBS!$D29),"□","")))</f>
         <v/>
       </c>
-      <c r="J28" s="22" t="str">
+      <c r="J28" s="24" t="str">
         <f>IF(WBS!$C29="","",IF(AND(WBS!$E29&lt;&gt;"",J$4&gt;=WBS!$E29,J$4&lt;=WBS!$F29),"■",IF(AND(J$4&gt;=WBS!$C29,J$4&lt;=WBS!$D29),"□","")))</f>
         <v/>
       </c>
-      <c r="K28" s="22" t="str">
+      <c r="K28" s="24" t="str">
         <f>IF(WBS!$C29="","",IF(AND(WBS!$E29&lt;&gt;"",K$4&gt;=WBS!$E29,K$4&lt;=WBS!$F29),"■",IF(AND(K$4&gt;=WBS!$C29,K$4&lt;=WBS!$D29),"□","")))</f>
         <v/>
       </c>
-      <c r="L28" s="22" t="str">
+      <c r="L28" s="24" t="str">
         <f>IF(WBS!$C29="","",IF(AND(WBS!$E29&lt;&gt;"",L$4&gt;=WBS!$E29,L$4&lt;=WBS!$F29),"■",IF(AND(L$4&gt;=WBS!$C29,L$4&lt;=WBS!$D29),"□","")))</f>
         <v/>
       </c>
-      <c r="M28" s="22" t="str">
+      <c r="M28" s="24" t="str">
         <f>IF(WBS!$C29="","",IF(AND(WBS!$E29&lt;&gt;"",M$4&gt;=WBS!$E29,M$4&lt;=WBS!$F29),"■",IF(AND(M$4&gt;=WBS!$C29,M$4&lt;=WBS!$D29),"□","")))</f>
         <v/>
       </c>
-      <c r="N28" s="22" t="str">
+      <c r="N28" s="24" t="str">
         <f>IF(WBS!$C29="","",IF(AND(WBS!$E29&lt;&gt;"",N$4&gt;=WBS!$E29,N$4&lt;=WBS!$F29),"■",IF(AND(N$4&gt;=WBS!$C29,N$4&lt;=WBS!$D29),"□","")))</f>
         <v/>
       </c>
-      <c r="O28" s="22" t="str">
+      <c r="O28" s="24" t="str">
         <f>IF(WBS!$C29="","",IF(AND(WBS!$E29&lt;&gt;"",O$4&gt;=WBS!$E29,O$4&lt;=WBS!$F29),"■",IF(AND(O$4&gt;=WBS!$C29,O$4&lt;=WBS!$D29),"□","")))</f>
         <v/>
       </c>
-      <c r="P28" s="22" t="str">
+      <c r="P28" s="24" t="str">
         <f>IF(WBS!$C29="","",IF(AND(WBS!$E29&lt;&gt;"",P$4&gt;=WBS!$E29,P$4&lt;=WBS!$F29),"■",IF(AND(P$4&gt;=WBS!$C29,P$4&lt;=WBS!$D29),"□","")))</f>
         <v/>
       </c>
-      <c r="Q28" s="22" t="str">
+      <c r="Q28" s="24" t="str">
         <f>IF(WBS!$C29="","",IF(AND(WBS!$E29&lt;&gt;"",Q$4&gt;=WBS!$E29,Q$4&lt;=WBS!$F29),"■",IF(AND(Q$4&gt;=WBS!$C29,Q$4&lt;=WBS!$D29),"□","")))</f>
         <v/>
       </c>
-      <c r="R28" s="22" t="str">
+      <c r="R28" s="24" t="str">
         <f>IF(WBS!$C29="","",IF(AND(WBS!$E29&lt;&gt;"",R$4&gt;=WBS!$E29,R$4&lt;=WBS!$F29),"■",IF(AND(R$4&gt;=WBS!$C29,R$4&lt;=WBS!$D29),"□","")))</f>
         <v/>
       </c>
-      <c r="S28" s="22" t="str">
+      <c r="S28" s="24" t="str">
         <f>IF(WBS!$C29="","",IF(AND(WBS!$E29&lt;&gt;"",S$4&gt;=WBS!$E29,S$4&lt;=WBS!$F29),"■",IF(AND(S$4&gt;=WBS!$C29,S$4&lt;=WBS!$D29),"□","")))</f>
         <v>□</v>
       </c>
-      <c r="T28" s="22" t="str">
+      <c r="T28" s="24" t="str">
         <f>IF(WBS!$C29="","",IF(AND(WBS!$E29&lt;&gt;"",T$4&gt;=WBS!$E29,T$4&lt;=WBS!$F29),"■",IF(AND(T$4&gt;=WBS!$C29,T$4&lt;=WBS!$D29),"□","")))</f>
         <v>□</v>
       </c>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A29" s="21" t="str">
+      <c r="A29" s="23" t="str">
         <f>WBS!A30</f>
         <v>5.1</v>
       </c>
-      <c r="B29" s="21" t="str">
+      <c r="B29" s="23" t="str">
         <f>WBS!B30</f>
         <v>Làm slide (≤ 15 slide nội dung)</v>
       </c>
-      <c r="C29" s="22" t="str">
+      <c r="C29" s="24" t="str">
         <f>IF(WBS!$C30="","",IF(AND(WBS!$E30&lt;&gt;"",C$4&gt;=WBS!$E30,C$4&lt;=WBS!$F30),"■",IF(AND(C$4&gt;=WBS!$C30,C$4&lt;=WBS!$D30),"□","")))</f>
         <v/>
       </c>
-      <c r="D29" s="22" t="str">
+      <c r="D29" s="24" t="str">
         <f>IF(WBS!$C30="","",IF(AND(WBS!$E30&lt;&gt;"",D$4&gt;=WBS!$E30,D$4&lt;=WBS!$F30),"■",IF(AND(D$4&gt;=WBS!$C30,D$4&lt;=WBS!$D30),"□","")))</f>
         <v/>
       </c>
-      <c r="E29" s="22" t="str">
+      <c r="E29" s="24" t="str">
         <f>IF(WBS!$C30="","",IF(AND(WBS!$E30&lt;&gt;"",E$4&gt;=WBS!$E30,E$4&lt;=WBS!$F30),"■",IF(AND(E$4&gt;=WBS!$C30,E$4&lt;=WBS!$D30),"□","")))</f>
         <v/>
       </c>
-      <c r="F29" s="22" t="str">
+      <c r="F29" s="24" t="str">
         <f>IF(WBS!$C30="","",IF(AND(WBS!$E30&lt;&gt;"",F$4&gt;=WBS!$E30,F$4&lt;=WBS!$F30),"■",IF(AND(F$4&gt;=WBS!$C30,F$4&lt;=WBS!$D30),"□","")))</f>
         <v/>
       </c>
-      <c r="G29" s="22" t="str">
+      <c r="G29" s="24" t="str">
         <f>IF(WBS!$C30="","",IF(AND(WBS!$E30&lt;&gt;"",G$4&gt;=WBS!$E30,G$4&lt;=WBS!$F30),"■",IF(AND(G$4&gt;=WBS!$C30,G$4&lt;=WBS!$D30),"□","")))</f>
         <v/>
       </c>
-      <c r="H29" s="22" t="str">
+      <c r="H29" s="24" t="str">
         <f>IF(WBS!$C30="","",IF(AND(WBS!$E30&lt;&gt;"",H$4&gt;=WBS!$E30,H$4&lt;=WBS!$F30),"■",IF(AND(H$4&gt;=WBS!$C30,H$4&lt;=WBS!$D30),"□","")))</f>
         <v/>
       </c>
-      <c r="I29" s="22" t="str">
+      <c r="I29" s="24" t="str">
         <f>IF(WBS!$C30="","",IF(AND(WBS!$E30&lt;&gt;"",I$4&gt;=WBS!$E30,I$4&lt;=WBS!$F30),"■",IF(AND(I$4&gt;=WBS!$C30,I$4&lt;=WBS!$D30),"□","")))</f>
         <v/>
       </c>
-      <c r="J29" s="22" t="str">
+      <c r="J29" s="24" t="str">
         <f>IF(WBS!$C30="","",IF(AND(WBS!$E30&lt;&gt;"",J$4&gt;=WBS!$E30,J$4&lt;=WBS!$F30),"■",IF(AND(J$4&gt;=WBS!$C30,J$4&lt;=WBS!$D30),"□","")))</f>
         <v/>
       </c>
-      <c r="K29" s="22" t="str">
+      <c r="K29" s="24" t="str">
         <f>IF(WBS!$C30="","",IF(AND(WBS!$E30&lt;&gt;"",K$4&gt;=WBS!$E30,K$4&lt;=WBS!$F30),"■",IF(AND(K$4&gt;=WBS!$C30,K$4&lt;=WBS!$D30),"□","")))</f>
         <v/>
       </c>
-      <c r="L29" s="22" t="str">
+      <c r="L29" s="24" t="str">
         <f>IF(WBS!$C30="","",IF(AND(WBS!$E30&lt;&gt;"",L$4&gt;=WBS!$E30,L$4&lt;=WBS!$F30),"■",IF(AND(L$4&gt;=WBS!$C30,L$4&lt;=WBS!$D30),"□","")))</f>
         <v/>
       </c>
-      <c r="M29" s="22" t="str">
+      <c r="M29" s="24" t="str">
         <f>IF(WBS!$C30="","",IF(AND(WBS!$E30&lt;&gt;"",M$4&gt;=WBS!$E30,M$4&lt;=WBS!$F30),"■",IF(AND(M$4&gt;=WBS!$C30,M$4&lt;=WBS!$D30),"□","")))</f>
         <v/>
       </c>
-      <c r="N29" s="22" t="str">
+      <c r="N29" s="24" t="str">
         <f>IF(WBS!$C30="","",IF(AND(WBS!$E30&lt;&gt;"",N$4&gt;=WBS!$E30,N$4&lt;=WBS!$F30),"■",IF(AND(N$4&gt;=WBS!$C30,N$4&lt;=WBS!$D30),"□","")))</f>
         <v/>
       </c>
-      <c r="O29" s="22" t="str">
+      <c r="O29" s="24" t="str">
         <f>IF(WBS!$C30="","",IF(AND(WBS!$E30&lt;&gt;"",O$4&gt;=WBS!$E30,O$4&lt;=WBS!$F30),"■",IF(AND(O$4&gt;=WBS!$C30,O$4&lt;=WBS!$D30),"□","")))</f>
         <v/>
       </c>
-      <c r="P29" s="22" t="str">
+      <c r="P29" s="24" t="str">
         <f>IF(WBS!$C30="","",IF(AND(WBS!$E30&lt;&gt;"",P$4&gt;=WBS!$E30,P$4&lt;=WBS!$F30),"■",IF(AND(P$4&gt;=WBS!$C30,P$4&lt;=WBS!$D30),"□","")))</f>
         <v/>
       </c>
-      <c r="Q29" s="22" t="str">
+      <c r="Q29" s="24" t="str">
         <f>IF(WBS!$C30="","",IF(AND(WBS!$E30&lt;&gt;"",Q$4&gt;=WBS!$E30,Q$4&lt;=WBS!$F30),"■",IF(AND(Q$4&gt;=WBS!$C30,Q$4&lt;=WBS!$D30),"□","")))</f>
         <v/>
       </c>
-      <c r="R29" s="22" t="str">
+      <c r="R29" s="24" t="str">
         <f>IF(WBS!$C30="","",IF(AND(WBS!$E30&lt;&gt;"",R$4&gt;=WBS!$E30,R$4&lt;=WBS!$F30),"■",IF(AND(R$4&gt;=WBS!$C30,R$4&lt;=WBS!$D30),"□","")))</f>
         <v/>
       </c>
-      <c r="S29" s="22" t="str">
+      <c r="S29" s="24" t="str">
         <f>IF(WBS!$C30="","",IF(AND(WBS!$E30&lt;&gt;"",S$4&gt;=WBS!$E30,S$4&lt;=WBS!$F30),"■",IF(AND(S$4&gt;=WBS!$C30,S$4&lt;=WBS!$D30),"□","")))</f>
         <v>□</v>
       </c>
-      <c r="T29" s="22" t="str">
+      <c r="T29" s="24" t="str">
         <f>IF(WBS!$C30="","",IF(AND(WBS!$E30&lt;&gt;"",T$4&gt;=WBS!$E30,T$4&lt;=WBS!$F30),"■",IF(AND(T$4&gt;=WBS!$C30,T$4&lt;=WBS!$D30),"□","")))</f>
         <v/>
       </c>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A30" s="21" t="str">
+      <c r="A30" s="23" t="str">
         <f>WBS!A31</f>
         <v>5.2</v>
       </c>
-      <c r="B30" s="21" t="str">
+      <c r="B30" s="23" t="str">
         <f>WBS!B31</f>
         <v>Tập thuyết trình, soạn câu hỏi</v>
       </c>
-      <c r="C30" s="22" t="str">
+      <c r="C30" s="24" t="str">
         <f>IF(WBS!$C31="","",IF(AND(WBS!$E31&lt;&gt;"",C$4&gt;=WBS!$E31,C$4&lt;=WBS!$F31),"■",IF(AND(C$4&gt;=WBS!$C31,C$4&lt;=WBS!$D31),"□","")))</f>
         <v/>
       </c>
-      <c r="D30" s="22" t="str">
+      <c r="D30" s="24" t="str">
         <f>IF(WBS!$C31="","",IF(AND(WBS!$E31&lt;&gt;"",D$4&gt;=WBS!$E31,D$4&lt;=WBS!$F31),"■",IF(AND(D$4&gt;=WBS!$C31,D$4&lt;=WBS!$D31),"□","")))</f>
         <v/>
       </c>
-      <c r="E30" s="22" t="str">
+      <c r="E30" s="24" t="str">
         <f>IF(WBS!$C31="","",IF(AND(WBS!$E31&lt;&gt;"",E$4&gt;=WBS!$E31,E$4&lt;=WBS!$F31),"■",IF(AND(E$4&gt;=WBS!$C31,E$4&lt;=WBS!$D31),"□","")))</f>
         <v/>
       </c>
-      <c r="F30" s="22" t="str">
+      <c r="F30" s="24" t="str">
         <f>IF(WBS!$C31="","",IF(AND(WBS!$E31&lt;&gt;"",F$4&gt;=WBS!$E31,F$4&lt;=WBS!$F31),"■",IF(AND(F$4&gt;=WBS!$C31,F$4&lt;=WBS!$D31),"□","")))</f>
         <v/>
       </c>
-      <c r="G30" s="22" t="str">
+      <c r="G30" s="24" t="str">
         <f>IF(WBS!$C31="","",IF(AND(WBS!$E31&lt;&gt;"",G$4&gt;=WBS!$E31,G$4&lt;=WBS!$F31),"■",IF(AND(G$4&gt;=WBS!$C31,G$4&lt;=WBS!$D31),"□","")))</f>
         <v/>
       </c>
-      <c r="H30" s="22" t="str">
+      <c r="H30" s="24" t="str">
         <f>IF(WBS!$C31="","",IF(AND(WBS!$E31&lt;&gt;"",H$4&gt;=WBS!$E31,H$4&lt;=WBS!$F31),"■",IF(AND(H$4&gt;=WBS!$C31,H$4&lt;=WBS!$D31),"□","")))</f>
         <v/>
       </c>
-      <c r="I30" s="22" t="str">
+      <c r="I30" s="24" t="str">
         <f>IF(WBS!$C31="","",IF(AND(WBS!$E31&lt;&gt;"",I$4&gt;=WBS!$E31,I$4&lt;=WBS!$F31),"■",IF(AND(I$4&gt;=WBS!$C31,I$4&lt;=WBS!$D31),"□","")))</f>
         <v/>
       </c>
-      <c r="J30" s="22" t="str">
+      <c r="J30" s="24" t="str">
         <f>IF(WBS!$C31="","",IF(AND(WBS!$E31&lt;&gt;"",J$4&gt;=WBS!$E31,J$4&lt;=WBS!$F31),"■",IF(AND(J$4&gt;=WBS!$C31,J$4&lt;=WBS!$D31),"□","")))</f>
         <v/>
       </c>
-      <c r="K30" s="22" t="str">
+      <c r="K30" s="24" t="str">
         <f>IF(WBS!$C31="","",IF(AND(WBS!$E31&lt;&gt;"",K$4&gt;=WBS!$E31,K$4&lt;=WBS!$F31),"■",IF(AND(K$4&gt;=WBS!$C31,K$4&lt;=WBS!$D31),"□","")))</f>
         <v/>
       </c>
-      <c r="L30" s="22" t="str">
+      <c r="L30" s="24" t="str">
         <f>IF(WBS!$C31="","",IF(AND(WBS!$E31&lt;&gt;"",L$4&gt;=WBS!$E31,L$4&lt;=WBS!$F31),"■",IF(AND(L$4&gt;=WBS!$C31,L$4&lt;=WBS!$D31),"□","")))</f>
         <v/>
       </c>
-      <c r="M30" s="22" t="str">
+      <c r="M30" s="24" t="str">
         <f>IF(WBS!$C31="","",IF(AND(WBS!$E31&lt;&gt;"",M$4&gt;=WBS!$E31,M$4&lt;=WBS!$F31),"■",IF(AND(M$4&gt;=WBS!$C31,M$4&lt;=WBS!$D31),"□","")))</f>
         <v/>
       </c>
-      <c r="N30" s="22" t="str">
+      <c r="N30" s="24" t="str">
         <f>IF(WBS!$C31="","",IF(AND(WBS!$E31&lt;&gt;"",N$4&gt;=WBS!$E31,N$4&lt;=WBS!$F31),"■",IF(AND(N$4&gt;=WBS!$C31,N$4&lt;=WBS!$D31),"□","")))</f>
         <v/>
       </c>
-      <c r="O30" s="22" t="str">
+      <c r="O30" s="24" t="str">
         <f>IF(WBS!$C31="","",IF(AND(WBS!$E31&lt;&gt;"",O$4&gt;=WBS!$E31,O$4&lt;=WBS!$F31),"■",IF(AND(O$4&gt;=WBS!$C31,O$4&lt;=WBS!$D31),"□","")))</f>
         <v/>
       </c>
-      <c r="P30" s="22" t="str">
+      <c r="P30" s="24" t="str">
         <f>IF(WBS!$C31="","",IF(AND(WBS!$E31&lt;&gt;"",P$4&gt;=WBS!$E31,P$4&lt;=WBS!$F31),"■",IF(AND(P$4&gt;=WBS!$C31,P$4&lt;=WBS!$D31),"□","")))</f>
         <v/>
       </c>
-      <c r="Q30" s="22" t="str">
+      <c r="Q30" s="24" t="str">
         <f>IF(WBS!$C31="","",IF(AND(WBS!$E31&lt;&gt;"",Q$4&gt;=WBS!$E31,Q$4&lt;=WBS!$F31),"■",IF(AND(Q$4&gt;=WBS!$C31,Q$4&lt;=WBS!$D31),"□","")))</f>
         <v/>
       </c>
-      <c r="R30" s="22" t="str">
+      <c r="R30" s="24" t="str">
         <f>IF(WBS!$C31="","",IF(AND(WBS!$E31&lt;&gt;"",R$4&gt;=WBS!$E31,R$4&lt;=WBS!$F31),"■",IF(AND(R$4&gt;=WBS!$C31,R$4&lt;=WBS!$D31),"□","")))</f>
         <v/>
       </c>
-      <c r="S30" s="22" t="str">
+      <c r="S30" s="24" t="str">
         <f>IF(WBS!$C31="","",IF(AND(WBS!$E31&lt;&gt;"",S$4&gt;=WBS!$E31,S$4&lt;=WBS!$F31),"■",IF(AND(S$4&gt;=WBS!$C31,S$4&lt;=WBS!$D31),"□","")))</f>
         <v>□</v>
       </c>
-      <c r="T30" s="22" t="str">
+      <c r="T30" s="24" t="str">
         <f>IF(WBS!$C31="","",IF(AND(WBS!$E31&lt;&gt;"",T$4&gt;=WBS!$E31,T$4&lt;=WBS!$F31),"■",IF(AND(T$4&gt;=WBS!$C31,T$4&lt;=WBS!$D31),"□","")))</f>
         <v/>
       </c>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A31" s="21" t="str">
+      <c r="A31" s="23" t="str">
         <f>WBS!A32</f>
         <v>5.3</v>
       </c>
-      <c r="B31" s="21" t="str">
+      <c r="B31" s="23" t="str">
         <f>WBS!B32</f>
         <v>Nộp bài</v>
       </c>
-      <c r="C31" s="22" t="str">
+      <c r="C31" s="24" t="str">
         <f>IF(WBS!$C32="","",IF(AND(WBS!$E32&lt;&gt;"",C$4&gt;=WBS!$E32,C$4&lt;=WBS!$F32),"■",IF(AND(C$4&gt;=WBS!$C32,C$4&lt;=WBS!$D32),"□","")))</f>
         <v/>
       </c>
-      <c r="D31" s="22" t="str">
+      <c r="D31" s="24" t="str">
         <f>IF(WBS!$C32="","",IF(AND(WBS!$E32&lt;&gt;"",D$4&gt;=WBS!$E32,D$4&lt;=WBS!$F32),"■",IF(AND(D$4&gt;=WBS!$C32,D$4&lt;=WBS!$D32),"□","")))</f>
         <v/>
       </c>
-      <c r="E31" s="22" t="str">
+      <c r="E31" s="24" t="str">
         <f>IF(WBS!$C32="","",IF(AND(WBS!$E32&lt;&gt;"",E$4&gt;=WBS!$E32,E$4&lt;=WBS!$F32),"■",IF(AND(E$4&gt;=WBS!$C32,E$4&lt;=WBS!$D32),"□","")))</f>
         <v/>
       </c>
-      <c r="F31" s="22" t="str">
+      <c r="F31" s="24" t="str">
         <f>IF(WBS!$C32="","",IF(AND(WBS!$E32&lt;&gt;"",F$4&gt;=WBS!$E32,F$4&lt;=WBS!$F32),"■",IF(AND(F$4&gt;=WBS!$C32,F$4&lt;=WBS!$D32),"□","")))</f>
         <v/>
       </c>
-      <c r="G31" s="22" t="str">
+      <c r="G31" s="24" t="str">
         <f>IF(WBS!$C32="","",IF(AND(WBS!$E32&lt;&gt;"",G$4&gt;=WBS!$E32,G$4&lt;=WBS!$F32),"■",IF(AND(G$4&gt;=WBS!$C32,G$4&lt;=WBS!$D32),"□","")))</f>
         <v/>
       </c>
-      <c r="H31" s="22" t="str">
+      <c r="H31" s="24" t="str">
         <f>IF(WBS!$C32="","",IF(AND(WBS!$E32&lt;&gt;"",H$4&gt;=WBS!$E32,H$4&lt;=WBS!$F32),"■",IF(AND(H$4&gt;=WBS!$C32,H$4&lt;=WBS!$D32),"□","")))</f>
         <v/>
       </c>
-      <c r="I31" s="22" t="str">
+      <c r="I31" s="24" t="str">
         <f>IF(WBS!$C32="","",IF(AND(WBS!$E32&lt;&gt;"",I$4&gt;=WBS!$E32,I$4&lt;=WBS!$F32),"■",IF(AND(I$4&gt;=WBS!$C32,I$4&lt;=WBS!$D32),"□","")))</f>
         <v/>
       </c>
-      <c r="J31" s="22" t="str">
+      <c r="J31" s="24" t="str">
         <f>IF(WBS!$C32="","",IF(AND(WBS!$E32&lt;&gt;"",J$4&gt;=WBS!$E32,J$4&lt;=WBS!$F32),"■",IF(AND(J$4&gt;=WBS!$C32,J$4&lt;=WBS!$D32),"□","")))</f>
         <v/>
       </c>
-      <c r="K31" s="22" t="str">
+      <c r="K31" s="24" t="str">
         <f>IF(WBS!$C32="","",IF(AND(WBS!$E32&lt;&gt;"",K$4&gt;=WBS!$E32,K$4&lt;=WBS!$F32),"■",IF(AND(K$4&gt;=WBS!$C32,K$4&lt;=WBS!$D32),"□","")))</f>
         <v/>
       </c>
-      <c r="L31" s="22" t="str">
+      <c r="L31" s="24" t="str">
         <f>IF(WBS!$C32="","",IF(AND(WBS!$E32&lt;&gt;"",L$4&gt;=WBS!$E32,L$4&lt;=WBS!$F32),"■",IF(AND(L$4&gt;=WBS!$C32,L$4&lt;=WBS!$D32),"□","")))</f>
         <v/>
       </c>
-      <c r="M31" s="22" t="str">
+      <c r="M31" s="24" t="str">
         <f>IF(WBS!$C32="","",IF(AND(WBS!$E32&lt;&gt;"",M$4&gt;=WBS!$E32,M$4&lt;=WBS!$F32),"■",IF(AND(M$4&gt;=WBS!$C32,M$4&lt;=WBS!$D32),"□","")))</f>
         <v/>
       </c>
-      <c r="N31" s="22" t="str">
+      <c r="N31" s="24" t="str">
         <f>IF(WBS!$C32="","",IF(AND(WBS!$E32&lt;&gt;"",N$4&gt;=WBS!$E32,N$4&lt;=WBS!$F32),"■",IF(AND(N$4&gt;=WBS!$C32,N$4&lt;=WBS!$D32),"□","")))</f>
         <v/>
       </c>
-      <c r="O31" s="22" t="str">
+      <c r="O31" s="24" t="str">
         <f>IF(WBS!$C32="","",IF(AND(WBS!$E32&lt;&gt;"",O$4&gt;=WBS!$E32,O$4&lt;=WBS!$F32),"■",IF(AND(O$4&gt;=WBS!$C32,O$4&lt;=WBS!$D32),"□","")))</f>
         <v/>
       </c>
-      <c r="P31" s="22" t="str">
+      <c r="P31" s="24" t="str">
         <f>IF(WBS!$C32="","",IF(AND(WBS!$E32&lt;&gt;"",P$4&gt;=WBS!$E32,P$4&lt;=WBS!$F32),"■",IF(AND(P$4&gt;=WBS!$C32,P$4&lt;=WBS!$D32),"□","")))</f>
         <v/>
       </c>
-      <c r="Q31" s="22" t="str">
+      <c r="Q31" s="24" t="str">
         <f>IF(WBS!$C32="","",IF(AND(WBS!$E32&lt;&gt;"",Q$4&gt;=WBS!$E32,Q$4&lt;=WBS!$F32),"■",IF(AND(Q$4&gt;=WBS!$C32,Q$4&lt;=WBS!$D32),"□","")))</f>
         <v/>
       </c>
-      <c r="R31" s="22" t="str">
+      <c r="R31" s="24" t="str">
         <f>IF(WBS!$C32="","",IF(AND(WBS!$E32&lt;&gt;"",R$4&gt;=WBS!$E32,R$4&lt;=WBS!$F32),"■",IF(AND(R$4&gt;=WBS!$C32,R$4&lt;=WBS!$D32),"□","")))</f>
         <v/>
       </c>
-      <c r="S31" s="22" t="str">
+      <c r="S31" s="24" t="str">
         <f>IF(WBS!$C32="","",IF(AND(WBS!$E32&lt;&gt;"",S$4&gt;=WBS!$E32,S$4&lt;=WBS!$F32),"■",IF(AND(S$4&gt;=WBS!$C32,S$4&lt;=WBS!$D32),"□","")))</f>
         <v/>
       </c>
-      <c r="T31" s="22" t="str">
+      <c r="T31" s="24" t="str">
         <f>IF(WBS!$C32="","",IF(AND(WBS!$E32&lt;&gt;"",T$4&gt;=WBS!$E32,T$4&lt;=WBS!$F32),"■",IF(AND(T$4&gt;=WBS!$C32,T$4&lt;=WBS!$D32),"□","")))</f>
         <v>□</v>
       </c>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A32" s="21" t="str">
+      <c r="A32" s="23" t="str">
         <f>WBS!A33</f>
         <v>6</v>
       </c>
-      <c r="B32" s="21" t="str">
+      <c r="B32" s="23" t="str">
         <f>WBS!B33</f>
         <v>Quản lý dự án</v>
       </c>
-      <c r="C32" s="22" t="str">
+      <c r="C32" s="24" t="str">
         <f>IF(WBS!$C33="","",IF(AND(WBS!$E33&lt;&gt;"",C$4&gt;=WBS!$E33,C$4&lt;=WBS!$F33),"■",IF(AND(C$4&gt;=WBS!$C33,C$4&lt;=WBS!$D33),"□","")))</f>
         <v/>
       </c>
-      <c r="D32" s="22" t="str">
+      <c r="D32" s="24" t="str">
         <f>IF(WBS!$C33="","",IF(AND(WBS!$E33&lt;&gt;"",D$4&gt;=WBS!$E33,D$4&lt;=WBS!$F33),"■",IF(AND(D$4&gt;=WBS!$C33,D$4&lt;=WBS!$D33),"□","")))</f>
         <v/>
       </c>
-      <c r="E32" s="22" t="str">
+      <c r="E32" s="24" t="str">
         <f>IF(WBS!$C33="","",IF(AND(WBS!$E33&lt;&gt;"",E$4&gt;=WBS!$E33,E$4&lt;=WBS!$F33),"■",IF(AND(E$4&gt;=WBS!$C33,E$4&lt;=WBS!$D33),"□","")))</f>
         <v/>
       </c>
-      <c r="F32" s="22" t="str">
+      <c r="F32" s="24" t="str">
         <f>IF(WBS!$C33="","",IF(AND(WBS!$E33&lt;&gt;"",F$4&gt;=WBS!$E33,F$4&lt;=WBS!$F33),"■",IF(AND(F$4&gt;=WBS!$C33,F$4&lt;=WBS!$D33),"□","")))</f>
         <v/>
       </c>
-      <c r="G32" s="22" t="str">
+      <c r="G32" s="24" t="str">
         <f>IF(WBS!$C33="","",IF(AND(WBS!$E33&lt;&gt;"",G$4&gt;=WBS!$E33,G$4&lt;=WBS!$F33),"■",IF(AND(G$4&gt;=WBS!$C33,G$4&lt;=WBS!$D33),"□","")))</f>
         <v/>
       </c>
-      <c r="H32" s="22" t="str">
+      <c r="H32" s="24" t="str">
         <f>IF(WBS!$C33="","",IF(AND(WBS!$E33&lt;&gt;"",H$4&gt;=WBS!$E33,H$4&lt;=WBS!$F33),"■",IF(AND(H$4&gt;=WBS!$C33,H$4&lt;=WBS!$D33),"□","")))</f>
         <v/>
       </c>
-      <c r="I32" s="22" t="str">
+      <c r="I32" s="24" t="str">
         <f>IF(WBS!$C33="","",IF(AND(WBS!$E33&lt;&gt;"",I$4&gt;=WBS!$E33,I$4&lt;=WBS!$F33),"■",IF(AND(I$4&gt;=WBS!$C33,I$4&lt;=WBS!$D33),"□","")))</f>
         <v/>
       </c>
-      <c r="J32" s="22" t="str">
+      <c r="J32" s="24" t="str">
         <f>IF(WBS!$C33="","",IF(AND(WBS!$E33&lt;&gt;"",J$4&gt;=WBS!$E33,J$4&lt;=WBS!$F33),"■",IF(AND(J$4&gt;=WBS!$C33,J$4&lt;=WBS!$D33),"□","")))</f>
         <v/>
       </c>
-      <c r="K32" s="22" t="str">
+      <c r="K32" s="24" t="str">
         <f>IF(WBS!$C33="","",IF(AND(WBS!$E33&lt;&gt;"",K$4&gt;=WBS!$E33,K$4&lt;=WBS!$F33),"■",IF(AND(K$4&gt;=WBS!$C33,K$4&lt;=WBS!$D33),"□","")))</f>
         <v>□</v>
       </c>
-      <c r="L32" s="22" t="str">
+      <c r="L32" s="24" t="str">
         <f>IF(WBS!$C33="","",IF(AND(WBS!$E33&lt;&gt;"",L$4&gt;=WBS!$E33,L$4&lt;=WBS!$F33),"■",IF(AND(L$4&gt;=WBS!$C33,L$4&lt;=WBS!$D33),"□","")))</f>
         <v/>
       </c>
-      <c r="M32" s="22" t="str">
+      <c r="M32" s="24" t="str">
         <f>IF(WBS!$C33="","",IF(AND(WBS!$E33&lt;&gt;"",M$4&gt;=WBS!$E33,M$4&lt;=WBS!$F33),"■",IF(AND(M$4&gt;=WBS!$C33,M$4&lt;=WBS!$D33),"□","")))</f>
         <v/>
       </c>
-      <c r="N32" s="22" t="str">
+      <c r="N32" s="24" t="str">
         <f>IF(WBS!$C33="","",IF(AND(WBS!$E33&lt;&gt;"",N$4&gt;=WBS!$E33,N$4&lt;=WBS!$F33),"■",IF(AND(N$4&gt;=WBS!$C33,N$4&lt;=WBS!$D33),"□","")))</f>
         <v/>
       </c>
-      <c r="O32" s="22" t="str">
+      <c r="O32" s="24" t="str">
         <f>IF(WBS!$C33="","",IF(AND(WBS!$E33&lt;&gt;"",O$4&gt;=WBS!$E33,O$4&lt;=WBS!$F33),"■",IF(AND(O$4&gt;=WBS!$C33,O$4&lt;=WBS!$D33),"□","")))</f>
         <v/>
       </c>
-      <c r="P32" s="22" t="str">
+      <c r="P32" s="24" t="str">
         <f>IF(WBS!$C33="","",IF(AND(WBS!$E33&lt;&gt;"",P$4&gt;=WBS!$E33,P$4&lt;=WBS!$F33),"■",IF(AND(P$4&gt;=WBS!$C33,P$4&lt;=WBS!$D33),"□","")))</f>
         <v/>
       </c>
-      <c r="Q32" s="22" t="str">
+      <c r="Q32" s="24" t="str">
         <f>IF(WBS!$C33="","",IF(AND(WBS!$E33&lt;&gt;"",Q$4&gt;=WBS!$E33,Q$4&lt;=WBS!$F33),"■",IF(AND(Q$4&gt;=WBS!$C33,Q$4&lt;=WBS!$D33),"□","")))</f>
         <v/>
       </c>
-      <c r="R32" s="22" t="str">
+      <c r="R32" s="24" t="str">
         <f>IF(WBS!$C33="","",IF(AND(WBS!$E33&lt;&gt;"",R$4&gt;=WBS!$E33,R$4&lt;=WBS!$F33),"■",IF(AND(R$4&gt;=WBS!$C33,R$4&lt;=WBS!$D33),"□","")))</f>
         <v/>
       </c>
-      <c r="S32" s="22" t="str">
+      <c r="S32" s="24" t="str">
         <f>IF(WBS!$C33="","",IF(AND(WBS!$E33&lt;&gt;"",S$4&gt;=WBS!$E33,S$4&lt;=WBS!$F33),"■",IF(AND(S$4&gt;=WBS!$C33,S$4&lt;=WBS!$D33),"□","")))</f>
         <v/>
       </c>
-      <c r="T32" s="22" t="str">
+      <c r="T32" s="24" t="str">
         <f>IF(WBS!$C33="","",IF(AND(WBS!$E33&lt;&gt;"",T$4&gt;=WBS!$E33,T$4&lt;=WBS!$F33),"■",IF(AND(T$4&gt;=WBS!$C33,T$4&lt;=WBS!$D33),"□","")))</f>
         <v/>
       </c>
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A33" s="21" t="str">
+      <c r="A33" s="23" t="str">
         <f>WBS!A34</f>
         <v>6.1</v>
       </c>
-      <c r="B33" s="21" t="str">
+      <c r="B33" s="23" t="str">
         <f>WBS!B34</f>
         <v>Lập WBS, Gantt, sổ rủi ro (Excel, MS Project)</v>
       </c>
-      <c r="C33" s="22" t="str">
+      <c r="C33" s="24" t="str">
         <f>IF(WBS!$C34="","",IF(AND(WBS!$E34&lt;&gt;"",C$4&gt;=WBS!$E34,C$4&lt;=WBS!$F34),"■",IF(AND(C$4&gt;=WBS!$C34,C$4&lt;=WBS!$D34),"□","")))</f>
         <v/>
       </c>
-      <c r="D33" s="22" t="str">
+      <c r="D33" s="24" t="str">
         <f>IF(WBS!$C34="","",IF(AND(WBS!$E34&lt;&gt;"",D$4&gt;=WBS!$E34,D$4&lt;=WBS!$F34),"■",IF(AND(D$4&gt;=WBS!$C34,D$4&lt;=WBS!$D34),"□","")))</f>
         <v/>
       </c>
-      <c r="E33" s="22" t="str">
+      <c r="E33" s="24" t="str">
         <f>IF(WBS!$C34="","",IF(AND(WBS!$E34&lt;&gt;"",E$4&gt;=WBS!$E34,E$4&lt;=WBS!$F34),"■",IF(AND(E$4&gt;=WBS!$C34,E$4&lt;=WBS!$D34),"□","")))</f>
         <v/>
       </c>
-      <c r="F33" s="22" t="str">
+      <c r="F33" s="24" t="str">
         <f>IF(WBS!$C34="","",IF(AND(WBS!$E34&lt;&gt;"",F$4&gt;=WBS!$E34,F$4&lt;=WBS!$F34),"■",IF(AND(F$4&gt;=WBS!$C34,F$4&lt;=WBS!$D34),"□","")))</f>
         <v/>
       </c>
-      <c r="G33" s="22" t="str">
+      <c r="G33" s="24" t="str">
         <f>IF(WBS!$C34="","",IF(AND(WBS!$E34&lt;&gt;"",G$4&gt;=WBS!$E34,G$4&lt;=WBS!$F34),"■",IF(AND(G$4&gt;=WBS!$C34,G$4&lt;=WBS!$D34),"□","")))</f>
         <v/>
       </c>
-      <c r="H33" s="22" t="str">
+      <c r="H33" s="24" t="str">
         <f>IF(WBS!$C34="","",IF(AND(WBS!$E34&lt;&gt;"",H$4&gt;=WBS!$E34,H$4&lt;=WBS!$F34),"■",IF(AND(H$4&gt;=WBS!$C34,H$4&lt;=WBS!$D34),"□","")))</f>
         <v/>
       </c>
-      <c r="I33" s="22" t="str">
+      <c r="I33" s="24" t="str">
         <f>IF(WBS!$C34="","",IF(AND(WBS!$E34&lt;&gt;"",I$4&gt;=WBS!$E34,I$4&lt;=WBS!$F34),"■",IF(AND(I$4&gt;=WBS!$C34,I$4&lt;=WBS!$D34),"□","")))</f>
         <v/>
       </c>
-      <c r="J33" s="22" t="str">
+      <c r="J33" s="24" t="str">
         <f>IF(WBS!$C34="","",IF(AND(WBS!$E34&lt;&gt;"",J$4&gt;=WBS!$E34,J$4&lt;=WBS!$F34),"■",IF(AND(J$4&gt;=WBS!$C34,J$4&lt;=WBS!$D34),"□","")))</f>
         <v/>
       </c>
-      <c r="K33" s="22" t="str">
+      <c r="K33" s="24" t="str">
         <f>IF(WBS!$C34="","",IF(AND(WBS!$E34&lt;&gt;"",K$4&gt;=WBS!$E34,K$4&lt;=WBS!$F34),"■",IF(AND(K$4&gt;=WBS!$C34,K$4&lt;=WBS!$D34),"□","")))</f>
         <v>■</v>
       </c>
-      <c r="L33" s="22" t="str">
+      <c r="L33" s="24" t="str">
         <f>IF(WBS!$C34="","",IF(AND(WBS!$E34&lt;&gt;"",L$4&gt;=WBS!$E34,L$4&lt;=WBS!$F34),"■",IF(AND(L$4&gt;=WBS!$C34,L$4&lt;=WBS!$D34),"□","")))</f>
         <v/>
       </c>
-      <c r="M33" s="22" t="str">
+      <c r="M33" s="24" t="str">
         <f>IF(WBS!$C34="","",IF(AND(WBS!$E34&lt;&gt;"",M$4&gt;=WBS!$E34,M$4&lt;=WBS!$F34),"■",IF(AND(M$4&gt;=WBS!$C34,M$4&lt;=WBS!$D34),"□","")))</f>
         <v/>
       </c>
-      <c r="N33" s="22" t="str">
+      <c r="N33" s="24" t="str">
         <f>IF(WBS!$C34="","",IF(AND(WBS!$E34&lt;&gt;"",N$4&gt;=WBS!$E34,N$4&lt;=WBS!$F34),"■",IF(AND(N$4&gt;=WBS!$C34,N$4&lt;=WBS!$D34),"□","")))</f>
         <v/>
       </c>
-      <c r="O33" s="22" t="str">
+      <c r="O33" s="24" t="str">
         <f>IF(WBS!$C34="","",IF(AND(WBS!$E34&lt;&gt;"",O$4&gt;=WBS!$E34,O$4&lt;=WBS!$F34),"■",IF(AND(O$4&gt;=WBS!$C34,O$4&lt;=WBS!$D34),"□","")))</f>
         <v/>
       </c>
-      <c r="P33" s="22" t="str">
+      <c r="P33" s="24" t="str">
         <f>IF(WBS!$C34="","",IF(AND(WBS!$E34&lt;&gt;"",P$4&gt;=WBS!$E34,P$4&lt;=WBS!$F34),"■",IF(AND(P$4&gt;=WBS!$C34,P$4&lt;=WBS!$D34),"□","")))</f>
         <v/>
       </c>
-      <c r="Q33" s="22" t="str">
+      <c r="Q33" s="24" t="str">
         <f>IF(WBS!$C34="","",IF(AND(WBS!$E34&lt;&gt;"",Q$4&gt;=WBS!$E34,Q$4&lt;=WBS!$F34),"■",IF(AND(Q$4&gt;=WBS!$C34,Q$4&lt;=WBS!$D34),"□","")))</f>
         <v/>
       </c>
-      <c r="R33" s="22" t="str">
+      <c r="R33" s="24" t="str">
         <f>IF(WBS!$C34="","",IF(AND(WBS!$E34&lt;&gt;"",R$4&gt;=WBS!$E34,R$4&lt;=WBS!$F34),"■",IF(AND(R$4&gt;=WBS!$C34,R$4&lt;=WBS!$D34),"□","")))</f>
         <v/>
       </c>
-      <c r="S33" s="22" t="str">
+      <c r="S33" s="24" t="str">
         <f>IF(WBS!$C34="","",IF(AND(WBS!$E34&lt;&gt;"",S$4&gt;=WBS!$E34,S$4&lt;=WBS!$F34),"■",IF(AND(S$4&gt;=WBS!$C34,S$4&lt;=WBS!$D34),"□","")))</f>
         <v/>
       </c>
-      <c r="T33" s="22" t="str">
+      <c r="T33" s="24" t="str">
         <f>IF(WBS!$C34="","",IF(AND(WBS!$E34&lt;&gt;"",T$4&gt;=WBS!$E34,T$4&lt;=WBS!$F34),"■",IF(AND(T$4&gt;=WBS!$C34,T$4&lt;=WBS!$D34),"□","")))</f>
         <v/>
       </c>
@@ -5114,405 +5686,405 @@
   <sheetData>
     <row r="1" spans="1:11" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="K4" s="5" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A5" s="10" t="s">
-        <v>119</v>
+      <c r="A5" s="13" t="s">
+        <v>121</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="D5" s="23">
+        <v>123</v>
+      </c>
+      <c r="D5" s="25">
         <v>5</v>
       </c>
-      <c r="E5" s="23">
+      <c r="E5" s="25">
         <v>4</v>
       </c>
-      <c r="F5" s="24">
+      <c r="F5" s="26">
         <f t="shared" ref="F5:F13" si="0">D5*E5</f>
         <v>20</v>
       </c>
-      <c r="G5" s="10" t="str">
+      <c r="G5" s="13" t="str">
         <f t="shared" ref="G5:G13" si="1">IF(F5&gt;=15,"Đỏ",IF(F5&gt;=8,"Vàng","Xanh"))</f>
         <v>Đỏ</v>
       </c>
-      <c r="H5" s="23" t="s">
-        <v>122</v>
+      <c r="H5" s="25" t="s">
+        <v>124</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>123</v>
-      </c>
-      <c r="J5" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="K5" s="23" t="s">
         <v>125</v>
       </c>
+      <c r="J5" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="K5" s="25" t="s">
+        <v>127</v>
+      </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" s="10" t="s">
-        <v>126</v>
+      <c r="A6" s="13" t="s">
+        <v>128</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>128</v>
-      </c>
-      <c r="D6" s="23">
+        <v>130</v>
+      </c>
+      <c r="D6" s="25">
         <v>5</v>
       </c>
-      <c r="E6" s="23">
+      <c r="E6" s="25">
         <v>3</v>
       </c>
-      <c r="F6" s="24">
+      <c r="F6" s="26">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="G6" s="10" t="str">
+      <c r="G6" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Đỏ</v>
       </c>
-      <c r="H6" s="23" t="s">
-        <v>129</v>
+      <c r="H6" s="25" t="s">
+        <v>131</v>
       </c>
       <c r="I6" s="11" t="s">
-        <v>130</v>
-      </c>
-      <c r="J6" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="K6" s="23" t="s">
-        <v>131</v>
+        <v>132</v>
+      </c>
+      <c r="J6" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="K6" s="25" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A7" s="10" t="s">
-        <v>132</v>
+      <c r="A7" s="13" t="s">
+        <v>134</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="D7" s="23">
+        <v>136</v>
+      </c>
+      <c r="D7" s="25">
         <v>4</v>
       </c>
-      <c r="E7" s="23">
+      <c r="E7" s="25">
         <v>4</v>
       </c>
-      <c r="F7" s="24">
+      <c r="F7" s="26">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="G7" s="10" t="str">
+      <c r="G7" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Đỏ</v>
       </c>
-      <c r="H7" s="23" t="s">
-        <v>122</v>
+      <c r="H7" s="25" t="s">
+        <v>124</v>
       </c>
       <c r="I7" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="J7" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="K7" s="23" t="s">
-        <v>125</v>
+        <v>137</v>
+      </c>
+      <c r="J7" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="K7" s="25" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8" s="10" t="s">
-        <v>136</v>
+      <c r="A8" s="13" t="s">
+        <v>138</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>138</v>
-      </c>
-      <c r="D8" s="23">
+        <v>140</v>
+      </c>
+      <c r="D8" s="25">
         <v>3</v>
       </c>
-      <c r="E8" s="23">
+      <c r="E8" s="25">
         <v>3</v>
       </c>
-      <c r="F8" s="24">
+      <c r="F8" s="26">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="G8" s="10" t="str">
+      <c r="G8" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Vàng</v>
       </c>
-      <c r="H8" s="23" t="s">
-        <v>139</v>
+      <c r="H8" s="25" t="s">
+        <v>141</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="J8" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="K8" s="23" t="s">
-        <v>141</v>
+        <v>142</v>
+      </c>
+      <c r="J8" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="K8" s="25" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="10" t="s">
-        <v>142</v>
+      <c r="A9" s="13" t="s">
+        <v>144</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="D9" s="23">
+        <v>146</v>
+      </c>
+      <c r="D9" s="25">
         <v>2</v>
       </c>
-      <c r="E9" s="23">
+      <c r="E9" s="25">
         <v>4</v>
       </c>
-      <c r="F9" s="24">
+      <c r="F9" s="26">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="G9" s="10" t="str">
+      <c r="G9" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Vàng</v>
       </c>
-      <c r="H9" s="23" t="s">
-        <v>122</v>
+      <c r="H9" s="25" t="s">
+        <v>124</v>
       </c>
       <c r="I9" s="11" t="s">
-        <v>145</v>
-      </c>
-      <c r="J9" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="K9" s="23" t="s">
-        <v>141</v>
+        <v>147</v>
+      </c>
+      <c r="J9" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="K9" s="25" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A10" s="10" t="s">
-        <v>146</v>
+      <c r="A10" s="13" t="s">
+        <v>148</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>148</v>
-      </c>
-      <c r="D10" s="23">
+        <v>150</v>
+      </c>
+      <c r="D10" s="25">
         <v>3</v>
       </c>
-      <c r="E10" s="23">
+      <c r="E10" s="25">
         <v>5</v>
       </c>
-      <c r="F10" s="24">
+      <c r="F10" s="26">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="G10" s="10" t="str">
+      <c r="G10" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Đỏ</v>
       </c>
-      <c r="H10" s="23" t="s">
-        <v>122</v>
+      <c r="H10" s="25" t="s">
+        <v>124</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>149</v>
-      </c>
-      <c r="J10" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="K10" s="23" t="s">
-        <v>141</v>
+        <v>151</v>
+      </c>
+      <c r="J10" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="K10" s="25" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A11" s="10" t="s">
-        <v>150</v>
+      <c r="A11" s="13" t="s">
+        <v>152</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>152</v>
-      </c>
-      <c r="D11" s="23">
+        <v>154</v>
+      </c>
+      <c r="D11" s="25">
         <v>3</v>
       </c>
-      <c r="E11" s="23">
+      <c r="E11" s="25">
         <v>3</v>
       </c>
-      <c r="F11" s="24">
+      <c r="F11" s="26">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="G11" s="10" t="str">
+      <c r="G11" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Vàng</v>
       </c>
-      <c r="H11" s="23" t="s">
-        <v>122</v>
+      <c r="H11" s="25" t="s">
+        <v>124</v>
       </c>
       <c r="I11" s="11" t="s">
-        <v>153</v>
-      </c>
-      <c r="J11" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="K11" s="23" t="s">
-        <v>141</v>
+        <v>155</v>
+      </c>
+      <c r="J11" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="K11" s="25" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12" s="10" t="s">
-        <v>154</v>
+      <c r="A12" s="13" t="s">
+        <v>156</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>156</v>
-      </c>
-      <c r="D12" s="23">
+        <v>158</v>
+      </c>
+      <c r="D12" s="25">
         <v>3</v>
       </c>
-      <c r="E12" s="23">
+      <c r="E12" s="25">
         <v>5</v>
       </c>
-      <c r="F12" s="24">
+      <c r="F12" s="26">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="G12" s="10" t="str">
+      <c r="G12" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Đỏ</v>
       </c>
-      <c r="H12" s="23" t="s">
-        <v>122</v>
+      <c r="H12" s="25" t="s">
+        <v>124</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>157</v>
-      </c>
-      <c r="J12" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="K12" s="23" t="s">
-        <v>158</v>
+        <v>159</v>
+      </c>
+      <c r="J12" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="K12" s="25" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="10" t="s">
-        <v>159</v>
+      <c r="A13" s="13" t="s">
+        <v>161</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>161</v>
-      </c>
-      <c r="D13" s="23">
+        <v>163</v>
+      </c>
+      <c r="D13" s="25">
         <v>1</v>
       </c>
-      <c r="E13" s="23">
+      <c r="E13" s="25">
         <v>5</v>
       </c>
-      <c r="F13" s="24">
+      <c r="F13" s="26">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="G13" s="10" t="str">
+      <c r="G13" s="13" t="str">
         <f t="shared" si="1"/>
         <v>Xanh</v>
       </c>
-      <c r="H13" s="23" t="s">
-        <v>162</v>
+      <c r="H13" s="25" t="s">
+        <v>164</v>
       </c>
       <c r="I13" s="11" t="s">
-        <v>163</v>
-      </c>
-      <c r="J13" s="10" t="s">
-        <v>124</v>
-      </c>
-      <c r="K13" s="23" t="s">
-        <v>141</v>
+        <v>165</v>
+      </c>
+      <c r="J13" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="K13" s="25" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B15" s="17" t="s">
-        <v>164</v>
-      </c>
-      <c r="F15" s="24">
+      <c r="B15" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="F15" s="26">
         <f>COUNTIF(G5:G13,"Đỏ")</f>
         <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B16" s="17" t="s">
-        <v>165</v>
-      </c>
-      <c r="F16" s="24">
+      <c r="B16" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="F16" s="26">
         <f>COUNTIF(G5:G13,"Vàng")</f>
         <v>3</v>
       </c>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B17" s="17" t="s">
-        <v>166</v>
-      </c>
-      <c r="F17" s="25">
+      <c r="B17" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="F17" s="27">
         <f>AVERAGE(F5:F13)</f>
         <v>12.444444444444445</v>
       </c>
@@ -5544,7 +6116,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="62" customWidth="1"/>
@@ -5552,215 +6124,234 @@
     <col min="3" max="3" width="13" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="30" customWidth="1"/>
+    <col min="7" max="7" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+        <v>175</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
-        <v>174</v>
-      </c>
-      <c r="B5" s="26">
+        <v>177</v>
+      </c>
+      <c r="B5" s="28">
         <v>2.5</v>
       </c>
-      <c r="C5" s="15">
+      <c r="C5" s="17">
         <v>1</v>
       </c>
-      <c r="D5" s="27">
+      <c r="D5" s="29">
         <f>B5*C5</f>
         <v>2.5</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+        <v>178</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
-        <v>176</v>
-      </c>
-      <c r="B6" s="26">
+        <v>179</v>
+      </c>
+      <c r="B6" s="28">
         <v>2.5</v>
       </c>
-      <c r="C6" s="15">
+      <c r="C6" s="17">
         <v>1</v>
       </c>
-      <c r="D6" s="27">
+      <c r="D6" s="29">
         <f>B6*C6</f>
         <v>2.5</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="B7" s="26">
+        <v>181</v>
+      </c>
+      <c r="B7" s="28">
         <v>2</v>
       </c>
-      <c r="C7" s="15">
+      <c r="C7" s="17">
         <v>1</v>
       </c>
-      <c r="D7" s="27">
+      <c r="D7" s="29">
         <f>B7*C7</f>
         <v>2</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+        <v>182</v>
+      </c>
+      <c r="G7" s="11" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
-        <v>180</v>
-      </c>
-      <c r="B8" s="26">
+        <v>183</v>
+      </c>
+      <c r="B8" s="28">
         <v>2</v>
       </c>
-      <c r="C8" s="15">
+      <c r="C8" s="17">
         <v>0</v>
       </c>
-      <c r="D8" s="27">
+      <c r="D8" s="29">
         <f>B8*C8</f>
         <v>0</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+        <v>90</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
-        <v>181</v>
-      </c>
-      <c r="B9" s="26">
+        <v>184</v>
+      </c>
+      <c r="B9" s="28">
         <v>1</v>
       </c>
-      <c r="C9" s="15">
+      <c r="C9" s="17">
         <v>0</v>
       </c>
-      <c r="D9" s="27">
+      <c r="D9" s="29">
         <f>B9*C9</f>
         <v>0</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="17" t="s">
-        <v>183</v>
-      </c>
-      <c r="B10" s="25">
+        <v>185</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="B10" s="27">
         <f>SUM(B5:B9)</f>
         <v>10</v>
       </c>
-      <c r="C10" s="28">
+      <c r="C10" s="30">
         <f>D10/B10</f>
         <v>0.7</v>
       </c>
-      <c r="D10" s="29">
+      <c r="D10" s="31">
         <f>SUM(D5:D9)</f>
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
-        <v>185</v>
-      </c>
-      <c r="C13" s="23" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="26.4" x14ac:dyDescent="0.3">
+        <v>189</v>
+      </c>
+      <c r="C13" s="25" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
-        <v>187</v>
-      </c>
-      <c r="C14" s="23" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+        <v>191</v>
+      </c>
+      <c r="C14" s="25" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
-        <v>189</v>
-      </c>
-      <c r="C15" s="23" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+        <v>193</v>
+      </c>
+      <c r="C15" s="25" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="C16" s="25" t="s">
         <v>190</v>
-      </c>
-      <c r="C16" s="23" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
-        <v>191</v>
-      </c>
-      <c r="C17" s="23" t="s">
-        <v>186</v>
+        <v>195</v>
+      </c>
+      <c r="C17" s="25" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
-        <v>192</v>
-      </c>
-      <c r="C18" s="23" t="s">
-        <v>193</v>
+        <v>196</v>
+      </c>
+      <c r="C18" s="25" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="C19" s="23" t="s">
-        <v>195</v>
+        <v>198</v>
+      </c>
+      <c r="C19" s="25" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="C20" s="23" t="s">
-        <v>186</v>
+        <v>200</v>
+      </c>
+      <c r="C20" s="25" t="s">
+        <v>190</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="C13:C20">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
-      <formula>"Đạt"</formula>
+    <cfRule type="expression" dxfId="2" priority="1">
+      <formula>LEFT(C13,3)="Đạt"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="1" priority="2">
       <formula>LEFT(C13,5)="Chưa "</formula>
@@ -5770,6 +6361,7 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -5786,75 +6378,75 @@
   <sheetData>
     <row r="1" spans="1:4" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="30">
+      <c r="A4" s="32">
         <v>46314</v>
       </c>
-      <c r="B4" s="23">
+      <c r="B4" s="25">
         <v>1</v>
       </c>
-      <c r="C4" s="31" t="s">
-        <v>202</v>
-      </c>
-      <c r="D4" s="10">
+      <c r="C4" s="33" t="s">
+        <v>206</v>
+      </c>
+      <c r="D4" s="13">
         <f>SUM($B$4:B4)</f>
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="30">
+      <c r="A5" s="32">
         <v>46315</v>
       </c>
-      <c r="B5" s="23">
+      <c r="B5" s="25">
         <v>10</v>
       </c>
-      <c r="C5" s="31" t="s">
-        <v>203</v>
-      </c>
-      <c r="D5" s="10">
+      <c r="C5" s="33" t="s">
+        <v>207</v>
+      </c>
+      <c r="D5" s="13">
         <f>SUM($B$4:B5)</f>
         <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A6" s="30">
+      <c r="A6" s="32">
         <v>46321</v>
       </c>
-      <c r="B6" s="23">
-        <v>35</v>
-      </c>
-      <c r="C6" s="31" t="s">
-        <v>204</v>
-      </c>
-      <c r="D6" s="10">
+      <c r="B6" s="25">
+        <v>42</v>
+      </c>
+      <c r="C6" s="33" t="s">
+        <v>208</v>
+      </c>
+      <c r="D6" s="13">
         <f>SUM($B$4:B6)</f>
-        <v>46</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="17" t="s">
-        <v>205</v>
-      </c>
-      <c r="B7" s="24">
+      <c r="A7" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="B7" s="26">
         <f>SUM(B4:B6)</f>
-        <v>46</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
